--- a/Customer Rate Tariff Template_Week 44_2026.xlsx
+++ b/Customer Rate Tariff Template_Week 44_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stephanie.galera.RAMPSLOGISTICS\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6194C3F-41E5-4DC5-850C-CF69400CA460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4066E937-8EAF-46BC-A479-D731B9695AEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{493693A0-0616-4273-B364-7C8DEB21885C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{493693A0-0616-4273-B364-7C8DEB21885C}"/>
   </bookViews>
   <sheets>
     <sheet name="TT" sheetId="28" r:id="rId1"/>
@@ -2037,85 +2037,42 @@
     <xf numFmtId="8" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -2134,19 +2091,46 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2155,113 +2139,29 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2275,14 +2175,23 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2295,6 +2204,36 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2311,104 +2250,50 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2422,30 +2307,145 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -3846,32 +3846,32 @@
       <c r="P7" s="16"/>
     </row>
     <row r="8" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B8" s="257" t="s">
+      <c r="B8" s="193" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="257"/>
-      <c r="D8" s="257"/>
-      <c r="E8" s="257"/>
-      <c r="F8" s="257"/>
-      <c r="G8" s="257"/>
-      <c r="H8" s="257"/>
-      <c r="I8" s="257"/>
-      <c r="J8" s="257"/>
-      <c r="K8" s="257"/>
-      <c r="L8" s="257"/>
-      <c r="M8" s="257"/>
-      <c r="N8" s="257"/>
-      <c r="O8" s="257"/>
-      <c r="P8" s="257"/>
+      <c r="C8" s="193"/>
+      <c r="D8" s="193"/>
+      <c r="E8" s="193"/>
+      <c r="F8" s="193"/>
+      <c r="G8" s="193"/>
+      <c r="H8" s="193"/>
+      <c r="I8" s="193"/>
+      <c r="J8" s="193"/>
+      <c r="K8" s="193"/>
+      <c r="L8" s="193"/>
+      <c r="M8" s="193"/>
+      <c r="N8" s="193"/>
+      <c r="O8" s="193"/>
+      <c r="P8" s="193"/>
     </row>
     <row r="9" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="223" t="s">
+      <c r="C9" s="194" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="223"/>
+      <c r="D9" s="194"/>
       <c r="E9" s="92" t="s">
         <v>3</v>
       </c>
@@ -3910,10 +3910,10 @@
       </c>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B10" s="299" t="s">
+      <c r="B10" s="209" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="299" t="s">
+      <c r="C10" s="209" t="s">
         <v>16</v>
       </c>
       <c r="D10" s="18" t="s">
@@ -3959,8 +3959,8 @@
       </c>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B11" s="300"/>
-      <c r="C11" s="300"/>
+      <c r="B11" s="210"/>
+      <c r="C11" s="210"/>
       <c r="D11" s="18" t="s">
         <v>22</v>
       </c>
@@ -4004,8 +4004,8 @@
       </c>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B12" s="300"/>
-      <c r="C12" s="299" t="s">
+      <c r="B12" s="210"/>
+      <c r="C12" s="209" t="s">
         <v>16</v>
       </c>
       <c r="D12" s="82" t="s">
@@ -4052,8 +4052,8 @@
       </c>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B13" s="300"/>
-      <c r="C13" s="300"/>
+      <c r="B13" s="210"/>
+      <c r="C13" s="210"/>
       <c r="D13" s="82" t="s">
         <v>22</v>
       </c>
@@ -4099,10 +4099,10 @@
       <c r="Q13" s="24"/>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B14" s="301" t="s">
+      <c r="B14" s="211" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="241" t="s">
+      <c r="C14" s="213" t="s">
         <v>16</v>
       </c>
       <c r="D14" s="18" t="s">
@@ -4149,8 +4149,8 @@
       </c>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B15" s="302"/>
-      <c r="C15" s="241"/>
+      <c r="B15" s="212"/>
+      <c r="C15" s="213"/>
       <c r="D15" s="18" t="s">
         <v>22</v>
       </c>
@@ -4195,10 +4195,10 @@
       </c>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B16" s="301" t="s">
+      <c r="B16" s="211" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="301" t="s">
+      <c r="C16" s="211" t="s">
         <v>16</v>
       </c>
       <c r="D16" s="18" t="s">
@@ -4245,8 +4245,8 @@
       </c>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B17" s="302"/>
-      <c r="C17" s="302"/>
+      <c r="B17" s="212"/>
+      <c r="C17" s="212"/>
       <c r="D17" s="18" t="s">
         <v>22</v>
       </c>
@@ -4291,10 +4291,10 @@
       </c>
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B18" s="301" t="s">
+      <c r="B18" s="211" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="241" t="s">
+      <c r="C18" s="213" t="s">
         <v>29</v>
       </c>
       <c r="D18" s="18" t="s">
@@ -4342,8 +4342,8 @@
       <c r="Q18" s="24"/>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B19" s="305"/>
-      <c r="C19" s="241"/>
+      <c r="B19" s="221"/>
+      <c r="C19" s="213"/>
       <c r="D19" s="18" t="s">
         <v>22</v>
       </c>
@@ -4389,8 +4389,8 @@
       <c r="Q19" s="24"/>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B20" s="305"/>
-      <c r="C20" s="241" t="s">
+      <c r="B20" s="221"/>
+      <c r="C20" s="213" t="s">
         <v>16</v>
       </c>
       <c r="D20" s="18" t="s">
@@ -4437,8 +4437,8 @@
       </c>
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B21" s="302"/>
-      <c r="C21" s="241"/>
+      <c r="B21" s="212"/>
+      <c r="C21" s="213"/>
       <c r="D21" s="18" t="s">
         <v>22</v>
       </c>
@@ -4520,74 +4520,74 @@
       <c r="P23" s="161"/>
     </row>
     <row r="24" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="239" t="s">
+      <c r="B24" s="223" t="s">
         <v>33</v>
       </c>
-      <c r="C24" s="239"/>
-      <c r="D24" s="239"/>
-      <c r="E24" s="239"/>
-      <c r="F24" s="239"/>
-      <c r="G24" s="239"/>
-      <c r="H24" s="239"/>
-      <c r="I24" s="239"/>
-      <c r="J24" s="239"/>
-      <c r="K24" s="239"/>
-      <c r="L24" s="239"/>
-      <c r="M24" s="239"/>
-      <c r="N24" s="239"/>
-      <c r="O24" s="239"/>
-      <c r="P24" s="239"/>
+      <c r="C24" s="223"/>
+      <c r="D24" s="223"/>
+      <c r="E24" s="223"/>
+      <c r="F24" s="223"/>
+      <c r="G24" s="223"/>
+      <c r="H24" s="223"/>
+      <c r="I24" s="223"/>
+      <c r="J24" s="223"/>
+      <c r="K24" s="223"/>
+      <c r="L24" s="223"/>
+      <c r="M24" s="223"/>
+      <c r="N24" s="223"/>
+      <c r="O24" s="223"/>
+      <c r="P24" s="223"/>
     </row>
     <row r="25" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B25" s="239"/>
-      <c r="C25" s="239"/>
-      <c r="D25" s="239"/>
-      <c r="E25" s="239"/>
-      <c r="F25" s="239"/>
-      <c r="G25" s="239"/>
-      <c r="H25" s="239"/>
-      <c r="I25" s="239"/>
-      <c r="J25" s="239"/>
-      <c r="K25" s="239"/>
-      <c r="L25" s="239"/>
-      <c r="M25" s="239"/>
-      <c r="N25" s="239"/>
-      <c r="O25" s="239"/>
-      <c r="P25" s="239"/>
+      <c r="B25" s="223"/>
+      <c r="C25" s="223"/>
+      <c r="D25" s="223"/>
+      <c r="E25" s="223"/>
+      <c r="F25" s="223"/>
+      <c r="G25" s="223"/>
+      <c r="H25" s="223"/>
+      <c r="I25" s="223"/>
+      <c r="J25" s="223"/>
+      <c r="K25" s="223"/>
+      <c r="L25" s="223"/>
+      <c r="M25" s="223"/>
+      <c r="N25" s="223"/>
+      <c r="O25" s="223"/>
+      <c r="P25" s="223"/>
     </row>
     <row r="26" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B26" s="239"/>
-      <c r="C26" s="239"/>
-      <c r="D26" s="239"/>
-      <c r="E26" s="239"/>
-      <c r="F26" s="239"/>
-      <c r="G26" s="239"/>
-      <c r="H26" s="239"/>
-      <c r="I26" s="239"/>
-      <c r="J26" s="239"/>
-      <c r="K26" s="239"/>
-      <c r="L26" s="239"/>
-      <c r="M26" s="239"/>
-      <c r="N26" s="239"/>
-      <c r="O26" s="239"/>
-      <c r="P26" s="239"/>
+      <c r="B26" s="223"/>
+      <c r="C26" s="223"/>
+      <c r="D26" s="223"/>
+      <c r="E26" s="223"/>
+      <c r="F26" s="223"/>
+      <c r="G26" s="223"/>
+      <c r="H26" s="223"/>
+      <c r="I26" s="223"/>
+      <c r="J26" s="223"/>
+      <c r="K26" s="223"/>
+      <c r="L26" s="223"/>
+      <c r="M26" s="223"/>
+      <c r="N26" s="223"/>
+      <c r="O26" s="223"/>
+      <c r="P26" s="223"/>
     </row>
     <row r="27" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B27" s="239"/>
-      <c r="C27" s="239"/>
-      <c r="D27" s="239"/>
-      <c r="E27" s="239"/>
-      <c r="F27" s="239"/>
-      <c r="G27" s="239"/>
-      <c r="H27" s="239"/>
-      <c r="I27" s="239"/>
-      <c r="J27" s="239"/>
-      <c r="K27" s="239"/>
-      <c r="L27" s="239"/>
-      <c r="M27" s="239"/>
-      <c r="N27" s="239"/>
-      <c r="O27" s="239"/>
-      <c r="P27" s="239"/>
+      <c r="B27" s="223"/>
+      <c r="C27" s="223"/>
+      <c r="D27" s="223"/>
+      <c r="E27" s="223"/>
+      <c r="F27" s="223"/>
+      <c r="G27" s="223"/>
+      <c r="H27" s="223"/>
+      <c r="I27" s="223"/>
+      <c r="J27" s="223"/>
+      <c r="K27" s="223"/>
+      <c r="L27" s="223"/>
+      <c r="M27" s="223"/>
+      <c r="N27" s="223"/>
+      <c r="O27" s="223"/>
+      <c r="P27" s="223"/>
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B28" s="28"/>
@@ -4716,32 +4716,32 @@
       <c r="Q34" s="26"/>
     </row>
     <row r="35" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B35" s="303" t="s">
+      <c r="B35" s="214" t="s">
         <v>34</v>
       </c>
-      <c r="C35" s="271"/>
-      <c r="D35" s="271"/>
-      <c r="E35" s="271"/>
-      <c r="F35" s="271"/>
-      <c r="G35" s="271"/>
-      <c r="H35" s="271"/>
-      <c r="I35" s="271"/>
-      <c r="J35" s="271"/>
-      <c r="K35" s="271"/>
-      <c r="L35" s="271"/>
-      <c r="M35" s="271"/>
-      <c r="N35" s="271"/>
-      <c r="O35" s="271"/>
-      <c r="P35" s="271"/>
+      <c r="C35" s="191"/>
+      <c r="D35" s="191"/>
+      <c r="E35" s="191"/>
+      <c r="F35" s="191"/>
+      <c r="G35" s="191"/>
+      <c r="H35" s="191"/>
+      <c r="I35" s="191"/>
+      <c r="J35" s="191"/>
+      <c r="K35" s="191"/>
+      <c r="L35" s="191"/>
+      <c r="M35" s="191"/>
+      <c r="N35" s="191"/>
+      <c r="O35" s="191"/>
+      <c r="P35" s="191"/>
     </row>
     <row r="36" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B36" s="92" t="s">
         <v>1</v>
       </c>
-      <c r="C36" s="223" t="s">
+      <c r="C36" s="194" t="s">
         <v>2</v>
       </c>
-      <c r="D36" s="223"/>
+      <c r="D36" s="194"/>
       <c r="E36" s="92" t="s">
         <v>3</v>
       </c>
@@ -4772,13 +4772,13 @@
       <c r="N36" s="92" t="s">
         <v>14</v>
       </c>
-      <c r="O36" s="223" t="s">
+      <c r="O36" s="194" t="s">
         <v>36</v>
       </c>
-      <c r="P36" s="223"/>
+      <c r="P36" s="194"/>
     </row>
     <row r="37" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B37" s="304" t="s">
+      <c r="B37" s="215" t="s">
         <v>37</v>
       </c>
       <c r="C37" s="108" t="s">
@@ -4820,13 +4820,13 @@
       <c r="N37" s="112" t="s">
         <v>39</v>
       </c>
-      <c r="O37" s="224" t="s">
+      <c r="O37" s="216" t="s">
         <v>40</v>
       </c>
-      <c r="P37" s="225"/>
+      <c r="P37" s="217"/>
     </row>
     <row r="38" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B38" s="304"/>
+      <c r="B38" s="215"/>
       <c r="C38" s="108" t="s">
         <v>16</v>
       </c>
@@ -4866,8 +4866,8 @@
       <c r="N38" s="112" t="s">
         <v>39</v>
       </c>
-      <c r="O38" s="228"/>
-      <c r="P38" s="229"/>
+      <c r="O38" s="218"/>
+      <c r="P38" s="219"/>
     </row>
     <row r="39" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="162" t="s">
@@ -4911,10 +4911,10 @@
       <c r="N39" s="65" t="s">
         <v>43</v>
       </c>
-      <c r="O39" s="242" t="s">
+      <c r="O39" s="220" t="s">
         <v>44</v>
       </c>
-      <c r="P39" s="242"/>
+      <c r="P39" s="220"/>
     </row>
     <row r="40" spans="2:17" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="162" t="s">
@@ -5006,10 +5006,10 @@
       <c r="N41" s="112" t="s">
         <v>39</v>
       </c>
-      <c r="O41" s="242" t="s">
+      <c r="O41" s="220" t="s">
         <v>44</v>
       </c>
-      <c r="P41" s="242"/>
+      <c r="P41" s="220"/>
     </row>
     <row r="42" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B42" s="35"/>
@@ -5050,78 +5050,78 @@
       <c r="Q43" s="7"/>
     </row>
     <row r="44" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B44" s="217" t="s">
+      <c r="B44" s="198" t="s">
         <v>33</v>
       </c>
-      <c r="C44" s="218"/>
-      <c r="D44" s="218"/>
-      <c r="E44" s="218"/>
-      <c r="F44" s="218"/>
-      <c r="G44" s="218"/>
-      <c r="H44" s="218"/>
-      <c r="I44" s="218"/>
-      <c r="J44" s="218"/>
-      <c r="K44" s="218"/>
-      <c r="L44" s="218"/>
-      <c r="M44" s="218"/>
-      <c r="N44" s="218"/>
-      <c r="O44" s="218"/>
-      <c r="P44" s="218"/>
-      <c r="Q44" s="219"/>
+      <c r="C44" s="199"/>
+      <c r="D44" s="199"/>
+      <c r="E44" s="199"/>
+      <c r="F44" s="199"/>
+      <c r="G44" s="199"/>
+      <c r="H44" s="199"/>
+      <c r="I44" s="199"/>
+      <c r="J44" s="199"/>
+      <c r="K44" s="199"/>
+      <c r="L44" s="199"/>
+      <c r="M44" s="199"/>
+      <c r="N44" s="199"/>
+      <c r="O44" s="199"/>
+      <c r="P44" s="199"/>
+      <c r="Q44" s="200"/>
     </row>
     <row r="45" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B45" s="217"/>
-      <c r="C45" s="218"/>
-      <c r="D45" s="218"/>
-      <c r="E45" s="218"/>
-      <c r="F45" s="218"/>
-      <c r="G45" s="218"/>
-      <c r="H45" s="218"/>
-      <c r="I45" s="218"/>
-      <c r="J45" s="218"/>
-      <c r="K45" s="218"/>
-      <c r="L45" s="218"/>
-      <c r="M45" s="218"/>
-      <c r="N45" s="218"/>
-      <c r="O45" s="218"/>
-      <c r="P45" s="218"/>
-      <c r="Q45" s="219"/>
+      <c r="B45" s="198"/>
+      <c r="C45" s="199"/>
+      <c r="D45" s="199"/>
+      <c r="E45" s="199"/>
+      <c r="F45" s="199"/>
+      <c r="G45" s="199"/>
+      <c r="H45" s="199"/>
+      <c r="I45" s="199"/>
+      <c r="J45" s="199"/>
+      <c r="K45" s="199"/>
+      <c r="L45" s="199"/>
+      <c r="M45" s="199"/>
+      <c r="N45" s="199"/>
+      <c r="O45" s="199"/>
+      <c r="P45" s="199"/>
+      <c r="Q45" s="200"/>
     </row>
     <row r="46" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B46" s="217"/>
-      <c r="C46" s="218"/>
-      <c r="D46" s="218"/>
-      <c r="E46" s="218"/>
-      <c r="F46" s="218"/>
-      <c r="G46" s="218"/>
-      <c r="H46" s="218"/>
-      <c r="I46" s="218"/>
-      <c r="J46" s="218"/>
-      <c r="K46" s="218"/>
-      <c r="L46" s="218"/>
-      <c r="M46" s="218"/>
-      <c r="N46" s="218"/>
-      <c r="O46" s="218"/>
-      <c r="P46" s="218"/>
-      <c r="Q46" s="219"/>
+      <c r="B46" s="198"/>
+      <c r="C46" s="199"/>
+      <c r="D46" s="199"/>
+      <c r="E46" s="199"/>
+      <c r="F46" s="199"/>
+      <c r="G46" s="199"/>
+      <c r="H46" s="199"/>
+      <c r="I46" s="199"/>
+      <c r="J46" s="199"/>
+      <c r="K46" s="199"/>
+      <c r="L46" s="199"/>
+      <c r="M46" s="199"/>
+      <c r="N46" s="199"/>
+      <c r="O46" s="199"/>
+      <c r="P46" s="199"/>
+      <c r="Q46" s="200"/>
     </row>
     <row r="47" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B47" s="220"/>
-      <c r="C47" s="221"/>
-      <c r="D47" s="221"/>
-      <c r="E47" s="221"/>
-      <c r="F47" s="221"/>
-      <c r="G47" s="221"/>
-      <c r="H47" s="221"/>
-      <c r="I47" s="221"/>
-      <c r="J47" s="221"/>
-      <c r="K47" s="221"/>
-      <c r="L47" s="221"/>
-      <c r="M47" s="221"/>
-      <c r="N47" s="221"/>
-      <c r="O47" s="221"/>
-      <c r="P47" s="221"/>
-      <c r="Q47" s="222"/>
+      <c r="B47" s="201"/>
+      <c r="C47" s="202"/>
+      <c r="D47" s="202"/>
+      <c r="E47" s="202"/>
+      <c r="F47" s="202"/>
+      <c r="G47" s="202"/>
+      <c r="H47" s="202"/>
+      <c r="I47" s="202"/>
+      <c r="J47" s="202"/>
+      <c r="K47" s="202"/>
+      <c r="L47" s="202"/>
+      <c r="M47" s="202"/>
+      <c r="N47" s="202"/>
+      <c r="O47" s="202"/>
+      <c r="P47" s="202"/>
+      <c r="Q47" s="203"/>
     </row>
     <row r="48" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B48" s="28"/>
@@ -5287,35 +5287,35 @@
       <c r="R56" s="26"/>
     </row>
     <row r="57" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B57" s="260" t="s">
+      <c r="B57" s="206" t="s">
         <v>48</v>
       </c>
-      <c r="C57" s="261"/>
-      <c r="D57" s="261"/>
-      <c r="E57" s="261"/>
-      <c r="F57" s="261"/>
-      <c r="G57" s="261"/>
-      <c r="H57" s="261"/>
-      <c r="I57" s="261"/>
-      <c r="J57" s="261"/>
-      <c r="K57" s="261"/>
-      <c r="L57" s="261"/>
-      <c r="M57" s="261"/>
-      <c r="N57" s="261"/>
-      <c r="O57" s="261"/>
-      <c r="P57" s="261"/>
-      <c r="Q57" s="261"/>
-      <c r="R57" s="261"/>
-      <c r="S57" s="262"/>
+      <c r="C57" s="207"/>
+      <c r="D57" s="207"/>
+      <c r="E57" s="207"/>
+      <c r="F57" s="207"/>
+      <c r="G57" s="207"/>
+      <c r="H57" s="207"/>
+      <c r="I57" s="207"/>
+      <c r="J57" s="207"/>
+      <c r="K57" s="207"/>
+      <c r="L57" s="207"/>
+      <c r="M57" s="207"/>
+      <c r="N57" s="207"/>
+      <c r="O57" s="207"/>
+      <c r="P57" s="207"/>
+      <c r="Q57" s="207"/>
+      <c r="R57" s="207"/>
+      <c r="S57" s="224"/>
     </row>
     <row r="58" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B58" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="C58" s="223" t="s">
+      <c r="C58" s="194" t="s">
         <v>2</v>
       </c>
-      <c r="D58" s="223"/>
+      <c r="D58" s="194"/>
       <c r="E58" s="92" t="s">
         <v>3</v>
       </c>
@@ -5355,16 +5355,16 @@
       <c r="Q58" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="R58" s="293" t="s">
+      <c r="R58" s="225" t="s">
         <v>36</v>
       </c>
-      <c r="S58" s="294"/>
+      <c r="S58" s="226"/>
     </row>
     <row r="59" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B59" s="264" t="s">
+      <c r="B59" s="227" t="s">
         <v>53</v>
       </c>
-      <c r="C59" s="265" t="s">
+      <c r="C59" s="222" t="s">
         <v>54</v>
       </c>
       <c r="D59" s="109" t="s">
@@ -5412,14 +5412,14 @@
       <c r="Q59" s="112" t="s">
         <v>39</v>
       </c>
-      <c r="R59" s="295" t="s">
+      <c r="R59" s="234" t="s">
         <v>57</v>
       </c>
-      <c r="S59" s="296"/>
+      <c r="S59" s="235"/>
     </row>
     <row r="60" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B60" s="264"/>
-      <c r="C60" s="265"/>
+      <c r="B60" s="227"/>
+      <c r="C60" s="222"/>
       <c r="D60" s="109" t="s">
         <v>22</v>
       </c>
@@ -5465,14 +5465,14 @@
       <c r="Q60" s="112" t="s">
         <v>39</v>
       </c>
-      <c r="R60" s="295"/>
-      <c r="S60" s="296"/>
+      <c r="R60" s="234"/>
+      <c r="S60" s="235"/>
     </row>
     <row r="61" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="264" t="s">
+      <c r="B61" s="227" t="s">
         <v>58</v>
       </c>
-      <c r="C61" s="265" t="s">
+      <c r="C61" s="222" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="109" t="s">
@@ -5520,12 +5520,12 @@
       <c r="Q61" s="112" t="s">
         <v>39</v>
       </c>
-      <c r="R61" s="295"/>
-      <c r="S61" s="296"/>
+      <c r="R61" s="234"/>
+      <c r="S61" s="235"/>
     </row>
     <row r="62" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B62" s="264"/>
-      <c r="C62" s="265"/>
+      <c r="B62" s="227"/>
+      <c r="C62" s="222"/>
       <c r="D62" s="109" t="s">
         <v>22</v>
       </c>
@@ -5571,14 +5571,14 @@
       <c r="Q62" s="112" t="s">
         <v>39</v>
       </c>
-      <c r="R62" s="297"/>
-      <c r="S62" s="298"/>
+      <c r="R62" s="236"/>
+      <c r="S62" s="237"/>
     </row>
     <row r="63" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="287" t="s">
+      <c r="B63" s="242" t="s">
         <v>59</v>
       </c>
-      <c r="C63" s="289" t="s">
+      <c r="C63" s="196" t="s">
         <v>29</v>
       </c>
       <c r="D63" s="88" t="s">
@@ -5626,14 +5626,14 @@
       <c r="Q63" s="65" t="s">
         <v>61</v>
       </c>
-      <c r="R63" s="224" t="s">
+      <c r="R63" s="216" t="s">
         <v>62</v>
       </c>
-      <c r="S63" s="225"/>
+      <c r="S63" s="217"/>
     </row>
     <row r="64" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B64" s="288"/>
-      <c r="C64" s="290"/>
+      <c r="B64" s="243"/>
+      <c r="C64" s="197"/>
       <c r="D64" s="88" t="s">
         <v>22</v>
       </c>
@@ -5679,14 +5679,14 @@
       <c r="Q64" s="65" t="s">
         <v>61</v>
       </c>
-      <c r="R64" s="228"/>
-      <c r="S64" s="229"/>
+      <c r="R64" s="218"/>
+      <c r="S64" s="219"/>
     </row>
     <row r="65" spans="2:19" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="264" t="s">
+      <c r="B65" s="227" t="s">
         <v>63</v>
       </c>
-      <c r="C65" s="265" t="s">
+      <c r="C65" s="222" t="s">
         <v>54</v>
       </c>
       <c r="D65" s="109" t="s">
@@ -5734,14 +5734,14 @@
       <c r="Q65" s="112" t="s">
         <v>39</v>
       </c>
-      <c r="R65" s="266" t="s">
+      <c r="R65" s="228" t="s">
         <v>64</v>
       </c>
-      <c r="S65" s="267"/>
+      <c r="S65" s="229"/>
     </row>
     <row r="66" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B66" s="264"/>
-      <c r="C66" s="265"/>
+      <c r="B66" s="227"/>
+      <c r="C66" s="222"/>
       <c r="D66" s="109" t="s">
         <v>22</v>
       </c>
@@ -5787,14 +5787,14 @@
       <c r="Q66" s="112" t="s">
         <v>39</v>
       </c>
-      <c r="R66" s="268"/>
-      <c r="S66" s="269"/>
+      <c r="R66" s="230"/>
+      <c r="S66" s="231"/>
     </row>
     <row r="67" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B67" s="287" t="s">
+      <c r="B67" s="242" t="s">
         <v>65</v>
       </c>
-      <c r="C67" s="289" t="s">
+      <c r="C67" s="196" t="s">
         <v>29</v>
       </c>
       <c r="D67" s="88" t="s">
@@ -5842,14 +5842,14 @@
       <c r="Q67" s="65" t="s">
         <v>61</v>
       </c>
-      <c r="R67" s="224" t="s">
+      <c r="R67" s="216" t="s">
         <v>62</v>
       </c>
-      <c r="S67" s="225"/>
+      <c r="S67" s="217"/>
     </row>
     <row r="68" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B68" s="288"/>
-      <c r="C68" s="290"/>
+      <c r="B68" s="243"/>
+      <c r="C68" s="197"/>
       <c r="D68" s="88" t="s">
         <v>22</v>
       </c>
@@ -5895,14 +5895,14 @@
       <c r="Q68" s="65" t="s">
         <v>61</v>
       </c>
-      <c r="R68" s="228"/>
-      <c r="S68" s="229"/>
+      <c r="R68" s="218"/>
+      <c r="S68" s="219"/>
     </row>
     <row r="69" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B69" s="291" t="s">
+      <c r="B69" s="247" t="s">
         <v>66</v>
       </c>
-      <c r="C69" s="265" t="s">
+      <c r="C69" s="222" t="s">
         <v>54</v>
       </c>
       <c r="D69" s="109" t="s">
@@ -5950,14 +5950,14 @@
       <c r="Q69" s="112" t="s">
         <v>39</v>
       </c>
-      <c r="R69" s="266" t="s">
+      <c r="R69" s="228" t="s">
         <v>64</v>
       </c>
-      <c r="S69" s="267"/>
+      <c r="S69" s="229"/>
     </row>
     <row r="70" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B70" s="292"/>
-      <c r="C70" s="265"/>
+      <c r="B70" s="248"/>
+      <c r="C70" s="222"/>
       <c r="D70" s="109" t="s">
         <v>22</v>
       </c>
@@ -6003,14 +6003,14 @@
       <c r="Q70" s="112" t="s">
         <v>39</v>
       </c>
-      <c r="R70" s="268"/>
-      <c r="S70" s="269"/>
+      <c r="R70" s="230"/>
+      <c r="S70" s="231"/>
     </row>
     <row r="71" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B71" s="264" t="s">
+      <c r="B71" s="227" t="s">
         <v>67</v>
       </c>
-      <c r="C71" s="265" t="s">
+      <c r="C71" s="222" t="s">
         <v>54</v>
       </c>
       <c r="D71" s="109" t="s">
@@ -6058,12 +6058,12 @@
       <c r="Q71" s="112" t="s">
         <v>39</v>
       </c>
-      <c r="R71" s="268"/>
-      <c r="S71" s="269"/>
+      <c r="R71" s="230"/>
+      <c r="S71" s="231"/>
     </row>
     <row r="72" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B72" s="264"/>
-      <c r="C72" s="265"/>
+      <c r="B72" s="227"/>
+      <c r="C72" s="222"/>
       <c r="D72" s="109" t="s">
         <v>22</v>
       </c>
@@ -6109,14 +6109,14 @@
       <c r="Q72" s="112" t="s">
         <v>39</v>
       </c>
-      <c r="R72" s="285"/>
-      <c r="S72" s="286"/>
+      <c r="R72" s="232"/>
+      <c r="S72" s="233"/>
     </row>
     <row r="73" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B73" s="282" t="s">
+      <c r="B73" s="244" t="s">
         <v>68</v>
       </c>
-      <c r="C73" s="283" t="s">
+      <c r="C73" s="245" t="s">
         <v>29</v>
       </c>
       <c r="D73" s="154" t="s">
@@ -6164,14 +6164,14 @@
       <c r="Q73" s="156" t="s">
         <v>69</v>
       </c>
-      <c r="R73" s="273" t="s">
+      <c r="R73" s="238" t="s">
         <v>70</v>
       </c>
-      <c r="S73" s="274"/>
+      <c r="S73" s="239"/>
     </row>
     <row r="74" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B74" s="282"/>
-      <c r="C74" s="284"/>
+      <c r="B74" s="244"/>
+      <c r="C74" s="246"/>
       <c r="D74" s="154" t="s">
         <v>22</v>
       </c>
@@ -6217,14 +6217,14 @@
       <c r="Q74" s="156" t="s">
         <v>69</v>
       </c>
-      <c r="R74" s="275"/>
-      <c r="S74" s="276"/>
+      <c r="R74" s="240"/>
+      <c r="S74" s="241"/>
     </row>
     <row r="75" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B75" s="264" t="s">
+      <c r="B75" s="227" t="s">
         <v>71</v>
       </c>
-      <c r="C75" s="265" t="s">
+      <c r="C75" s="222" t="s">
         <v>54</v>
       </c>
       <c r="D75" s="109" t="s">
@@ -6272,14 +6272,14 @@
       <c r="Q75" s="112" t="s">
         <v>39</v>
       </c>
-      <c r="R75" s="266" t="s">
+      <c r="R75" s="228" t="s">
         <v>64</v>
       </c>
-      <c r="S75" s="267"/>
+      <c r="S75" s="229"/>
     </row>
     <row r="76" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B76" s="264"/>
-      <c r="C76" s="265"/>
+      <c r="B76" s="227"/>
+      <c r="C76" s="222"/>
       <c r="D76" s="109" t="s">
         <v>22</v>
       </c>
@@ -6325,14 +6325,14 @@
       <c r="Q76" s="112" t="s">
         <v>39</v>
       </c>
-      <c r="R76" s="268"/>
-      <c r="S76" s="269"/>
+      <c r="R76" s="230"/>
+      <c r="S76" s="231"/>
     </row>
     <row r="77" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B77" s="264" t="s">
+      <c r="B77" s="227" t="s">
         <v>72</v>
       </c>
-      <c r="C77" s="265" t="s">
+      <c r="C77" s="222" t="s">
         <v>54</v>
       </c>
       <c r="D77" s="109" t="s">
@@ -6380,12 +6380,12 @@
       <c r="Q77" s="112" t="s">
         <v>39</v>
       </c>
-      <c r="R77" s="268"/>
-      <c r="S77" s="269"/>
+      <c r="R77" s="230"/>
+      <c r="S77" s="231"/>
     </row>
     <row r="78" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B78" s="264"/>
-      <c r="C78" s="265"/>
+      <c r="B78" s="227"/>
+      <c r="C78" s="222"/>
       <c r="D78" s="109" t="s">
         <v>22</v>
       </c>
@@ -6431,14 +6431,14 @@
       <c r="Q78" s="112" t="s">
         <v>39</v>
       </c>
-      <c r="R78" s="268"/>
-      <c r="S78" s="269"/>
+      <c r="R78" s="230"/>
+      <c r="S78" s="231"/>
     </row>
     <row r="79" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B79" s="264" t="s">
+      <c r="B79" s="227" t="s">
         <v>73</v>
       </c>
-      <c r="C79" s="265" t="s">
+      <c r="C79" s="222" t="s">
         <v>54</v>
       </c>
       <c r="D79" s="109" t="s">
@@ -6486,12 +6486,12 @@
       <c r="Q79" s="112" t="s">
         <v>39</v>
       </c>
-      <c r="R79" s="268"/>
-      <c r="S79" s="269"/>
+      <c r="R79" s="230"/>
+      <c r="S79" s="231"/>
     </row>
     <row r="80" spans="2:19" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B80" s="264"/>
-      <c r="C80" s="265"/>
+      <c r="B80" s="227"/>
+      <c r="C80" s="222"/>
       <c r="D80" s="109" t="s">
         <v>22</v>
       </c>
@@ -6537,39 +6537,39 @@
       <c r="Q80" s="112" t="s">
         <v>39</v>
       </c>
-      <c r="R80" s="285"/>
-      <c r="S80" s="286"/>
+      <c r="R80" s="232"/>
+      <c r="S80" s="233"/>
     </row>
     <row r="81" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B81" s="260" t="s">
+      <c r="B81" s="206" t="s">
         <v>74</v>
       </c>
-      <c r="C81" s="261"/>
-      <c r="D81" s="261"/>
-      <c r="E81" s="261"/>
-      <c r="F81" s="261"/>
-      <c r="G81" s="261"/>
-      <c r="H81" s="261"/>
-      <c r="I81" s="261"/>
-      <c r="J81" s="261"/>
-      <c r="K81" s="261"/>
-      <c r="L81" s="261"/>
-      <c r="M81" s="261"/>
-      <c r="N81" s="261"/>
-      <c r="O81" s="261"/>
-      <c r="P81" s="261"/>
-      <c r="Q81" s="261"/>
-      <c r="R81" s="257"/>
-      <c r="S81" s="277"/>
+      <c r="C81" s="207"/>
+      <c r="D81" s="207"/>
+      <c r="E81" s="207"/>
+      <c r="F81" s="207"/>
+      <c r="G81" s="207"/>
+      <c r="H81" s="207"/>
+      <c r="I81" s="207"/>
+      <c r="J81" s="207"/>
+      <c r="K81" s="207"/>
+      <c r="L81" s="207"/>
+      <c r="M81" s="207"/>
+      <c r="N81" s="207"/>
+      <c r="O81" s="207"/>
+      <c r="P81" s="207"/>
+      <c r="Q81" s="207"/>
+      <c r="R81" s="193"/>
+      <c r="S81" s="252"/>
     </row>
     <row r="82" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B82" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="C82" s="188" t="s">
+      <c r="C82" s="249" t="s">
         <v>2</v>
       </c>
-      <c r="D82" s="189"/>
+      <c r="D82" s="250"/>
       <c r="E82" s="92" t="s">
         <v>3</v>
       </c>
@@ -6609,16 +6609,16 @@
       <c r="Q82" s="92" t="s">
         <v>14</v>
       </c>
-      <c r="R82" s="188" t="s">
+      <c r="R82" s="249" t="s">
         <v>36</v>
       </c>
-      <c r="S82" s="263"/>
+      <c r="S82" s="251"/>
     </row>
     <row r="83" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B83" s="278" t="s">
-        <v>75</v>
-      </c>
-      <c r="C83" s="280" t="s">
+      <c r="B83" s="253" t="s">
+        <v>75</v>
+      </c>
+      <c r="C83" s="255" t="s">
         <v>76</v>
       </c>
       <c r="D83" s="109" t="s">
@@ -6666,14 +6666,14 @@
       <c r="Q83" s="112" t="s">
         <v>39</v>
       </c>
-      <c r="R83" s="273" t="s">
+      <c r="R83" s="238" t="s">
         <v>57</v>
       </c>
-      <c r="S83" s="274"/>
+      <c r="S83" s="239"/>
     </row>
     <row r="84" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B84" s="279"/>
-      <c r="C84" s="281"/>
+      <c r="B84" s="254"/>
+      <c r="C84" s="256"/>
       <c r="D84" s="109" t="s">
         <v>22</v>
       </c>
@@ -6719,39 +6719,39 @@
       <c r="Q84" s="112" t="s">
         <v>39</v>
       </c>
-      <c r="R84" s="275"/>
-      <c r="S84" s="276"/>
+      <c r="R84" s="240"/>
+      <c r="S84" s="241"/>
     </row>
     <row r="85" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B85" s="260" t="s">
+      <c r="B85" s="206" t="s">
         <v>77</v>
       </c>
-      <c r="C85" s="261"/>
-      <c r="D85" s="261"/>
-      <c r="E85" s="261"/>
-      <c r="F85" s="261"/>
-      <c r="G85" s="261"/>
-      <c r="H85" s="261"/>
-      <c r="I85" s="261"/>
-      <c r="J85" s="261"/>
-      <c r="K85" s="261"/>
-      <c r="L85" s="261"/>
-      <c r="M85" s="261"/>
-      <c r="N85" s="261"/>
-      <c r="O85" s="261"/>
-      <c r="P85" s="261"/>
-      <c r="Q85" s="261"/>
-      <c r="R85" s="261"/>
-      <c r="S85" s="262"/>
+      <c r="C85" s="207"/>
+      <c r="D85" s="207"/>
+      <c r="E85" s="207"/>
+      <c r="F85" s="207"/>
+      <c r="G85" s="207"/>
+      <c r="H85" s="207"/>
+      <c r="I85" s="207"/>
+      <c r="J85" s="207"/>
+      <c r="K85" s="207"/>
+      <c r="L85" s="207"/>
+      <c r="M85" s="207"/>
+      <c r="N85" s="207"/>
+      <c r="O85" s="207"/>
+      <c r="P85" s="207"/>
+      <c r="Q85" s="207"/>
+      <c r="R85" s="207"/>
+      <c r="S85" s="224"/>
     </row>
     <row r="86" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B86" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="C86" s="188" t="s">
+      <c r="C86" s="249" t="s">
         <v>2</v>
       </c>
-      <c r="D86" s="189"/>
+      <c r="D86" s="250"/>
       <c r="E86" s="92" t="s">
         <v>3</v>
       </c>
@@ -6791,16 +6791,16 @@
       <c r="Q86" s="92" t="s">
         <v>14</v>
       </c>
-      <c r="R86" s="188" t="s">
+      <c r="R86" s="249" t="s">
         <v>36</v>
       </c>
-      <c r="S86" s="263"/>
+      <c r="S86" s="251"/>
     </row>
     <row r="87" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B87" s="264" t="s">
+      <c r="B87" s="227" t="s">
         <v>78</v>
       </c>
-      <c r="C87" s="265" t="s">
+      <c r="C87" s="222" t="s">
         <v>76</v>
       </c>
       <c r="D87" s="109" t="s">
@@ -6848,14 +6848,14 @@
       <c r="Q87" s="112" t="s">
         <v>39</v>
       </c>
-      <c r="R87" s="273" t="s">
+      <c r="R87" s="238" t="s">
         <v>57</v>
       </c>
-      <c r="S87" s="274"/>
+      <c r="S87" s="239"/>
     </row>
     <row r="88" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B88" s="264"/>
-      <c r="C88" s="265"/>
+      <c r="B88" s="227"/>
+      <c r="C88" s="222"/>
       <c r="D88" s="109" t="s">
         <v>22</v>
       </c>
@@ -6901,39 +6901,39 @@
       <c r="Q88" s="112" t="s">
         <v>39</v>
       </c>
-      <c r="R88" s="275"/>
-      <c r="S88" s="276"/>
+      <c r="R88" s="240"/>
+      <c r="S88" s="241"/>
     </row>
     <row r="89" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B89" s="270" t="s">
+      <c r="B89" s="190" t="s">
         <v>80</v>
       </c>
-      <c r="C89" s="271"/>
-      <c r="D89" s="271"/>
-      <c r="E89" s="271"/>
-      <c r="F89" s="271"/>
-      <c r="G89" s="271"/>
-      <c r="H89" s="271"/>
-      <c r="I89" s="271"/>
-      <c r="J89" s="271"/>
-      <c r="K89" s="271"/>
-      <c r="L89" s="271"/>
-      <c r="M89" s="271"/>
-      <c r="N89" s="271"/>
-      <c r="O89" s="271"/>
-      <c r="P89" s="271"/>
-      <c r="Q89" s="271"/>
-      <c r="R89" s="271"/>
-      <c r="S89" s="272"/>
+      <c r="C89" s="191"/>
+      <c r="D89" s="191"/>
+      <c r="E89" s="191"/>
+      <c r="F89" s="191"/>
+      <c r="G89" s="191"/>
+      <c r="H89" s="191"/>
+      <c r="I89" s="191"/>
+      <c r="J89" s="191"/>
+      <c r="K89" s="191"/>
+      <c r="L89" s="191"/>
+      <c r="M89" s="191"/>
+      <c r="N89" s="191"/>
+      <c r="O89" s="191"/>
+      <c r="P89" s="191"/>
+      <c r="Q89" s="191"/>
+      <c r="R89" s="191"/>
+      <c r="S89" s="257"/>
     </row>
     <row r="90" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B90" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="C90" s="188" t="s">
+      <c r="C90" s="249" t="s">
         <v>2</v>
       </c>
-      <c r="D90" s="189"/>
+      <c r="D90" s="250"/>
       <c r="E90" s="92" t="s">
         <v>3</v>
       </c>
@@ -6973,16 +6973,16 @@
       <c r="Q90" s="92" t="s">
         <v>14</v>
       </c>
-      <c r="R90" s="188" t="s">
+      <c r="R90" s="249" t="s">
         <v>36</v>
       </c>
-      <c r="S90" s="263"/>
+      <c r="S90" s="251"/>
     </row>
     <row r="91" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B91" s="264" t="s">
+      <c r="B91" s="227" t="s">
         <v>81</v>
       </c>
-      <c r="C91" s="265" t="s">
+      <c r="C91" s="222" t="s">
         <v>76</v>
       </c>
       <c r="D91" s="109" t="s">
@@ -7030,14 +7030,14 @@
       <c r="Q91" s="112" t="s">
         <v>39</v>
       </c>
-      <c r="R91" s="273" t="s">
+      <c r="R91" s="238" t="s">
         <v>57</v>
       </c>
-      <c r="S91" s="274"/>
+      <c r="S91" s="239"/>
     </row>
     <row r="92" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B92" s="264"/>
-      <c r="C92" s="265"/>
+      <c r="B92" s="227"/>
+      <c r="C92" s="222"/>
       <c r="D92" s="109" t="s">
         <v>22</v>
       </c>
@@ -7083,39 +7083,39 @@
       <c r="Q92" s="112" t="s">
         <v>39</v>
       </c>
-      <c r="R92" s="275"/>
-      <c r="S92" s="276"/>
+      <c r="R92" s="240"/>
+      <c r="S92" s="241"/>
     </row>
     <row r="93" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B93" s="270" t="s">
+      <c r="B93" s="190" t="s">
         <v>82</v>
       </c>
-      <c r="C93" s="271"/>
-      <c r="D93" s="271"/>
-      <c r="E93" s="271"/>
-      <c r="F93" s="271"/>
-      <c r="G93" s="271"/>
-      <c r="H93" s="271"/>
-      <c r="I93" s="271"/>
-      <c r="J93" s="271"/>
-      <c r="K93" s="271"/>
-      <c r="L93" s="271"/>
-      <c r="M93" s="271"/>
-      <c r="N93" s="271"/>
-      <c r="O93" s="271"/>
-      <c r="P93" s="271"/>
-      <c r="Q93" s="271"/>
-      <c r="R93" s="271"/>
-      <c r="S93" s="272"/>
+      <c r="C93" s="191"/>
+      <c r="D93" s="191"/>
+      <c r="E93" s="191"/>
+      <c r="F93" s="191"/>
+      <c r="G93" s="191"/>
+      <c r="H93" s="191"/>
+      <c r="I93" s="191"/>
+      <c r="J93" s="191"/>
+      <c r="K93" s="191"/>
+      <c r="L93" s="191"/>
+      <c r="M93" s="191"/>
+      <c r="N93" s="191"/>
+      <c r="O93" s="191"/>
+      <c r="P93" s="191"/>
+      <c r="Q93" s="191"/>
+      <c r="R93" s="191"/>
+      <c r="S93" s="257"/>
     </row>
     <row r="94" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B94" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="C94" s="188" t="s">
+      <c r="C94" s="249" t="s">
         <v>2</v>
       </c>
-      <c r="D94" s="189"/>
+      <c r="D94" s="250"/>
       <c r="E94" s="92" t="s">
         <v>3</v>
       </c>
@@ -7155,16 +7155,16 @@
       <c r="Q94" s="92" t="s">
         <v>14</v>
       </c>
-      <c r="R94" s="188" t="s">
+      <c r="R94" s="249" t="s">
         <v>36</v>
       </c>
-      <c r="S94" s="263"/>
+      <c r="S94" s="251"/>
     </row>
     <row r="95" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B95" s="264" t="s">
+      <c r="B95" s="227" t="s">
         <v>83</v>
       </c>
-      <c r="C95" s="265" t="s">
+      <c r="C95" s="222" t="s">
         <v>76</v>
       </c>
       <c r="D95" s="109" t="s">
@@ -7212,14 +7212,14 @@
       <c r="Q95" s="112" t="s">
         <v>39</v>
       </c>
-      <c r="R95" s="273" t="s">
+      <c r="R95" s="238" t="s">
         <v>57</v>
       </c>
-      <c r="S95" s="274"/>
+      <c r="S95" s="239"/>
     </row>
     <row r="96" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B96" s="264"/>
-      <c r="C96" s="265"/>
+      <c r="B96" s="227"/>
+      <c r="C96" s="222"/>
       <c r="D96" s="109" t="s">
         <v>22</v>
       </c>
@@ -7265,39 +7265,39 @@
       <c r="Q96" s="112" t="s">
         <v>39</v>
       </c>
-      <c r="R96" s="275"/>
-      <c r="S96" s="276"/>
+      <c r="R96" s="240"/>
+      <c r="S96" s="241"/>
     </row>
     <row r="97" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B97" s="260" t="s">
+      <c r="B97" s="206" t="s">
         <v>84</v>
       </c>
-      <c r="C97" s="261"/>
-      <c r="D97" s="261"/>
-      <c r="E97" s="261"/>
-      <c r="F97" s="261"/>
-      <c r="G97" s="261"/>
-      <c r="H97" s="261"/>
-      <c r="I97" s="261"/>
-      <c r="J97" s="261"/>
-      <c r="K97" s="261"/>
-      <c r="L97" s="261"/>
-      <c r="M97" s="261"/>
-      <c r="N97" s="261"/>
-      <c r="O97" s="261"/>
-      <c r="P97" s="261"/>
-      <c r="Q97" s="261"/>
-      <c r="R97" s="257"/>
-      <c r="S97" s="257"/>
+      <c r="C97" s="207"/>
+      <c r="D97" s="207"/>
+      <c r="E97" s="207"/>
+      <c r="F97" s="207"/>
+      <c r="G97" s="207"/>
+      <c r="H97" s="207"/>
+      <c r="I97" s="207"/>
+      <c r="J97" s="207"/>
+      <c r="K97" s="207"/>
+      <c r="L97" s="207"/>
+      <c r="M97" s="207"/>
+      <c r="N97" s="207"/>
+      <c r="O97" s="207"/>
+      <c r="P97" s="207"/>
+      <c r="Q97" s="207"/>
+      <c r="R97" s="193"/>
+      <c r="S97" s="193"/>
     </row>
     <row r="98" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B98" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="C98" s="188" t="s">
+      <c r="C98" s="249" t="s">
         <v>2</v>
       </c>
-      <c r="D98" s="189"/>
+      <c r="D98" s="250"/>
       <c r="E98" s="92" t="s">
         <v>3</v>
       </c>
@@ -7337,16 +7337,16 @@
       <c r="Q98" s="92" t="s">
         <v>14</v>
       </c>
-      <c r="R98" s="188" t="s">
+      <c r="R98" s="249" t="s">
         <v>36</v>
       </c>
-      <c r="S98" s="263"/>
+      <c r="S98" s="251"/>
     </row>
     <row r="99" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B99" s="264" t="s">
-        <v>85</v>
-      </c>
-      <c r="C99" s="265" t="s">
+      <c r="B99" s="227" t="s">
+        <v>85</v>
+      </c>
+      <c r="C99" s="222" t="s">
         <v>76</v>
       </c>
       <c r="D99" s="109" t="s">
@@ -7394,15 +7394,15 @@
       <c r="Q99" s="112" t="s">
         <v>39</v>
       </c>
-      <c r="R99" s="266" t="s">
+      <c r="R99" s="228" t="s">
         <v>86</v>
       </c>
-      <c r="S99" s="267"/>
+      <c r="S99" s="229"/>
       <c r="T99"/>
     </row>
     <row r="100" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B100" s="264"/>
-      <c r="C100" s="265"/>
+      <c r="B100" s="227"/>
+      <c r="C100" s="222"/>
       <c r="D100" s="109" t="s">
         <v>22</v>
       </c>
@@ -7448,40 +7448,40 @@
       <c r="Q100" s="112" t="s">
         <v>39</v>
       </c>
-      <c r="R100" s="268"/>
-      <c r="S100" s="269"/>
+      <c r="R100" s="230"/>
+      <c r="S100" s="231"/>
       <c r="T100"/>
     </row>
     <row r="101" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B101" s="260" t="s">
+      <c r="B101" s="206" t="s">
         <v>87</v>
       </c>
-      <c r="C101" s="261"/>
-      <c r="D101" s="261"/>
-      <c r="E101" s="261"/>
-      <c r="F101" s="261"/>
-      <c r="G101" s="261"/>
-      <c r="H101" s="261"/>
-      <c r="I101" s="261"/>
-      <c r="J101" s="261"/>
-      <c r="K101" s="261"/>
-      <c r="L101" s="261"/>
-      <c r="M101" s="261"/>
-      <c r="N101" s="261"/>
-      <c r="O101" s="261"/>
-      <c r="P101" s="261"/>
-      <c r="Q101" s="261"/>
-      <c r="R101" s="261"/>
-      <c r="S101" s="262"/>
+      <c r="C101" s="207"/>
+      <c r="D101" s="207"/>
+      <c r="E101" s="207"/>
+      <c r="F101" s="207"/>
+      <c r="G101" s="207"/>
+      <c r="H101" s="207"/>
+      <c r="I101" s="207"/>
+      <c r="J101" s="207"/>
+      <c r="K101" s="207"/>
+      <c r="L101" s="207"/>
+      <c r="M101" s="207"/>
+      <c r="N101" s="207"/>
+      <c r="O101" s="207"/>
+      <c r="P101" s="207"/>
+      <c r="Q101" s="207"/>
+      <c r="R101" s="207"/>
+      <c r="S101" s="224"/>
     </row>
     <row r="102" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B102" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="C102" s="188" t="s">
+      <c r="C102" s="249" t="s">
         <v>2</v>
       </c>
-      <c r="D102" s="189"/>
+      <c r="D102" s="250"/>
       <c r="E102" s="92" t="s">
         <v>3</v>
       </c>
@@ -7521,16 +7521,16 @@
       <c r="Q102" s="92" t="s">
         <v>14</v>
       </c>
-      <c r="R102" s="188" t="s">
+      <c r="R102" s="249" t="s">
         <v>36</v>
       </c>
-      <c r="S102" s="263"/>
+      <c r="S102" s="251"/>
     </row>
     <row r="103" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B103" s="264" t="s">
+      <c r="B103" s="227" t="s">
         <v>88</v>
       </c>
-      <c r="C103" s="265" t="s">
+      <c r="C103" s="222" t="s">
         <v>29</v>
       </c>
       <c r="D103" s="109" t="s">
@@ -7578,15 +7578,15 @@
       <c r="Q103" s="112" t="s">
         <v>39</v>
       </c>
-      <c r="R103" s="266" t="s">
+      <c r="R103" s="228" t="s">
         <v>86</v>
       </c>
-      <c r="S103" s="267"/>
+      <c r="S103" s="229"/>
       <c r="T103"/>
     </row>
     <row r="104" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B104" s="264"/>
-      <c r="C104" s="265"/>
+      <c r="B104" s="227"/>
+      <c r="C104" s="222"/>
       <c r="D104" s="109" t="s">
         <v>22</v>
       </c>
@@ -7632,8 +7632,8 @@
       <c r="Q104" s="112" t="s">
         <v>39</v>
       </c>
-      <c r="R104" s="268"/>
-      <c r="S104" s="269"/>
+      <c r="R104" s="230"/>
+      <c r="S104" s="231"/>
       <c r="T104"/>
     </row>
     <row r="105" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7657,137 +7657,137 @@
       <c r="S105" s="105"/>
     </row>
     <row r="106" spans="2:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B106" s="247" t="s">
+      <c r="B106" s="260" t="s">
         <v>32</v>
       </c>
-      <c r="C106" s="248"/>
-      <c r="D106" s="248"/>
-      <c r="E106" s="248"/>
-      <c r="F106" s="248"/>
-      <c r="G106" s="248"/>
-      <c r="H106" s="248"/>
-      <c r="I106" s="248"/>
-      <c r="J106" s="248"/>
-      <c r="K106" s="248"/>
-      <c r="L106" s="248"/>
-      <c r="M106" s="248"/>
-      <c r="N106" s="248"/>
-      <c r="O106" s="248"/>
-      <c r="P106" s="248"/>
-      <c r="Q106" s="248"/>
-      <c r="R106" s="248"/>
-      <c r="S106" s="249"/>
+      <c r="C106" s="261"/>
+      <c r="D106" s="261"/>
+      <c r="E106" s="261"/>
+      <c r="F106" s="261"/>
+      <c r="G106" s="261"/>
+      <c r="H106" s="261"/>
+      <c r="I106" s="261"/>
+      <c r="J106" s="261"/>
+      <c r="K106" s="261"/>
+      <c r="L106" s="261"/>
+      <c r="M106" s="261"/>
+      <c r="N106" s="261"/>
+      <c r="O106" s="261"/>
+      <c r="P106" s="261"/>
+      <c r="Q106" s="261"/>
+      <c r="R106" s="261"/>
+      <c r="S106" s="262"/>
     </row>
     <row r="107" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B107" s="250" t="s">
+      <c r="B107" s="263" t="s">
         <v>33</v>
       </c>
-      <c r="C107" s="200"/>
-      <c r="D107" s="200"/>
-      <c r="E107" s="200"/>
-      <c r="F107" s="200"/>
-      <c r="G107" s="200"/>
-      <c r="H107" s="200"/>
-      <c r="I107" s="200"/>
-      <c r="J107" s="200"/>
-      <c r="K107" s="200"/>
-      <c r="L107" s="200"/>
-      <c r="M107" s="200"/>
-      <c r="N107" s="200"/>
-      <c r="O107" s="200"/>
-      <c r="P107" s="200"/>
-      <c r="Q107" s="200"/>
-      <c r="R107" s="200"/>
-      <c r="S107" s="251"/>
+      <c r="C107" s="264"/>
+      <c r="D107" s="264"/>
+      <c r="E107" s="264"/>
+      <c r="F107" s="264"/>
+      <c r="G107" s="264"/>
+      <c r="H107" s="264"/>
+      <c r="I107" s="264"/>
+      <c r="J107" s="264"/>
+      <c r="K107" s="264"/>
+      <c r="L107" s="264"/>
+      <c r="M107" s="264"/>
+      <c r="N107" s="264"/>
+      <c r="O107" s="264"/>
+      <c r="P107" s="264"/>
+      <c r="Q107" s="264"/>
+      <c r="R107" s="264"/>
+      <c r="S107" s="265"/>
     </row>
     <row r="108" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B108" s="250"/>
-      <c r="C108" s="200"/>
-      <c r="D108" s="200"/>
-      <c r="E108" s="200"/>
-      <c r="F108" s="200"/>
-      <c r="G108" s="200"/>
-      <c r="H108" s="200"/>
-      <c r="I108" s="200"/>
-      <c r="J108" s="200"/>
-      <c r="K108" s="200"/>
-      <c r="L108" s="200"/>
-      <c r="M108" s="200"/>
-      <c r="N108" s="200"/>
-      <c r="O108" s="200"/>
-      <c r="P108" s="200"/>
-      <c r="Q108" s="200"/>
-      <c r="R108" s="200"/>
-      <c r="S108" s="251"/>
+      <c r="B108" s="263"/>
+      <c r="C108" s="264"/>
+      <c r="D108" s="264"/>
+      <c r="E108" s="264"/>
+      <c r="F108" s="264"/>
+      <c r="G108" s="264"/>
+      <c r="H108" s="264"/>
+      <c r="I108" s="264"/>
+      <c r="J108" s="264"/>
+      <c r="K108" s="264"/>
+      <c r="L108" s="264"/>
+      <c r="M108" s="264"/>
+      <c r="N108" s="264"/>
+      <c r="O108" s="264"/>
+      <c r="P108" s="264"/>
+      <c r="Q108" s="264"/>
+      <c r="R108" s="264"/>
+      <c r="S108" s="265"/>
     </row>
     <row r="109" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B109" s="250"/>
-      <c r="C109" s="200"/>
-      <c r="D109" s="200"/>
-      <c r="E109" s="200"/>
-      <c r="F109" s="200"/>
-      <c r="G109" s="200"/>
-      <c r="H109" s="200"/>
-      <c r="I109" s="200"/>
-      <c r="J109" s="200"/>
-      <c r="K109" s="200"/>
-      <c r="L109" s="200"/>
-      <c r="M109" s="200"/>
-      <c r="N109" s="200"/>
-      <c r="O109" s="200"/>
-      <c r="P109" s="200"/>
-      <c r="Q109" s="200"/>
-      <c r="R109" s="200"/>
-      <c r="S109" s="251"/>
+      <c r="B109" s="263"/>
+      <c r="C109" s="264"/>
+      <c r="D109" s="264"/>
+      <c r="E109" s="264"/>
+      <c r="F109" s="264"/>
+      <c r="G109" s="264"/>
+      <c r="H109" s="264"/>
+      <c r="I109" s="264"/>
+      <c r="J109" s="264"/>
+      <c r="K109" s="264"/>
+      <c r="L109" s="264"/>
+      <c r="M109" s="264"/>
+      <c r="N109" s="264"/>
+      <c r="O109" s="264"/>
+      <c r="P109" s="264"/>
+      <c r="Q109" s="264"/>
+      <c r="R109" s="264"/>
+      <c r="S109" s="265"/>
     </row>
     <row r="110" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B110" s="252"/>
-      <c r="C110" s="253"/>
-      <c r="D110" s="253"/>
-      <c r="E110" s="253"/>
-      <c r="F110" s="253"/>
-      <c r="G110" s="253"/>
-      <c r="H110" s="253"/>
-      <c r="I110" s="253"/>
-      <c r="J110" s="253"/>
-      <c r="K110" s="253"/>
-      <c r="L110" s="253"/>
-      <c r="M110" s="253"/>
-      <c r="N110" s="253"/>
-      <c r="O110" s="253"/>
-      <c r="P110" s="253"/>
-      <c r="Q110" s="253"/>
-      <c r="R110" s="253"/>
-      <c r="S110" s="254"/>
+      <c r="B110" s="266"/>
+      <c r="C110" s="267"/>
+      <c r="D110" s="267"/>
+      <c r="E110" s="267"/>
+      <c r="F110" s="267"/>
+      <c r="G110" s="267"/>
+      <c r="H110" s="267"/>
+      <c r="I110" s="267"/>
+      <c r="J110" s="267"/>
+      <c r="K110" s="267"/>
+      <c r="L110" s="267"/>
+      <c r="M110" s="267"/>
+      <c r="N110" s="267"/>
+      <c r="O110" s="267"/>
+      <c r="P110" s="267"/>
+      <c r="Q110" s="267"/>
+      <c r="R110" s="267"/>
+      <c r="S110" s="268"/>
     </row>
     <row r="119" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B119" s="246" t="s">
+      <c r="B119" s="269" t="s">
         <v>89</v>
       </c>
-      <c r="C119" s="246"/>
-      <c r="D119" s="246"/>
-      <c r="E119" s="246"/>
-      <c r="F119" s="246"/>
-      <c r="G119" s="246"/>
-      <c r="H119" s="246"/>
-      <c r="I119" s="246"/>
-      <c r="J119" s="246"/>
-      <c r="K119" s="246"/>
-      <c r="L119" s="246"/>
-      <c r="M119" s="246"/>
-      <c r="N119" s="246"/>
-      <c r="O119" s="246"/>
-      <c r="P119" s="246"/>
+      <c r="C119" s="269"/>
+      <c r="D119" s="269"/>
+      <c r="E119" s="269"/>
+      <c r="F119" s="269"/>
+      <c r="G119" s="269"/>
+      <c r="H119" s="269"/>
+      <c r="I119" s="269"/>
+      <c r="J119" s="269"/>
+      <c r="K119" s="269"/>
+      <c r="L119" s="269"/>
+      <c r="M119" s="269"/>
+      <c r="N119" s="269"/>
+      <c r="O119" s="269"/>
+      <c r="P119" s="269"/>
       <c r="Q119" s="100"/>
     </row>
     <row r="120" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B120" s="92" t="s">
         <v>1</v>
       </c>
-      <c r="C120" s="223" t="s">
+      <c r="C120" s="194" t="s">
         <v>2</v>
       </c>
-      <c r="D120" s="223"/>
+      <c r="D120" s="194"/>
       <c r="E120" s="92" t="s">
         <v>3</v>
       </c>
@@ -7818,17 +7818,17 @@
       <c r="N120" s="92" t="s">
         <v>14</v>
       </c>
-      <c r="O120" s="223" t="s">
+      <c r="O120" s="194" t="s">
         <v>36</v>
       </c>
-      <c r="P120" s="223"/>
-      <c r="Q120" s="223"/>
+      <c r="P120" s="194"/>
+      <c r="Q120" s="194"/>
     </row>
     <row r="121" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B121" s="240" t="s">
+      <c r="B121" s="195" t="s">
         <v>91</v>
       </c>
-      <c r="C121" s="241" t="s">
+      <c r="C121" s="213" t="s">
         <v>16</v>
       </c>
       <c r="D121" s="18" t="s">
@@ -7866,15 +7866,15 @@
       <c r="N121" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="O121" s="242" t="s">
+      <c r="O121" s="220" t="s">
         <v>44</v>
       </c>
-      <c r="P121" s="242"/>
-      <c r="Q121" s="242"/>
+      <c r="P121" s="220"/>
+      <c r="Q121" s="220"/>
     </row>
     <row r="122" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B122" s="240"/>
-      <c r="C122" s="241"/>
+      <c r="B122" s="195"/>
+      <c r="C122" s="213"/>
       <c r="D122" s="18" t="s">
         <v>22</v>
       </c>
@@ -7910,9 +7910,9 @@
       <c r="N122" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="O122" s="242"/>
-      <c r="P122" s="242"/>
-      <c r="Q122" s="242"/>
+      <c r="O122" s="220"/>
+      <c r="P122" s="220"/>
+      <c r="Q122" s="220"/>
     </row>
     <row r="123" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B123" s="35"/>
@@ -7953,78 +7953,78 @@
       <c r="Q124" s="7"/>
     </row>
     <row r="125" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B125" s="217" t="s">
+      <c r="B125" s="198" t="s">
         <v>33</v>
       </c>
-      <c r="C125" s="218"/>
-      <c r="D125" s="218"/>
-      <c r="E125" s="218"/>
-      <c r="F125" s="218"/>
-      <c r="G125" s="218"/>
-      <c r="H125" s="218"/>
-      <c r="I125" s="218"/>
-      <c r="J125" s="218"/>
-      <c r="K125" s="218"/>
-      <c r="L125" s="218"/>
-      <c r="M125" s="218"/>
-      <c r="N125" s="218"/>
-      <c r="O125" s="218"/>
-      <c r="P125" s="218"/>
-      <c r="Q125" s="219"/>
+      <c r="C125" s="199"/>
+      <c r="D125" s="199"/>
+      <c r="E125" s="199"/>
+      <c r="F125" s="199"/>
+      <c r="G125" s="199"/>
+      <c r="H125" s="199"/>
+      <c r="I125" s="199"/>
+      <c r="J125" s="199"/>
+      <c r="K125" s="199"/>
+      <c r="L125" s="199"/>
+      <c r="M125" s="199"/>
+      <c r="N125" s="199"/>
+      <c r="O125" s="199"/>
+      <c r="P125" s="199"/>
+      <c r="Q125" s="200"/>
     </row>
     <row r="126" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B126" s="217"/>
-      <c r="C126" s="218"/>
-      <c r="D126" s="218"/>
-      <c r="E126" s="218"/>
-      <c r="F126" s="218"/>
-      <c r="G126" s="218"/>
-      <c r="H126" s="218"/>
-      <c r="I126" s="218"/>
-      <c r="J126" s="218"/>
-      <c r="K126" s="218"/>
-      <c r="L126" s="218"/>
-      <c r="M126" s="218"/>
-      <c r="N126" s="218"/>
-      <c r="O126" s="218"/>
-      <c r="P126" s="218"/>
-      <c r="Q126" s="219"/>
+      <c r="B126" s="198"/>
+      <c r="C126" s="199"/>
+      <c r="D126" s="199"/>
+      <c r="E126" s="199"/>
+      <c r="F126" s="199"/>
+      <c r="G126" s="199"/>
+      <c r="H126" s="199"/>
+      <c r="I126" s="199"/>
+      <c r="J126" s="199"/>
+      <c r="K126" s="199"/>
+      <c r="L126" s="199"/>
+      <c r="M126" s="199"/>
+      <c r="N126" s="199"/>
+      <c r="O126" s="199"/>
+      <c r="P126" s="199"/>
+      <c r="Q126" s="200"/>
     </row>
     <row r="127" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B127" s="217"/>
-      <c r="C127" s="218"/>
-      <c r="D127" s="218"/>
-      <c r="E127" s="218"/>
-      <c r="F127" s="218"/>
-      <c r="G127" s="218"/>
-      <c r="H127" s="218"/>
-      <c r="I127" s="218"/>
-      <c r="J127" s="218"/>
-      <c r="K127" s="218"/>
-      <c r="L127" s="218"/>
-      <c r="M127" s="218"/>
-      <c r="N127" s="218"/>
-      <c r="O127" s="218"/>
-      <c r="P127" s="218"/>
-      <c r="Q127" s="219"/>
+      <c r="B127" s="198"/>
+      <c r="C127" s="199"/>
+      <c r="D127" s="199"/>
+      <c r="E127" s="199"/>
+      <c r="F127" s="199"/>
+      <c r="G127" s="199"/>
+      <c r="H127" s="199"/>
+      <c r="I127" s="199"/>
+      <c r="J127" s="199"/>
+      <c r="K127" s="199"/>
+      <c r="L127" s="199"/>
+      <c r="M127" s="199"/>
+      <c r="N127" s="199"/>
+      <c r="O127" s="199"/>
+      <c r="P127" s="199"/>
+      <c r="Q127" s="200"/>
     </row>
     <row r="128" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B128" s="220"/>
-      <c r="C128" s="221"/>
-      <c r="D128" s="221"/>
-      <c r="E128" s="221"/>
-      <c r="F128" s="221"/>
-      <c r="G128" s="221"/>
-      <c r="H128" s="221"/>
-      <c r="I128" s="221"/>
-      <c r="J128" s="221"/>
-      <c r="K128" s="221"/>
-      <c r="L128" s="221"/>
-      <c r="M128" s="221"/>
-      <c r="N128" s="221"/>
-      <c r="O128" s="221"/>
-      <c r="P128" s="221"/>
-      <c r="Q128" s="222"/>
+      <c r="B128" s="201"/>
+      <c r="C128" s="202"/>
+      <c r="D128" s="202"/>
+      <c r="E128" s="202"/>
+      <c r="F128" s="202"/>
+      <c r="G128" s="202"/>
+      <c r="H128" s="202"/>
+      <c r="I128" s="202"/>
+      <c r="J128" s="202"/>
+      <c r="K128" s="202"/>
+      <c r="L128" s="202"/>
+      <c r="M128" s="202"/>
+      <c r="N128" s="202"/>
+      <c r="O128" s="202"/>
+      <c r="P128" s="202"/>
+      <c r="Q128" s="203"/>
     </row>
     <row r="129" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B129" s="28"/>
@@ -8046,32 +8046,32 @@
     </row>
     <row r="134" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="135" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B135" s="260" t="s">
+      <c r="B135" s="206" t="s">
         <v>94</v>
       </c>
-      <c r="C135" s="261"/>
-      <c r="D135" s="261"/>
-      <c r="E135" s="261"/>
-      <c r="F135" s="261"/>
-      <c r="G135" s="261"/>
-      <c r="H135" s="261"/>
-      <c r="I135" s="261"/>
-      <c r="J135" s="261"/>
-      <c r="K135" s="261"/>
-      <c r="L135" s="261"/>
-      <c r="M135" s="261"/>
-      <c r="N135" s="261"/>
-      <c r="O135" s="261"/>
-      <c r="P135" s="261"/>
+      <c r="C135" s="207"/>
+      <c r="D135" s="207"/>
+      <c r="E135" s="207"/>
+      <c r="F135" s="207"/>
+      <c r="G135" s="207"/>
+      <c r="H135" s="207"/>
+      <c r="I135" s="207"/>
+      <c r="J135" s="207"/>
+      <c r="K135" s="207"/>
+      <c r="L135" s="207"/>
+      <c r="M135" s="207"/>
+      <c r="N135" s="207"/>
+      <c r="O135" s="207"/>
+      <c r="P135" s="207"/>
     </row>
     <row r="136" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B136" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="C136" s="223" t="s">
+      <c r="C136" s="194" t="s">
         <v>2</v>
       </c>
-      <c r="D136" s="223"/>
+      <c r="D136" s="194"/>
       <c r="E136" s="92" t="s">
         <v>3</v>
       </c>
@@ -8120,7 +8120,7 @@
         <v>17</v>
       </c>
       <c r="E137" s="90">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="F137" s="176">
         <v>340</v>
@@ -8139,30 +8139,30 @@
       </c>
       <c r="K137" s="67">
         <f>SUM(E137:J137)</f>
-        <v>2099</v>
+        <v>2199</v>
       </c>
       <c r="L137" s="66">
         <v>200</v>
       </c>
       <c r="M137" s="67">
         <f>SUM(K137:L137)</f>
-        <v>2299</v>
+        <v>2399</v>
       </c>
       <c r="N137" s="65" t="s">
         <v>99</v>
       </c>
       <c r="O137" s="180" t="s">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="P137" s="65" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="138" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B138" s="210" t="s">
+      <c r="B138" s="208" t="s">
         <v>100</v>
       </c>
-      <c r="C138" s="240" t="s">
+      <c r="C138" s="195" t="s">
         <v>29</v>
       </c>
       <c r="D138" s="88" t="s">
@@ -8209,8 +8209,8 @@
       </c>
     </row>
     <row r="139" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B139" s="210"/>
-      <c r="C139" s="240"/>
+      <c r="B139" s="208"/>
+      <c r="C139" s="195"/>
       <c r="D139" s="88" t="s">
         <v>22</v>
       </c>
@@ -8256,32 +8256,32 @@
     </row>
     <row r="141" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="142" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B142" s="260" t="s">
+      <c r="B142" s="206" t="s">
         <v>101</v>
       </c>
-      <c r="C142" s="261"/>
-      <c r="D142" s="261"/>
-      <c r="E142" s="261"/>
-      <c r="F142" s="261"/>
-      <c r="G142" s="261"/>
-      <c r="H142" s="261"/>
-      <c r="I142" s="261"/>
-      <c r="J142" s="261"/>
-      <c r="K142" s="261"/>
-      <c r="L142" s="261"/>
-      <c r="M142" s="261"/>
-      <c r="N142" s="261"/>
-      <c r="O142" s="261"/>
-      <c r="P142" s="261"/>
+      <c r="C142" s="207"/>
+      <c r="D142" s="207"/>
+      <c r="E142" s="207"/>
+      <c r="F142" s="207"/>
+      <c r="G142" s="207"/>
+      <c r="H142" s="207"/>
+      <c r="I142" s="207"/>
+      <c r="J142" s="207"/>
+      <c r="K142" s="207"/>
+      <c r="L142" s="207"/>
+      <c r="M142" s="207"/>
+      <c r="N142" s="207"/>
+      <c r="O142" s="207"/>
+      <c r="P142" s="207"/>
     </row>
     <row r="143" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B143" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="C143" s="223" t="s">
+      <c r="C143" s="194" t="s">
         <v>2</v>
       </c>
-      <c r="D143" s="223"/>
+      <c r="D143" s="194"/>
       <c r="E143" s="92" t="s">
         <v>3</v>
       </c>
@@ -8320,10 +8320,10 @@
       </c>
     </row>
     <row r="144" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B144" s="240" t="s">
+      <c r="B144" s="195" t="s">
         <v>102</v>
       </c>
-      <c r="C144" s="240" t="s">
+      <c r="C144" s="195" t="s">
         <v>16</v>
       </c>
       <c r="D144" s="88" t="s">
@@ -8369,8 +8369,8 @@
       </c>
     </row>
     <row r="145" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B145" s="240"/>
-      <c r="C145" s="240"/>
+      <c r="B145" s="195"/>
+      <c r="C145" s="195"/>
       <c r="D145" s="88" t="s">
         <v>22</v>
       </c>
@@ -8414,10 +8414,10 @@
       </c>
     </row>
     <row r="146" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B146" s="240" t="s">
+      <c r="B146" s="195" t="s">
         <v>105</v>
       </c>
-      <c r="C146" s="240" t="s">
+      <c r="C146" s="195" t="s">
         <v>29</v>
       </c>
       <c r="D146" s="88" t="s">
@@ -8463,8 +8463,8 @@
       </c>
     </row>
     <row r="147" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B147" s="240"/>
-      <c r="C147" s="240"/>
+      <c r="B147" s="195"/>
+      <c r="C147" s="195"/>
       <c r="D147" s="88" t="s">
         <v>22</v>
       </c>
@@ -8534,78 +8534,78 @@
       <c r="Q149" s="7"/>
     </row>
     <row r="150" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B150" s="217" t="s">
+      <c r="B150" s="198" t="s">
         <v>33</v>
       </c>
-      <c r="C150" s="218"/>
-      <c r="D150" s="218"/>
-      <c r="E150" s="218"/>
-      <c r="F150" s="218"/>
-      <c r="G150" s="218"/>
-      <c r="H150" s="218"/>
-      <c r="I150" s="218"/>
-      <c r="J150" s="218"/>
-      <c r="K150" s="218"/>
-      <c r="L150" s="218"/>
-      <c r="M150" s="218"/>
-      <c r="N150" s="218"/>
-      <c r="O150" s="218"/>
-      <c r="P150" s="218"/>
-      <c r="Q150" s="219"/>
+      <c r="C150" s="199"/>
+      <c r="D150" s="199"/>
+      <c r="E150" s="199"/>
+      <c r="F150" s="199"/>
+      <c r="G150" s="199"/>
+      <c r="H150" s="199"/>
+      <c r="I150" s="199"/>
+      <c r="J150" s="199"/>
+      <c r="K150" s="199"/>
+      <c r="L150" s="199"/>
+      <c r="M150" s="199"/>
+      <c r="N150" s="199"/>
+      <c r="O150" s="199"/>
+      <c r="P150" s="199"/>
+      <c r="Q150" s="200"/>
     </row>
     <row r="151" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B151" s="217"/>
-      <c r="C151" s="218"/>
-      <c r="D151" s="218"/>
-      <c r="E151" s="218"/>
-      <c r="F151" s="218"/>
-      <c r="G151" s="218"/>
-      <c r="H151" s="218"/>
-      <c r="I151" s="218"/>
-      <c r="J151" s="218"/>
-      <c r="K151" s="218"/>
-      <c r="L151" s="218"/>
-      <c r="M151" s="218"/>
-      <c r="N151" s="218"/>
-      <c r="O151" s="218"/>
-      <c r="P151" s="218"/>
-      <c r="Q151" s="219"/>
+      <c r="B151" s="198"/>
+      <c r="C151" s="199"/>
+      <c r="D151" s="199"/>
+      <c r="E151" s="199"/>
+      <c r="F151" s="199"/>
+      <c r="G151" s="199"/>
+      <c r="H151" s="199"/>
+      <c r="I151" s="199"/>
+      <c r="J151" s="199"/>
+      <c r="K151" s="199"/>
+      <c r="L151" s="199"/>
+      <c r="M151" s="199"/>
+      <c r="N151" s="199"/>
+      <c r="O151" s="199"/>
+      <c r="P151" s="199"/>
+      <c r="Q151" s="200"/>
     </row>
     <row r="152" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B152" s="217"/>
-      <c r="C152" s="218"/>
-      <c r="D152" s="218"/>
-      <c r="E152" s="218"/>
-      <c r="F152" s="218"/>
-      <c r="G152" s="218"/>
-      <c r="H152" s="218"/>
-      <c r="I152" s="218"/>
-      <c r="J152" s="218"/>
-      <c r="K152" s="218"/>
-      <c r="L152" s="218"/>
-      <c r="M152" s="218"/>
-      <c r="N152" s="218"/>
-      <c r="O152" s="218"/>
-      <c r="P152" s="218"/>
-      <c r="Q152" s="219"/>
+      <c r="B152" s="198"/>
+      <c r="C152" s="199"/>
+      <c r="D152" s="199"/>
+      <c r="E152" s="199"/>
+      <c r="F152" s="199"/>
+      <c r="G152" s="199"/>
+      <c r="H152" s="199"/>
+      <c r="I152" s="199"/>
+      <c r="J152" s="199"/>
+      <c r="K152" s="199"/>
+      <c r="L152" s="199"/>
+      <c r="M152" s="199"/>
+      <c r="N152" s="199"/>
+      <c r="O152" s="199"/>
+      <c r="P152" s="199"/>
+      <c r="Q152" s="200"/>
     </row>
     <row r="153" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B153" s="220"/>
-      <c r="C153" s="221"/>
-      <c r="D153" s="221"/>
-      <c r="E153" s="221"/>
-      <c r="F153" s="221"/>
-      <c r="G153" s="221"/>
-      <c r="H153" s="221"/>
-      <c r="I153" s="221"/>
-      <c r="J153" s="221"/>
-      <c r="K153" s="221"/>
-      <c r="L153" s="221"/>
-      <c r="M153" s="221"/>
-      <c r="N153" s="221"/>
-      <c r="O153" s="221"/>
-      <c r="P153" s="221"/>
-      <c r="Q153" s="222"/>
+      <c r="B153" s="201"/>
+      <c r="C153" s="202"/>
+      <c r="D153" s="202"/>
+      <c r="E153" s="202"/>
+      <c r="F153" s="202"/>
+      <c r="G153" s="202"/>
+      <c r="H153" s="202"/>
+      <c r="I153" s="202"/>
+      <c r="J153" s="202"/>
+      <c r="K153" s="202"/>
+      <c r="L153" s="202"/>
+      <c r="M153" s="202"/>
+      <c r="N153" s="202"/>
+      <c r="O153" s="202"/>
+      <c r="P153" s="202"/>
+      <c r="Q153" s="203"/>
     </row>
     <row r="155" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B155" s="28"/>
@@ -8626,32 +8626,32 @@
     </row>
     <row r="160" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="161" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B161" s="260" t="s">
+      <c r="B161" s="206" t="s">
         <v>106</v>
       </c>
-      <c r="C161" s="261"/>
-      <c r="D161" s="261"/>
-      <c r="E161" s="261"/>
-      <c r="F161" s="261"/>
-      <c r="G161" s="261"/>
-      <c r="H161" s="261"/>
-      <c r="I161" s="261"/>
-      <c r="J161" s="261"/>
-      <c r="K161" s="261"/>
-      <c r="L161" s="261"/>
-      <c r="M161" s="261"/>
-      <c r="N161" s="261"/>
-      <c r="O161" s="261"/>
-      <c r="P161" s="261"/>
+      <c r="C161" s="207"/>
+      <c r="D161" s="207"/>
+      <c r="E161" s="207"/>
+      <c r="F161" s="207"/>
+      <c r="G161" s="207"/>
+      <c r="H161" s="207"/>
+      <c r="I161" s="207"/>
+      <c r="J161" s="207"/>
+      <c r="K161" s="207"/>
+      <c r="L161" s="207"/>
+      <c r="M161" s="207"/>
+      <c r="N161" s="207"/>
+      <c r="O161" s="207"/>
+      <c r="P161" s="207"/>
     </row>
     <row r="162" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B162" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="C162" s="223" t="s">
+      <c r="C162" s="194" t="s">
         <v>2</v>
       </c>
-      <c r="D162" s="223"/>
+      <c r="D162" s="194"/>
       <c r="E162" s="92" t="s">
         <v>3</v>
       </c>
@@ -8690,10 +8690,10 @@
       </c>
     </row>
     <row r="163" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B163" s="210" t="s">
+      <c r="B163" s="208" t="s">
         <v>107</v>
       </c>
-      <c r="C163" s="240" t="s">
+      <c r="C163" s="195" t="s">
         <v>108</v>
       </c>
       <c r="D163" s="88" t="s">
@@ -8739,8 +8739,8 @@
       </c>
     </row>
     <row r="164" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B164" s="210"/>
-      <c r="C164" s="240"/>
+      <c r="B164" s="208"/>
+      <c r="C164" s="195"/>
       <c r="D164" s="88" t="s">
         <v>22</v>
       </c>
@@ -8804,78 +8804,78 @@
       <c r="Q166" s="7"/>
     </row>
     <row r="167" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B167" s="217" t="s">
+      <c r="B167" s="198" t="s">
         <v>33</v>
       </c>
-      <c r="C167" s="218"/>
-      <c r="D167" s="218"/>
-      <c r="E167" s="218"/>
-      <c r="F167" s="218"/>
-      <c r="G167" s="218"/>
-      <c r="H167" s="218"/>
-      <c r="I167" s="218"/>
-      <c r="J167" s="218"/>
-      <c r="K167" s="218"/>
-      <c r="L167" s="218"/>
-      <c r="M167" s="218"/>
-      <c r="N167" s="218"/>
-      <c r="O167" s="218"/>
-      <c r="P167" s="218"/>
-      <c r="Q167" s="219"/>
+      <c r="C167" s="199"/>
+      <c r="D167" s="199"/>
+      <c r="E167" s="199"/>
+      <c r="F167" s="199"/>
+      <c r="G167" s="199"/>
+      <c r="H167" s="199"/>
+      <c r="I167" s="199"/>
+      <c r="J167" s="199"/>
+      <c r="K167" s="199"/>
+      <c r="L167" s="199"/>
+      <c r="M167" s="199"/>
+      <c r="N167" s="199"/>
+      <c r="O167" s="199"/>
+      <c r="P167" s="199"/>
+      <c r="Q167" s="200"/>
     </row>
     <row r="168" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B168" s="217"/>
-      <c r="C168" s="218"/>
-      <c r="D168" s="218"/>
-      <c r="E168" s="218"/>
-      <c r="F168" s="218"/>
-      <c r="G168" s="218"/>
-      <c r="H168" s="218"/>
-      <c r="I168" s="218"/>
-      <c r="J168" s="218"/>
-      <c r="K168" s="218"/>
-      <c r="L168" s="218"/>
-      <c r="M168" s="218"/>
-      <c r="N168" s="218"/>
-      <c r="O168" s="218"/>
-      <c r="P168" s="218"/>
-      <c r="Q168" s="219"/>
+      <c r="B168" s="198"/>
+      <c r="C168" s="199"/>
+      <c r="D168" s="199"/>
+      <c r="E168" s="199"/>
+      <c r="F168" s="199"/>
+      <c r="G168" s="199"/>
+      <c r="H168" s="199"/>
+      <c r="I168" s="199"/>
+      <c r="J168" s="199"/>
+      <c r="K168" s="199"/>
+      <c r="L168" s="199"/>
+      <c r="M168" s="199"/>
+      <c r="N168" s="199"/>
+      <c r="O168" s="199"/>
+      <c r="P168" s="199"/>
+      <c r="Q168" s="200"/>
     </row>
     <row r="169" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B169" s="217"/>
-      <c r="C169" s="218"/>
-      <c r="D169" s="218"/>
-      <c r="E169" s="218"/>
-      <c r="F169" s="218"/>
-      <c r="G169" s="218"/>
-      <c r="H169" s="218"/>
-      <c r="I169" s="218"/>
-      <c r="J169" s="218"/>
-      <c r="K169" s="218"/>
-      <c r="L169" s="218"/>
-      <c r="M169" s="218"/>
-      <c r="N169" s="218"/>
-      <c r="O169" s="218"/>
-      <c r="P169" s="218"/>
-      <c r="Q169" s="219"/>
+      <c r="B169" s="198"/>
+      <c r="C169" s="199"/>
+      <c r="D169" s="199"/>
+      <c r="E169" s="199"/>
+      <c r="F169" s="199"/>
+      <c r="G169" s="199"/>
+      <c r="H169" s="199"/>
+      <c r="I169" s="199"/>
+      <c r="J169" s="199"/>
+      <c r="K169" s="199"/>
+      <c r="L169" s="199"/>
+      <c r="M169" s="199"/>
+      <c r="N169" s="199"/>
+      <c r="O169" s="199"/>
+      <c r="P169" s="199"/>
+      <c r="Q169" s="200"/>
     </row>
     <row r="170" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B170" s="220"/>
-      <c r="C170" s="221"/>
-      <c r="D170" s="221"/>
-      <c r="E170" s="221"/>
-      <c r="F170" s="221"/>
-      <c r="G170" s="221"/>
-      <c r="H170" s="221"/>
-      <c r="I170" s="221"/>
-      <c r="J170" s="221"/>
-      <c r="K170" s="221"/>
-      <c r="L170" s="221"/>
-      <c r="M170" s="221"/>
-      <c r="N170" s="221"/>
-      <c r="O170" s="221"/>
-      <c r="P170" s="221"/>
-      <c r="Q170" s="222"/>
+      <c r="B170" s="201"/>
+      <c r="C170" s="202"/>
+      <c r="D170" s="202"/>
+      <c r="E170" s="202"/>
+      <c r="F170" s="202"/>
+      <c r="G170" s="202"/>
+      <c r="H170" s="202"/>
+      <c r="I170" s="202"/>
+      <c r="J170" s="202"/>
+      <c r="K170" s="202"/>
+      <c r="L170" s="202"/>
+      <c r="M170" s="202"/>
+      <c r="N170" s="202"/>
+      <c r="O170" s="202"/>
+      <c r="P170" s="202"/>
+      <c r="Q170" s="203"/>
     </row>
     <row r="171" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B171" s="28"/>
@@ -8914,31 +8914,31 @@
       <c r="Q172" s="28"/>
     </row>
     <row r="174" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B174" s="256" t="s">
+      <c r="B174" s="192" t="s">
         <v>110</v>
       </c>
-      <c r="C174" s="257"/>
-      <c r="D174" s="257"/>
-      <c r="E174" s="257"/>
-      <c r="F174" s="257"/>
-      <c r="G174" s="257"/>
-      <c r="H174" s="257"/>
-      <c r="I174" s="257"/>
-      <c r="J174" s="257"/>
-      <c r="K174" s="257"/>
-      <c r="L174" s="257"/>
-      <c r="M174" s="257"/>
-      <c r="N174" s="257"/>
-      <c r="O174" s="257"/>
+      <c r="C174" s="193"/>
+      <c r="D174" s="193"/>
+      <c r="E174" s="193"/>
+      <c r="F174" s="193"/>
+      <c r="G174" s="193"/>
+      <c r="H174" s="193"/>
+      <c r="I174" s="193"/>
+      <c r="J174" s="193"/>
+      <c r="K174" s="193"/>
+      <c r="L174" s="193"/>
+      <c r="M174" s="193"/>
+      <c r="N174" s="193"/>
+      <c r="O174" s="193"/>
     </row>
     <row r="175" spans="2:17" ht="72" x14ac:dyDescent="0.3">
       <c r="B175" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="C175" s="223" t="s">
+      <c r="C175" s="194" t="s">
         <v>2</v>
       </c>
-      <c r="D175" s="223"/>
+      <c r="D175" s="194"/>
       <c r="E175" s="92" t="s">
         <v>3</v>
       </c>
@@ -8974,10 +8974,10 @@
       </c>
     </row>
     <row r="176" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B176" s="289" t="s">
+      <c r="B176" s="196" t="s">
         <v>114</v>
       </c>
-      <c r="C176" s="240" t="s">
+      <c r="C176" s="195" t="s">
         <v>16</v>
       </c>
       <c r="D176" s="88" t="s">
@@ -9020,8 +9020,8 @@
       </c>
     </row>
     <row r="177" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B177" s="290"/>
-      <c r="C177" s="240"/>
+      <c r="B177" s="197"/>
+      <c r="C177" s="195"/>
       <c r="D177" s="88" t="s">
         <v>22</v>
       </c>
@@ -9080,32 +9080,32 @@
     </row>
     <row r="186" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="187" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B187" s="260" t="s">
+      <c r="B187" s="206" t="s">
         <v>116</v>
       </c>
-      <c r="C187" s="261"/>
-      <c r="D187" s="261"/>
-      <c r="E187" s="261"/>
-      <c r="F187" s="261"/>
-      <c r="G187" s="261"/>
-      <c r="H187" s="261"/>
-      <c r="I187" s="261"/>
-      <c r="J187" s="261"/>
-      <c r="K187" s="261"/>
-      <c r="L187" s="261"/>
-      <c r="M187" s="261"/>
-      <c r="N187" s="261"/>
-      <c r="O187" s="261"/>
-      <c r="P187" s="261"/>
+      <c r="C187" s="207"/>
+      <c r="D187" s="207"/>
+      <c r="E187" s="207"/>
+      <c r="F187" s="207"/>
+      <c r="G187" s="207"/>
+      <c r="H187" s="207"/>
+      <c r="I187" s="207"/>
+      <c r="J187" s="207"/>
+      <c r="K187" s="207"/>
+      <c r="L187" s="207"/>
+      <c r="M187" s="207"/>
+      <c r="N187" s="207"/>
+      <c r="O187" s="207"/>
+      <c r="P187" s="207"/>
     </row>
     <row r="188" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B188" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="C188" s="223" t="s">
+      <c r="C188" s="194" t="s">
         <v>2</v>
       </c>
-      <c r="D188" s="223"/>
+      <c r="D188" s="194"/>
       <c r="E188" s="92" t="s">
         <v>3</v>
       </c>
@@ -9144,10 +9144,10 @@
       </c>
     </row>
     <row r="189" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B189" s="210" t="s">
+      <c r="B189" s="208" t="s">
         <v>118</v>
       </c>
-      <c r="C189" s="240" t="s">
+      <c r="C189" s="195" t="s">
         <v>98</v>
       </c>
       <c r="D189" s="88" t="s">
@@ -9193,8 +9193,8 @@
       </c>
     </row>
     <row r="190" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B190" s="210"/>
-      <c r="C190" s="240"/>
+      <c r="B190" s="208"/>
+      <c r="C190" s="195"/>
       <c r="D190" s="88" t="s">
         <v>22</v>
       </c>
@@ -9242,6 +9242,105 @@
     </row>
   </sheetData>
   <mergeCells count="123">
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="B161:P161"/>
+    <mergeCell ref="C162:D162"/>
+    <mergeCell ref="B163:B164"/>
+    <mergeCell ref="C163:C164"/>
+    <mergeCell ref="B167:Q170"/>
+    <mergeCell ref="C143:D143"/>
+    <mergeCell ref="B146:B147"/>
+    <mergeCell ref="C146:C147"/>
+    <mergeCell ref="B150:Q153"/>
+    <mergeCell ref="B125:Q128"/>
+    <mergeCell ref="B135:P135"/>
+    <mergeCell ref="C136:D136"/>
+    <mergeCell ref="B138:B139"/>
+    <mergeCell ref="C138:C139"/>
+    <mergeCell ref="B142:P142"/>
+    <mergeCell ref="B144:B145"/>
+    <mergeCell ref="C144:C145"/>
+    <mergeCell ref="B106:S106"/>
+    <mergeCell ref="B107:S110"/>
+    <mergeCell ref="B119:P119"/>
+    <mergeCell ref="C120:D120"/>
+    <mergeCell ref="O120:Q120"/>
+    <mergeCell ref="B121:B122"/>
+    <mergeCell ref="C121:C122"/>
+    <mergeCell ref="O121:Q122"/>
+    <mergeCell ref="B101:S101"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="R102:S102"/>
+    <mergeCell ref="B103:B104"/>
+    <mergeCell ref="C103:C104"/>
+    <mergeCell ref="R103:S104"/>
+    <mergeCell ref="B97:S97"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="R98:S98"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="C99:C100"/>
+    <mergeCell ref="R99:S100"/>
+    <mergeCell ref="B93:S93"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="R94:S94"/>
+    <mergeCell ref="B89:S89"/>
+    <mergeCell ref="B95:B96"/>
+    <mergeCell ref="C95:C96"/>
+    <mergeCell ref="R95:S96"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="R90:S90"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="C91:C92"/>
+    <mergeCell ref="R91:S92"/>
+    <mergeCell ref="B85:S85"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="R86:S86"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="B79:B80"/>
+    <mergeCell ref="R87:S88"/>
+    <mergeCell ref="B81:S81"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="R82:S82"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="C83:C84"/>
+    <mergeCell ref="R83:S84"/>
+    <mergeCell ref="R65:S66"/>
+    <mergeCell ref="R63:S64"/>
+    <mergeCell ref="R67:S68"/>
+    <mergeCell ref="B71:B72"/>
+    <mergeCell ref="C71:C72"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="R69:S72"/>
+    <mergeCell ref="B67:B68"/>
+    <mergeCell ref="C67:C68"/>
+    <mergeCell ref="B69:B70"/>
+    <mergeCell ref="C69:C70"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="C79:C80"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="B24:P27"/>
+    <mergeCell ref="O41:P41"/>
+    <mergeCell ref="B44:Q47"/>
+    <mergeCell ref="B57:S57"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="R58:S58"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="R75:S80"/>
+    <mergeCell ref="B75:B76"/>
+    <mergeCell ref="C75:C76"/>
+    <mergeCell ref="B77:B78"/>
+    <mergeCell ref="C77:C78"/>
+    <mergeCell ref="B59:B60"/>
+    <mergeCell ref="C59:C60"/>
+    <mergeCell ref="R59:S62"/>
+    <mergeCell ref="R73:S74"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="C63:C64"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C65:C66"/>
     <mergeCell ref="B174:O174"/>
     <mergeCell ref="B187:P187"/>
     <mergeCell ref="C188:D188"/>
@@ -9266,105 +9365,6 @@
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="C16:C17"/>
     <mergeCell ref="B18:B21"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="C79:C80"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="B24:P27"/>
-    <mergeCell ref="O41:P41"/>
-    <mergeCell ref="B44:Q47"/>
-    <mergeCell ref="B57:S57"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="R58:S58"/>
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="C61:C62"/>
-    <mergeCell ref="R75:S80"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="C75:C76"/>
-    <mergeCell ref="B77:B78"/>
-    <mergeCell ref="C77:C78"/>
-    <mergeCell ref="B59:B60"/>
-    <mergeCell ref="C59:C60"/>
-    <mergeCell ref="R59:S62"/>
-    <mergeCell ref="R73:S74"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="C63:C64"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C65:C66"/>
-    <mergeCell ref="R65:S66"/>
-    <mergeCell ref="R63:S64"/>
-    <mergeCell ref="R67:S68"/>
-    <mergeCell ref="B71:B72"/>
-    <mergeCell ref="C71:C72"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="C73:C74"/>
-    <mergeCell ref="R69:S72"/>
-    <mergeCell ref="B67:B68"/>
-    <mergeCell ref="C67:C68"/>
-    <mergeCell ref="B69:B70"/>
-    <mergeCell ref="C69:C70"/>
-    <mergeCell ref="B85:S85"/>
-    <mergeCell ref="C86:D86"/>
-    <mergeCell ref="R86:S86"/>
-    <mergeCell ref="B87:B88"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="B79:B80"/>
-    <mergeCell ref="R87:S88"/>
-    <mergeCell ref="B81:S81"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="R82:S82"/>
-    <mergeCell ref="B83:B84"/>
-    <mergeCell ref="C83:C84"/>
-    <mergeCell ref="R83:S84"/>
-    <mergeCell ref="B93:S93"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="R94:S94"/>
-    <mergeCell ref="B89:S89"/>
-    <mergeCell ref="B95:B96"/>
-    <mergeCell ref="C95:C96"/>
-    <mergeCell ref="R95:S96"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="R90:S90"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="C91:C92"/>
-    <mergeCell ref="R91:S92"/>
-    <mergeCell ref="C121:C122"/>
-    <mergeCell ref="O121:Q122"/>
-    <mergeCell ref="B101:S101"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="R102:S102"/>
-    <mergeCell ref="B103:B104"/>
-    <mergeCell ref="C103:C104"/>
-    <mergeCell ref="R103:S104"/>
-    <mergeCell ref="B97:S97"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="R98:S98"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="C99:C100"/>
-    <mergeCell ref="R99:S100"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="B161:P161"/>
-    <mergeCell ref="C162:D162"/>
-    <mergeCell ref="B163:B164"/>
-    <mergeCell ref="C163:C164"/>
-    <mergeCell ref="B167:Q170"/>
-    <mergeCell ref="C143:D143"/>
-    <mergeCell ref="B146:B147"/>
-    <mergeCell ref="C146:C147"/>
-    <mergeCell ref="B150:Q153"/>
-    <mergeCell ref="B125:Q128"/>
-    <mergeCell ref="B135:P135"/>
-    <mergeCell ref="C136:D136"/>
-    <mergeCell ref="B138:B139"/>
-    <mergeCell ref="C138:C139"/>
-    <mergeCell ref="B142:P142"/>
-    <mergeCell ref="B144:B145"/>
-    <mergeCell ref="C144:C145"/>
-    <mergeCell ref="B106:S106"/>
-    <mergeCell ref="B107:S110"/>
-    <mergeCell ref="B119:P119"/>
-    <mergeCell ref="C120:D120"/>
-    <mergeCell ref="O120:Q120"/>
-    <mergeCell ref="B121:B122"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9401,33 +9401,33 @@
   </cols>
   <sheetData>
     <row r="9" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B9" s="257" t="s">
+      <c r="B9" s="193" t="s">
         <v>121</v>
       </c>
-      <c r="C9" s="257"/>
-      <c r="D9" s="257"/>
-      <c r="E9" s="257"/>
-      <c r="F9" s="257"/>
-      <c r="G9" s="257"/>
-      <c r="H9" s="257"/>
-      <c r="I9" s="257"/>
-      <c r="J9" s="257"/>
-      <c r="K9" s="257"/>
-      <c r="L9" s="257"/>
-      <c r="M9" s="257"/>
-      <c r="N9" s="257"/>
-      <c r="O9" s="257"/>
-      <c r="P9" s="257"/>
-      <c r="Q9" s="257"/>
+      <c r="C9" s="193"/>
+      <c r="D9" s="193"/>
+      <c r="E9" s="193"/>
+      <c r="F9" s="193"/>
+      <c r="G9" s="193"/>
+      <c r="H9" s="193"/>
+      <c r="I9" s="193"/>
+      <c r="J9" s="193"/>
+      <c r="K9" s="193"/>
+      <c r="L9" s="193"/>
+      <c r="M9" s="193"/>
+      <c r="N9" s="193"/>
+      <c r="O9" s="193"/>
+      <c r="P9" s="193"/>
+      <c r="Q9" s="193"/>
     </row>
     <row r="10" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="232" t="s">
+      <c r="C10" s="282" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="232"/>
+      <c r="D10" s="282"/>
       <c r="E10" s="8" t="s">
         <v>3</v>
       </c>
@@ -9469,10 +9469,10 @@
       </c>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B11" s="241" t="s">
+      <c r="B11" s="213" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="241" t="s">
+      <c r="C11" s="213" t="s">
         <v>114</v>
       </c>
       <c r="D11" s="41" t="s">
@@ -9522,8 +9522,8 @@
       </c>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B12" s="241"/>
-      <c r="C12" s="241"/>
+      <c r="B12" s="213"/>
+      <c r="C12" s="213"/>
       <c r="D12" s="41" t="s">
         <v>22</v>
       </c>
@@ -9571,10 +9571,10 @@
       </c>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B13" s="241" t="s">
+      <c r="B13" s="213" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="241" t="s">
+      <c r="C13" s="213" t="s">
         <v>114</v>
       </c>
       <c r="D13" s="41" t="s">
@@ -9624,8 +9624,8 @@
       </c>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B14" s="241"/>
-      <c r="C14" s="241"/>
+      <c r="B14" s="213"/>
+      <c r="C14" s="213"/>
       <c r="D14" s="41" t="s">
         <v>22</v>
       </c>
@@ -9673,10 +9673,10 @@
       </c>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B15" s="301" t="s">
+      <c r="B15" s="211" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="241" t="s">
+      <c r="C15" s="213" t="s">
         <v>114</v>
       </c>
       <c r="D15" s="41" t="s">
@@ -9726,8 +9726,8 @@
       </c>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B16" s="301"/>
-      <c r="C16" s="241"/>
+      <c r="B16" s="211"/>
+      <c r="C16" s="213"/>
       <c r="D16" s="41" t="s">
         <v>22</v>
       </c>
@@ -9775,10 +9775,10 @@
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B17" s="241" t="s">
+      <c r="B17" s="213" t="s">
         <v>127</v>
       </c>
-      <c r="C17" s="241" t="s">
+      <c r="C17" s="213" t="s">
         <v>114</v>
       </c>
       <c r="D17" s="41" t="s">
@@ -9828,8 +9828,8 @@
       </c>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B18" s="241"/>
-      <c r="C18" s="241"/>
+      <c r="B18" s="213"/>
+      <c r="C18" s="213"/>
       <c r="D18" s="41" t="s">
         <v>22</v>
       </c>
@@ -9894,103 +9894,103 @@
       <c r="Q19" s="27"/>
     </row>
     <row r="20" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B20" s="306" t="s">
+      <c r="B20" s="286" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="307"/>
-      <c r="D20" s="307"/>
-      <c r="E20" s="307"/>
-      <c r="F20" s="307"/>
-      <c r="G20" s="307"/>
-      <c r="H20" s="307"/>
-      <c r="I20" s="307"/>
-      <c r="J20" s="307"/>
-      <c r="K20" s="307"/>
-      <c r="L20" s="307"/>
-      <c r="M20" s="307"/>
-      <c r="N20" s="307"/>
-      <c r="O20" s="307"/>
-      <c r="P20" s="307"/>
-      <c r="Q20" s="307"/>
-      <c r="R20" s="308"/>
+      <c r="C20" s="287"/>
+      <c r="D20" s="287"/>
+      <c r="E20" s="287"/>
+      <c r="F20" s="287"/>
+      <c r="G20" s="287"/>
+      <c r="H20" s="287"/>
+      <c r="I20" s="287"/>
+      <c r="J20" s="287"/>
+      <c r="K20" s="287"/>
+      <c r="L20" s="287"/>
+      <c r="M20" s="287"/>
+      <c r="N20" s="287"/>
+      <c r="O20" s="287"/>
+      <c r="P20" s="287"/>
+      <c r="Q20" s="287"/>
+      <c r="R20" s="288"/>
     </row>
     <row r="21" spans="2:18" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="196" t="s">
+      <c r="B21" s="289" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="197"/>
-      <c r="D21" s="197"/>
-      <c r="E21" s="197"/>
-      <c r="F21" s="197"/>
-      <c r="G21" s="197"/>
-      <c r="H21" s="197"/>
-      <c r="I21" s="197"/>
-      <c r="J21" s="197"/>
-      <c r="K21" s="197"/>
-      <c r="L21" s="197"/>
-      <c r="M21" s="197"/>
-      <c r="N21" s="197"/>
-      <c r="O21" s="197"/>
-      <c r="P21" s="197"/>
-      <c r="Q21" s="197"/>
-      <c r="R21" s="198"/>
+      <c r="C21" s="290"/>
+      <c r="D21" s="290"/>
+      <c r="E21" s="290"/>
+      <c r="F21" s="290"/>
+      <c r="G21" s="290"/>
+      <c r="H21" s="290"/>
+      <c r="I21" s="290"/>
+      <c r="J21" s="290"/>
+      <c r="K21" s="290"/>
+      <c r="L21" s="290"/>
+      <c r="M21" s="290"/>
+      <c r="N21" s="290"/>
+      <c r="O21" s="290"/>
+      <c r="P21" s="290"/>
+      <c r="Q21" s="290"/>
+      <c r="R21" s="291"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B22" s="199"/>
-      <c r="C22" s="200"/>
-      <c r="D22" s="200"/>
-      <c r="E22" s="200"/>
-      <c r="F22" s="200"/>
-      <c r="G22" s="200"/>
-      <c r="H22" s="200"/>
-      <c r="I22" s="200"/>
-      <c r="J22" s="200"/>
-      <c r="K22" s="200"/>
-      <c r="L22" s="200"/>
-      <c r="M22" s="200"/>
-      <c r="N22" s="200"/>
-      <c r="O22" s="200"/>
-      <c r="P22" s="200"/>
-      <c r="Q22" s="200"/>
-      <c r="R22" s="201"/>
+      <c r="B22" s="292"/>
+      <c r="C22" s="264"/>
+      <c r="D22" s="264"/>
+      <c r="E22" s="264"/>
+      <c r="F22" s="264"/>
+      <c r="G22" s="264"/>
+      <c r="H22" s="264"/>
+      <c r="I22" s="264"/>
+      <c r="J22" s="264"/>
+      <c r="K22" s="264"/>
+      <c r="L22" s="264"/>
+      <c r="M22" s="264"/>
+      <c r="N22" s="264"/>
+      <c r="O22" s="264"/>
+      <c r="P22" s="264"/>
+      <c r="Q22" s="264"/>
+      <c r="R22" s="293"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B23" s="199"/>
-      <c r="C23" s="200"/>
-      <c r="D23" s="200"/>
-      <c r="E23" s="200"/>
-      <c r="F23" s="200"/>
-      <c r="G23" s="200"/>
-      <c r="H23" s="200"/>
-      <c r="I23" s="200"/>
-      <c r="J23" s="200"/>
-      <c r="K23" s="200"/>
-      <c r="L23" s="200"/>
-      <c r="M23" s="200"/>
-      <c r="N23" s="200"/>
-      <c r="O23" s="200"/>
-      <c r="P23" s="200"/>
-      <c r="Q23" s="200"/>
-      <c r="R23" s="201"/>
+      <c r="B23" s="292"/>
+      <c r="C23" s="264"/>
+      <c r="D23" s="264"/>
+      <c r="E23" s="264"/>
+      <c r="F23" s="264"/>
+      <c r="G23" s="264"/>
+      <c r="H23" s="264"/>
+      <c r="I23" s="264"/>
+      <c r="J23" s="264"/>
+      <c r="K23" s="264"/>
+      <c r="L23" s="264"/>
+      <c r="M23" s="264"/>
+      <c r="N23" s="264"/>
+      <c r="O23" s="264"/>
+      <c r="P23" s="264"/>
+      <c r="Q23" s="264"/>
+      <c r="R23" s="293"/>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B24" s="202"/>
-      <c r="C24" s="203"/>
-      <c r="D24" s="203"/>
-      <c r="E24" s="203"/>
-      <c r="F24" s="203"/>
-      <c r="G24" s="203"/>
-      <c r="H24" s="203"/>
-      <c r="I24" s="203"/>
-      <c r="J24" s="203"/>
-      <c r="K24" s="203"/>
-      <c r="L24" s="203"/>
-      <c r="M24" s="203"/>
-      <c r="N24" s="203"/>
-      <c r="O24" s="203"/>
-      <c r="P24" s="203"/>
-      <c r="Q24" s="203"/>
-      <c r="R24" s="204"/>
+      <c r="B24" s="294"/>
+      <c r="C24" s="295"/>
+      <c r="D24" s="295"/>
+      <c r="E24" s="295"/>
+      <c r="F24" s="295"/>
+      <c r="G24" s="295"/>
+      <c r="H24" s="295"/>
+      <c r="I24" s="295"/>
+      <c r="J24" s="295"/>
+      <c r="K24" s="295"/>
+      <c r="L24" s="295"/>
+      <c r="M24" s="295"/>
+      <c r="N24" s="295"/>
+      <c r="O24" s="295"/>
+      <c r="P24" s="295"/>
+      <c r="Q24" s="295"/>
+      <c r="R24" s="296"/>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B25" s="25"/>
@@ -10146,34 +10146,34 @@
       <c r="Q33" s="27"/>
     </row>
     <row r="34" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B34" s="303" t="s">
+      <c r="B34" s="214" t="s">
         <v>129</v>
       </c>
-      <c r="C34" s="303"/>
-      <c r="D34" s="303"/>
-      <c r="E34" s="303"/>
-      <c r="F34" s="303"/>
-      <c r="G34" s="303"/>
-      <c r="H34" s="303"/>
-      <c r="I34" s="303"/>
-      <c r="J34" s="303"/>
-      <c r="K34" s="303"/>
-      <c r="L34" s="303"/>
-      <c r="M34" s="303"/>
-      <c r="N34" s="303"/>
-      <c r="O34" s="303"/>
-      <c r="P34" s="303"/>
-      <c r="Q34" s="303"/>
-      <c r="R34" s="303"/>
+      <c r="C34" s="214"/>
+      <c r="D34" s="214"/>
+      <c r="E34" s="214"/>
+      <c r="F34" s="214"/>
+      <c r="G34" s="214"/>
+      <c r="H34" s="214"/>
+      <c r="I34" s="214"/>
+      <c r="J34" s="214"/>
+      <c r="K34" s="214"/>
+      <c r="L34" s="214"/>
+      <c r="M34" s="214"/>
+      <c r="N34" s="214"/>
+      <c r="O34" s="214"/>
+      <c r="P34" s="214"/>
+      <c r="Q34" s="214"/>
+      <c r="R34" s="214"/>
     </row>
     <row r="35" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B35" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C35" s="232" t="s">
+      <c r="C35" s="282" t="s">
         <v>2</v>
       </c>
-      <c r="D35" s="232"/>
+      <c r="D35" s="282"/>
       <c r="E35" s="98" t="s">
         <v>130</v>
       </c>
@@ -10207,17 +10207,17 @@
       <c r="O35" s="95" t="s">
         <v>123</v>
       </c>
-      <c r="P35" s="223" t="s">
+      <c r="P35" s="194" t="s">
         <v>36</v>
       </c>
-      <c r="Q35" s="223"/>
-      <c r="R35" s="223"/>
+      <c r="Q35" s="194"/>
+      <c r="R35" s="194"/>
     </row>
     <row r="36" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="304" t="s">
+      <c r="B36" s="215" t="s">
         <v>132</v>
       </c>
-      <c r="C36" s="241" t="s">
+      <c r="C36" s="213" t="s">
         <v>114</v>
       </c>
       <c r="D36" s="41" t="s">
@@ -10259,15 +10259,15 @@
       <c r="O36" s="41" t="s">
         <v>125</v>
       </c>
-      <c r="P36" s="224" t="s">
+      <c r="P36" s="216" t="s">
         <v>134</v>
       </c>
-      <c r="Q36" s="319"/>
-      <c r="R36" s="225"/>
+      <c r="Q36" s="277"/>
+      <c r="R36" s="217"/>
     </row>
     <row r="37" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B37" s="304"/>
-      <c r="C37" s="241"/>
+      <c r="B37" s="215"/>
+      <c r="C37" s="213"/>
       <c r="D37" s="41" t="s">
         <v>22</v>
       </c>
@@ -10307,9 +10307,9 @@
       <c r="O37" s="41" t="s">
         <v>125</v>
       </c>
-      <c r="P37" s="226"/>
-      <c r="Q37" s="320"/>
-      <c r="R37" s="227"/>
+      <c r="P37" s="278"/>
+      <c r="Q37" s="279"/>
+      <c r="R37" s="280"/>
     </row>
     <row r="38" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B38" s="162" t="s">
@@ -10359,7 +10359,7 @@
       <c r="P38" s="258" t="s">
         <v>137</v>
       </c>
-      <c r="Q38" s="314"/>
+      <c r="Q38" s="283"/>
       <c r="R38" s="259"/>
     </row>
     <row r="39" spans="2:19" x14ac:dyDescent="0.3">
@@ -10403,86 +10403,86 @@
       <c r="S40" s="7"/>
     </row>
     <row r="41" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B41" s="217" t="s">
+      <c r="B41" s="198" t="s">
         <v>33</v>
       </c>
-      <c r="C41" s="217"/>
-      <c r="D41" s="217"/>
-      <c r="E41" s="217"/>
-      <c r="F41" s="217"/>
-      <c r="G41" s="217"/>
-      <c r="H41" s="217"/>
-      <c r="I41" s="217"/>
-      <c r="J41" s="217"/>
-      <c r="K41" s="217"/>
-      <c r="L41" s="217"/>
-      <c r="M41" s="217"/>
-      <c r="N41" s="217"/>
-      <c r="O41" s="217"/>
-      <c r="P41" s="217"/>
-      <c r="Q41" s="217"/>
-      <c r="R41" s="217"/>
-      <c r="S41" s="217"/>
+      <c r="C41" s="198"/>
+      <c r="D41" s="198"/>
+      <c r="E41" s="198"/>
+      <c r="F41" s="198"/>
+      <c r="G41" s="198"/>
+      <c r="H41" s="198"/>
+      <c r="I41" s="198"/>
+      <c r="J41" s="198"/>
+      <c r="K41" s="198"/>
+      <c r="L41" s="198"/>
+      <c r="M41" s="198"/>
+      <c r="N41" s="198"/>
+      <c r="O41" s="198"/>
+      <c r="P41" s="198"/>
+      <c r="Q41" s="198"/>
+      <c r="R41" s="198"/>
+      <c r="S41" s="198"/>
     </row>
     <row r="42" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B42" s="217"/>
-      <c r="C42" s="217"/>
-      <c r="D42" s="217"/>
-      <c r="E42" s="217"/>
-      <c r="F42" s="217"/>
-      <c r="G42" s="217"/>
-      <c r="H42" s="217"/>
-      <c r="I42" s="217"/>
-      <c r="J42" s="217"/>
-      <c r="K42" s="217"/>
-      <c r="L42" s="217"/>
-      <c r="M42" s="217"/>
-      <c r="N42" s="217"/>
-      <c r="O42" s="217"/>
-      <c r="P42" s="217"/>
-      <c r="Q42" s="217"/>
-      <c r="R42" s="217"/>
-      <c r="S42" s="217"/>
+      <c r="B42" s="198"/>
+      <c r="C42" s="198"/>
+      <c r="D42" s="198"/>
+      <c r="E42" s="198"/>
+      <c r="F42" s="198"/>
+      <c r="G42" s="198"/>
+      <c r="H42" s="198"/>
+      <c r="I42" s="198"/>
+      <c r="J42" s="198"/>
+      <c r="K42" s="198"/>
+      <c r="L42" s="198"/>
+      <c r="M42" s="198"/>
+      <c r="N42" s="198"/>
+      <c r="O42" s="198"/>
+      <c r="P42" s="198"/>
+      <c r="Q42" s="198"/>
+      <c r="R42" s="198"/>
+      <c r="S42" s="198"/>
     </row>
     <row r="43" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B43" s="217"/>
-      <c r="C43" s="217"/>
-      <c r="D43" s="217"/>
-      <c r="E43" s="217"/>
-      <c r="F43" s="217"/>
-      <c r="G43" s="217"/>
-      <c r="H43" s="217"/>
-      <c r="I43" s="217"/>
-      <c r="J43" s="217"/>
-      <c r="K43" s="217"/>
-      <c r="L43" s="217"/>
-      <c r="M43" s="217"/>
-      <c r="N43" s="217"/>
-      <c r="O43" s="217"/>
-      <c r="P43" s="217"/>
-      <c r="Q43" s="217"/>
-      <c r="R43" s="217"/>
-      <c r="S43" s="217"/>
+      <c r="B43" s="198"/>
+      <c r="C43" s="198"/>
+      <c r="D43" s="198"/>
+      <c r="E43" s="198"/>
+      <c r="F43" s="198"/>
+      <c r="G43" s="198"/>
+      <c r="H43" s="198"/>
+      <c r="I43" s="198"/>
+      <c r="J43" s="198"/>
+      <c r="K43" s="198"/>
+      <c r="L43" s="198"/>
+      <c r="M43" s="198"/>
+      <c r="N43" s="198"/>
+      <c r="O43" s="198"/>
+      <c r="P43" s="198"/>
+      <c r="Q43" s="198"/>
+      <c r="R43" s="198"/>
+      <c r="S43" s="198"/>
     </row>
     <row r="44" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B44" s="220"/>
-      <c r="C44" s="220"/>
-      <c r="D44" s="220"/>
-      <c r="E44" s="220"/>
-      <c r="F44" s="220"/>
-      <c r="G44" s="220"/>
-      <c r="H44" s="220"/>
-      <c r="I44" s="220"/>
-      <c r="J44" s="220"/>
-      <c r="K44" s="220"/>
-      <c r="L44" s="220"/>
-      <c r="M44" s="220"/>
-      <c r="N44" s="220"/>
-      <c r="O44" s="220"/>
-      <c r="P44" s="220"/>
-      <c r="Q44" s="220"/>
-      <c r="R44" s="220"/>
-      <c r="S44" s="220"/>
+      <c r="B44" s="201"/>
+      <c r="C44" s="201"/>
+      <c r="D44" s="201"/>
+      <c r="E44" s="201"/>
+      <c r="F44" s="201"/>
+      <c r="G44" s="201"/>
+      <c r="H44" s="201"/>
+      <c r="I44" s="201"/>
+      <c r="J44" s="201"/>
+      <c r="K44" s="201"/>
+      <c r="L44" s="201"/>
+      <c r="M44" s="201"/>
+      <c r="N44" s="201"/>
+      <c r="O44" s="201"/>
+      <c r="P44" s="201"/>
+      <c r="Q44" s="201"/>
+      <c r="R44" s="201"/>
+      <c r="S44" s="201"/>
     </row>
     <row r="45" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B45" s="35"/>
@@ -10640,33 +10640,33 @@
       <c r="R53" s="97"/>
     </row>
     <row r="54" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B54" s="260" t="s">
+      <c r="B54" s="206" t="s">
         <v>139</v>
       </c>
-      <c r="C54" s="260"/>
-      <c r="D54" s="260"/>
-      <c r="E54" s="260"/>
-      <c r="F54" s="260"/>
-      <c r="G54" s="260"/>
-      <c r="H54" s="260"/>
-      <c r="I54" s="260"/>
-      <c r="J54" s="260"/>
-      <c r="K54" s="260"/>
-      <c r="L54" s="260"/>
-      <c r="M54" s="260"/>
-      <c r="N54" s="260"/>
-      <c r="O54" s="260"/>
-      <c r="P54" s="260"/>
-      <c r="Q54" s="260"/>
+      <c r="C54" s="206"/>
+      <c r="D54" s="206"/>
+      <c r="E54" s="206"/>
+      <c r="F54" s="206"/>
+      <c r="G54" s="206"/>
+      <c r="H54" s="206"/>
+      <c r="I54" s="206"/>
+      <c r="J54" s="206"/>
+      <c r="K54" s="206"/>
+      <c r="L54" s="206"/>
+      <c r="M54" s="206"/>
+      <c r="N54" s="206"/>
+      <c r="O54" s="206"/>
+      <c r="P54" s="206"/>
+      <c r="Q54" s="206"/>
     </row>
     <row r="55" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B55" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="C55" s="223" t="s">
+      <c r="C55" s="194" t="s">
         <v>2</v>
       </c>
-      <c r="D55" s="223"/>
+      <c r="D55" s="194"/>
       <c r="E55" s="92" t="s">
         <v>3</v>
       </c>
@@ -10708,10 +10708,10 @@
       </c>
     </row>
     <row r="56" spans="2:18" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="309" t="s">
+      <c r="B56" s="276" t="s">
         <v>143</v>
       </c>
-      <c r="C56" s="310" t="s">
+      <c r="C56" s="281" t="s">
         <v>114</v>
       </c>
       <c r="D56" s="113" t="s">
@@ -10753,7 +10753,7 @@
       <c r="O56" s="175" t="s">
         <v>39</v>
       </c>
-      <c r="P56" s="312" t="s">
+      <c r="P56" s="270" t="s">
         <v>57</v>
       </c>
       <c r="Q56" s="113" t="s">
@@ -10761,8 +10761,8 @@
       </c>
     </row>
     <row r="57" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B57" s="309"/>
-      <c r="C57" s="310"/>
+      <c r="B57" s="276"/>
+      <c r="C57" s="281"/>
       <c r="D57" s="113" t="s">
         <v>22</v>
       </c>
@@ -10802,16 +10802,16 @@
       <c r="O57" s="175" t="s">
         <v>39</v>
       </c>
-      <c r="P57" s="313"/>
+      <c r="P57" s="271"/>
       <c r="Q57" s="113" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="58" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B58" s="309" t="s">
+      <c r="B58" s="276" t="s">
         <v>144</v>
       </c>
-      <c r="C58" s="310" t="s">
+      <c r="C58" s="281" t="s">
         <v>114</v>
       </c>
       <c r="D58" s="113" t="s">
@@ -10853,14 +10853,14 @@
       <c r="O58" s="175" t="s">
         <v>39</v>
       </c>
-      <c r="P58" s="313"/>
+      <c r="P58" s="271"/>
       <c r="Q58" s="113" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="59" spans="2:18" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="309"/>
-      <c r="C59" s="310"/>
+      <c r="B59" s="276"/>
+      <c r="C59" s="281"/>
       <c r="D59" s="113" t="s">
         <v>22</v>
       </c>
@@ -10900,16 +10900,16 @@
       <c r="O59" s="175" t="s">
         <v>39</v>
       </c>
-      <c r="P59" s="315"/>
+      <c r="P59" s="272"/>
       <c r="Q59" s="113" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="60" spans="2:18" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="309" t="s">
+      <c r="B60" s="276" t="s">
         <v>145</v>
       </c>
-      <c r="C60" s="310" t="s">
+      <c r="C60" s="281" t="s">
         <v>114</v>
       </c>
       <c r="D60" s="113" t="s">
@@ -10951,7 +10951,7 @@
       <c r="O60" s="175" t="s">
         <v>61</v>
       </c>
-      <c r="P60" s="316" t="s">
+      <c r="P60" s="273" t="s">
         <v>62</v>
       </c>
       <c r="Q60" s="113" t="s">
@@ -10959,8 +10959,8 @@
       </c>
     </row>
     <row r="61" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B61" s="309"/>
-      <c r="C61" s="310"/>
+      <c r="B61" s="276"/>
+      <c r="C61" s="281"/>
       <c r="D61" s="113" t="s">
         <v>22</v>
       </c>
@@ -11000,16 +11000,16 @@
       <c r="O61" s="175" t="s">
         <v>61</v>
       </c>
-      <c r="P61" s="317"/>
+      <c r="P61" s="274"/>
       <c r="Q61" s="113" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="62" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B62" s="309" t="s">
+      <c r="B62" s="276" t="s">
         <v>147</v>
       </c>
-      <c r="C62" s="310" t="s">
+      <c r="C62" s="281" t="s">
         <v>114</v>
       </c>
       <c r="D62" s="113" t="s">
@@ -11051,14 +11051,14 @@
       <c r="O62" s="175" t="s">
         <v>61</v>
       </c>
-      <c r="P62" s="317"/>
+      <c r="P62" s="274"/>
       <c r="Q62" s="113" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="63" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B63" s="309"/>
-      <c r="C63" s="310"/>
+      <c r="B63" s="276"/>
+      <c r="C63" s="281"/>
       <c r="D63" s="113" t="s">
         <v>22</v>
       </c>
@@ -11098,39 +11098,39 @@
       <c r="O63" s="175" t="s">
         <v>61</v>
       </c>
-      <c r="P63" s="318"/>
+      <c r="P63" s="275"/>
       <c r="Q63" s="113" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="64" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B64" s="270" t="s">
+      <c r="B64" s="190" t="s">
         <v>148</v>
       </c>
-      <c r="C64" s="270"/>
-      <c r="D64" s="256"/>
-      <c r="E64" s="256"/>
-      <c r="F64" s="270"/>
-      <c r="G64" s="256"/>
-      <c r="H64" s="256"/>
-      <c r="I64" s="270"/>
-      <c r="J64" s="256"/>
-      <c r="K64" s="256"/>
-      <c r="L64" s="256"/>
-      <c r="M64" s="270"/>
-      <c r="N64" s="256"/>
-      <c r="O64" s="256"/>
-      <c r="P64" s="256"/>
-      <c r="Q64" s="256"/>
+      <c r="C64" s="190"/>
+      <c r="D64" s="192"/>
+      <c r="E64" s="192"/>
+      <c r="F64" s="190"/>
+      <c r="G64" s="192"/>
+      <c r="H64" s="192"/>
+      <c r="I64" s="190"/>
+      <c r="J64" s="192"/>
+      <c r="K64" s="192"/>
+      <c r="L64" s="192"/>
+      <c r="M64" s="190"/>
+      <c r="N64" s="192"/>
+      <c r="O64" s="192"/>
+      <c r="P64" s="192"/>
+      <c r="Q64" s="192"/>
     </row>
     <row r="65" spans="2:62 3072:12198 12789:15082" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B65" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="C65" s="223" t="s">
+      <c r="C65" s="194" t="s">
         <v>2</v>
       </c>
-      <c r="D65" s="223"/>
+      <c r="D65" s="194"/>
       <c r="E65" s="8" t="s">
         <v>3</v>
       </c>
@@ -11172,7 +11172,7 @@
       </c>
     </row>
     <row r="66" spans="2:62 3072:12198 12789:15082" x14ac:dyDescent="0.3">
-      <c r="B66" s="278" t="s">
+      <c r="B66" s="253" t="s">
         <v>149</v>
       </c>
       <c r="C66" s="178" t="s">
@@ -11217,7 +11217,7 @@
       <c r="O66" s="175" t="s">
         <v>39</v>
       </c>
-      <c r="P66" s="312" t="s">
+      <c r="P66" s="270" t="s">
         <v>57</v>
       </c>
       <c r="Q66" s="119" t="s">
@@ -42673,7 +42673,7 @@
       </c>
     </row>
     <row r="67" spans="2:62 3072:12198 12789:15082" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B67" s="311"/>
+      <c r="B67" s="284"/>
       <c r="C67" s="178" t="s">
         <v>114</v>
       </c>
@@ -42716,7 +42716,7 @@
       <c r="O67" s="175" t="s">
         <v>39</v>
       </c>
-      <c r="P67" s="313"/>
+      <c r="P67" s="271"/>
       <c r="Q67" s="119" t="s">
         <v>92</v>
       </c>
@@ -54188,33 +54188,33 @@
       <c r="VHB67" s="128"/>
     </row>
     <row r="68" spans="2:62 3072:12198 12789:15082" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B68" s="260" t="s">
-        <v>150</v>
-      </c>
-      <c r="C68" s="260"/>
-      <c r="D68" s="260"/>
-      <c r="E68" s="260"/>
-      <c r="F68" s="260"/>
-      <c r="G68" s="260"/>
-      <c r="H68" s="260"/>
-      <c r="I68" s="260"/>
-      <c r="J68" s="260"/>
-      <c r="K68" s="260"/>
-      <c r="L68" s="260"/>
-      <c r="M68" s="260"/>
-      <c r="N68" s="260"/>
-      <c r="O68" s="260"/>
-      <c r="P68" s="260"/>
-      <c r="Q68" s="260"/>
+      <c r="B68" s="206" t="s">
+        <v>150</v>
+      </c>
+      <c r="C68" s="206"/>
+      <c r="D68" s="206"/>
+      <c r="E68" s="206"/>
+      <c r="F68" s="206"/>
+      <c r="G68" s="206"/>
+      <c r="H68" s="206"/>
+      <c r="I68" s="206"/>
+      <c r="J68" s="206"/>
+      <c r="K68" s="206"/>
+      <c r="L68" s="206"/>
+      <c r="M68" s="206"/>
+      <c r="N68" s="206"/>
+      <c r="O68" s="206"/>
+      <c r="P68" s="206"/>
+      <c r="Q68" s="206"/>
     </row>
     <row r="69" spans="2:62 3072:12198 12789:15082" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B69" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="C69" s="223" t="s">
+      <c r="C69" s="194" t="s">
         <v>2</v>
       </c>
-      <c r="D69" s="223"/>
+      <c r="D69" s="194"/>
       <c r="E69" s="8" t="s">
         <v>3</v>
       </c>
@@ -54256,7 +54256,7 @@
       </c>
     </row>
     <row r="70" spans="2:62 3072:12198 12789:15082" x14ac:dyDescent="0.3">
-      <c r="B70" s="278" t="s">
+      <c r="B70" s="253" t="s">
         <v>151</v>
       </c>
       <c r="C70" s="178" t="s">
@@ -54301,7 +54301,7 @@
       <c r="O70" s="175" t="s">
         <v>39</v>
       </c>
-      <c r="P70" s="312" t="s">
+      <c r="P70" s="270" t="s">
         <v>57</v>
       </c>
       <c r="Q70" s="119" t="s">
@@ -54309,7 +54309,7 @@
       </c>
     </row>
     <row r="71" spans="2:62 3072:12198 12789:15082" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B71" s="311"/>
+      <c r="B71" s="284"/>
       <c r="C71" s="178" t="s">
         <v>114</v>
       </c>
@@ -54352,7 +54352,7 @@
       <c r="O71" s="175" t="s">
         <v>39</v>
       </c>
-      <c r="P71" s="313"/>
+      <c r="P71" s="271"/>
       <c r="Q71" s="119" t="s">
         <v>92</v>
       </c>
@@ -54398,121 +54398,121 @@
       <c r="T74" s="6"/>
     </row>
     <row r="75" spans="2:62 3072:12198 12789:15082" x14ac:dyDescent="0.3">
-      <c r="B75" s="239" t="s">
+      <c r="B75" s="223" t="s">
         <v>33</v>
       </c>
-      <c r="C75" s="239"/>
-      <c r="D75" s="239"/>
-      <c r="E75" s="239"/>
-      <c r="F75" s="239"/>
-      <c r="G75" s="239"/>
-      <c r="H75" s="239"/>
-      <c r="I75" s="239"/>
-      <c r="J75" s="239"/>
-      <c r="K75" s="239"/>
-      <c r="L75" s="239"/>
-      <c r="M75" s="239"/>
-      <c r="N75" s="239"/>
-      <c r="O75" s="239"/>
-      <c r="P75" s="239"/>
-      <c r="Q75" s="239"/>
-      <c r="R75" s="239"/>
-      <c r="S75" s="239"/>
-      <c r="T75" s="239"/>
+      <c r="C75" s="223"/>
+      <c r="D75" s="223"/>
+      <c r="E75" s="223"/>
+      <c r="F75" s="223"/>
+      <c r="G75" s="223"/>
+      <c r="H75" s="223"/>
+      <c r="I75" s="223"/>
+      <c r="J75" s="223"/>
+      <c r="K75" s="223"/>
+      <c r="L75" s="223"/>
+      <c r="M75" s="223"/>
+      <c r="N75" s="223"/>
+      <c r="O75" s="223"/>
+      <c r="P75" s="223"/>
+      <c r="Q75" s="223"/>
+      <c r="R75" s="223"/>
+      <c r="S75" s="223"/>
+      <c r="T75" s="223"/>
     </row>
     <row r="76" spans="2:62 3072:12198 12789:15082" x14ac:dyDescent="0.3">
-      <c r="B76" s="239"/>
-      <c r="C76" s="239"/>
-      <c r="D76" s="239"/>
-      <c r="E76" s="239"/>
-      <c r="F76" s="239"/>
-      <c r="G76" s="239"/>
-      <c r="H76" s="239"/>
-      <c r="I76" s="239"/>
-      <c r="J76" s="239"/>
-      <c r="K76" s="239"/>
-      <c r="L76" s="239"/>
-      <c r="M76" s="239"/>
-      <c r="N76" s="239"/>
-      <c r="O76" s="239"/>
-      <c r="P76" s="239"/>
-      <c r="Q76" s="239"/>
-      <c r="R76" s="239"/>
-      <c r="S76" s="239"/>
-      <c r="T76" s="239"/>
+      <c r="B76" s="223"/>
+      <c r="C76" s="223"/>
+      <c r="D76" s="223"/>
+      <c r="E76" s="223"/>
+      <c r="F76" s="223"/>
+      <c r="G76" s="223"/>
+      <c r="H76" s="223"/>
+      <c r="I76" s="223"/>
+      <c r="J76" s="223"/>
+      <c r="K76" s="223"/>
+      <c r="L76" s="223"/>
+      <c r="M76" s="223"/>
+      <c r="N76" s="223"/>
+      <c r="O76" s="223"/>
+      <c r="P76" s="223"/>
+      <c r="Q76" s="223"/>
+      <c r="R76" s="223"/>
+      <c r="S76" s="223"/>
+      <c r="T76" s="223"/>
     </row>
     <row r="77" spans="2:62 3072:12198 12789:15082" x14ac:dyDescent="0.3">
-      <c r="B77" s="239"/>
-      <c r="C77" s="239"/>
-      <c r="D77" s="239"/>
-      <c r="E77" s="239"/>
-      <c r="F77" s="239"/>
-      <c r="G77" s="239"/>
-      <c r="H77" s="239"/>
-      <c r="I77" s="239"/>
-      <c r="J77" s="239"/>
-      <c r="K77" s="239"/>
-      <c r="L77" s="239"/>
-      <c r="M77" s="239"/>
-      <c r="N77" s="239"/>
-      <c r="O77" s="239"/>
-      <c r="P77" s="239"/>
-      <c r="Q77" s="239"/>
-      <c r="R77" s="239"/>
-      <c r="S77" s="239"/>
-      <c r="T77" s="239"/>
+      <c r="B77" s="223"/>
+      <c r="C77" s="223"/>
+      <c r="D77" s="223"/>
+      <c r="E77" s="223"/>
+      <c r="F77" s="223"/>
+      <c r="G77" s="223"/>
+      <c r="H77" s="223"/>
+      <c r="I77" s="223"/>
+      <c r="J77" s="223"/>
+      <c r="K77" s="223"/>
+      <c r="L77" s="223"/>
+      <c r="M77" s="223"/>
+      <c r="N77" s="223"/>
+      <c r="O77" s="223"/>
+      <c r="P77" s="223"/>
+      <c r="Q77" s="223"/>
+      <c r="R77" s="223"/>
+      <c r="S77" s="223"/>
+      <c r="T77" s="223"/>
     </row>
     <row r="78" spans="2:62 3072:12198 12789:15082" x14ac:dyDescent="0.3">
-      <c r="B78" s="239"/>
-      <c r="C78" s="239"/>
-      <c r="D78" s="239"/>
-      <c r="E78" s="239"/>
-      <c r="F78" s="239"/>
-      <c r="G78" s="239"/>
-      <c r="H78" s="239"/>
-      <c r="I78" s="239"/>
-      <c r="J78" s="239"/>
-      <c r="K78" s="239"/>
-      <c r="L78" s="239"/>
-      <c r="M78" s="239"/>
-      <c r="N78" s="239"/>
-      <c r="O78" s="239"/>
-      <c r="P78" s="239"/>
-      <c r="Q78" s="239"/>
-      <c r="R78" s="239"/>
-      <c r="S78" s="239"/>
-      <c r="T78" s="239"/>
+      <c r="B78" s="223"/>
+      <c r="C78" s="223"/>
+      <c r="D78" s="223"/>
+      <c r="E78" s="223"/>
+      <c r="F78" s="223"/>
+      <c r="G78" s="223"/>
+      <c r="H78" s="223"/>
+      <c r="I78" s="223"/>
+      <c r="J78" s="223"/>
+      <c r="K78" s="223"/>
+      <c r="L78" s="223"/>
+      <c r="M78" s="223"/>
+      <c r="N78" s="223"/>
+      <c r="O78" s="223"/>
+      <c r="P78" s="223"/>
+      <c r="Q78" s="223"/>
+      <c r="R78" s="223"/>
+      <c r="S78" s="223"/>
+      <c r="T78" s="223"/>
     </row>
     <row r="87" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B87" s="257" t="s">
+      <c r="B87" s="193" t="s">
         <v>152</v>
       </c>
-      <c r="C87" s="257"/>
-      <c r="D87" s="257"/>
-      <c r="E87" s="257"/>
-      <c r="F87" s="257"/>
-      <c r="G87" s="257"/>
-      <c r="H87" s="257"/>
-      <c r="I87" s="257"/>
-      <c r="J87" s="257"/>
-      <c r="K87" s="257"/>
-      <c r="L87" s="257"/>
-      <c r="M87" s="257"/>
-      <c r="N87" s="257"/>
-      <c r="O87" s="257"/>
-      <c r="P87" s="257"/>
-      <c r="Q87" s="257"/>
-      <c r="R87" s="257"/>
-      <c r="S87" s="257"/>
+      <c r="C87" s="193"/>
+      <c r="D87" s="193"/>
+      <c r="E87" s="193"/>
+      <c r="F87" s="193"/>
+      <c r="G87" s="193"/>
+      <c r="H87" s="193"/>
+      <c r="I87" s="193"/>
+      <c r="J87" s="193"/>
+      <c r="K87" s="193"/>
+      <c r="L87" s="193"/>
+      <c r="M87" s="193"/>
+      <c r="N87" s="193"/>
+      <c r="O87" s="193"/>
+      <c r="P87" s="193"/>
+      <c r="Q87" s="193"/>
+      <c r="R87" s="193"/>
+      <c r="S87" s="193"/>
     </row>
     <row r="88" spans="2:20" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B88" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C88" s="232" t="s">
+      <c r="C88" s="282" t="s">
         <v>2</v>
       </c>
-      <c r="D88" s="232"/>
+      <c r="D88" s="282"/>
       <c r="E88" s="98" t="s">
         <v>130</v>
       </c>
@@ -54549,17 +54549,17 @@
       <c r="P88" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="Q88" s="223" t="s">
+      <c r="Q88" s="194" t="s">
         <v>36</v>
       </c>
-      <c r="R88" s="223"/>
-      <c r="S88" s="223"/>
+      <c r="R88" s="194"/>
+      <c r="S88" s="194"/>
     </row>
     <row r="89" spans="2:20" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B89" s="289" t="s">
+      <c r="B89" s="196" t="s">
         <v>91</v>
       </c>
-      <c r="C89" s="241" t="s">
+      <c r="C89" s="213" t="s">
         <v>114</v>
       </c>
       <c r="D89" s="41" t="s">
@@ -54603,15 +54603,15 @@
       <c r="P89" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="Q89" s="242" t="s">
+      <c r="Q89" s="220" t="s">
         <v>44</v>
       </c>
-      <c r="R89" s="242"/>
-      <c r="S89" s="242"/>
+      <c r="R89" s="220"/>
+      <c r="S89" s="220"/>
     </row>
     <row r="90" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B90" s="240"/>
-      <c r="C90" s="241"/>
+      <c r="B90" s="195"/>
+      <c r="C90" s="213"/>
       <c r="D90" s="41" t="s">
         <v>22</v>
       </c>
@@ -54653,9 +54653,9 @@
       <c r="P90" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="Q90" s="242"/>
-      <c r="R90" s="242"/>
-      <c r="S90" s="242"/>
+      <c r="Q90" s="220"/>
+      <c r="R90" s="220"/>
+      <c r="S90" s="220"/>
     </row>
     <row r="92" spans="2:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B92" s="5" t="s">
@@ -54681,120 +54681,120 @@
       <c r="T92" s="6"/>
     </row>
     <row r="93" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B93" s="239" t="s">
+      <c r="B93" s="223" t="s">
         <v>33</v>
       </c>
-      <c r="C93" s="239"/>
-      <c r="D93" s="239"/>
-      <c r="E93" s="239"/>
-      <c r="F93" s="239"/>
-      <c r="G93" s="239"/>
-      <c r="H93" s="239"/>
-      <c r="I93" s="239"/>
-      <c r="J93" s="239"/>
-      <c r="K93" s="239"/>
-      <c r="L93" s="239"/>
-      <c r="M93" s="239"/>
-      <c r="N93" s="239"/>
-      <c r="O93" s="239"/>
-      <c r="P93" s="239"/>
-      <c r="Q93" s="239"/>
-      <c r="R93" s="239"/>
-      <c r="S93" s="239"/>
-      <c r="T93" s="239"/>
+      <c r="C93" s="223"/>
+      <c r="D93" s="223"/>
+      <c r="E93" s="223"/>
+      <c r="F93" s="223"/>
+      <c r="G93" s="223"/>
+      <c r="H93" s="223"/>
+      <c r="I93" s="223"/>
+      <c r="J93" s="223"/>
+      <c r="K93" s="223"/>
+      <c r="L93" s="223"/>
+      <c r="M93" s="223"/>
+      <c r="N93" s="223"/>
+      <c r="O93" s="223"/>
+      <c r="P93" s="223"/>
+      <c r="Q93" s="223"/>
+      <c r="R93" s="223"/>
+      <c r="S93" s="223"/>
+      <c r="T93" s="223"/>
     </row>
     <row r="94" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B94" s="239"/>
-      <c r="C94" s="239"/>
-      <c r="D94" s="239"/>
-      <c r="E94" s="239"/>
-      <c r="F94" s="239"/>
-      <c r="G94" s="239"/>
-      <c r="H94" s="239"/>
-      <c r="I94" s="239"/>
-      <c r="J94" s="239"/>
-      <c r="K94" s="239"/>
-      <c r="L94" s="239"/>
-      <c r="M94" s="239"/>
-      <c r="N94" s="239"/>
-      <c r="O94" s="239"/>
-      <c r="P94" s="239"/>
-      <c r="Q94" s="239"/>
-      <c r="R94" s="239"/>
-      <c r="S94" s="239"/>
-      <c r="T94" s="239"/>
+      <c r="B94" s="223"/>
+      <c r="C94" s="223"/>
+      <c r="D94" s="223"/>
+      <c r="E94" s="223"/>
+      <c r="F94" s="223"/>
+      <c r="G94" s="223"/>
+      <c r="H94" s="223"/>
+      <c r="I94" s="223"/>
+      <c r="J94" s="223"/>
+      <c r="K94" s="223"/>
+      <c r="L94" s="223"/>
+      <c r="M94" s="223"/>
+      <c r="N94" s="223"/>
+      <c r="O94" s="223"/>
+      <c r="P94" s="223"/>
+      <c r="Q94" s="223"/>
+      <c r="R94" s="223"/>
+      <c r="S94" s="223"/>
+      <c r="T94" s="223"/>
     </row>
     <row r="95" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B95" s="239"/>
-      <c r="C95" s="239"/>
-      <c r="D95" s="239"/>
-      <c r="E95" s="239"/>
-      <c r="F95" s="239"/>
-      <c r="G95" s="239"/>
-      <c r="H95" s="239"/>
-      <c r="I95" s="239"/>
-      <c r="J95" s="239"/>
-      <c r="K95" s="239"/>
-      <c r="L95" s="239"/>
-      <c r="M95" s="239"/>
-      <c r="N95" s="239"/>
-      <c r="O95" s="239"/>
-      <c r="P95" s="239"/>
-      <c r="Q95" s="239"/>
-      <c r="R95" s="239"/>
-      <c r="S95" s="239"/>
-      <c r="T95" s="239"/>
+      <c r="B95" s="223"/>
+      <c r="C95" s="223"/>
+      <c r="D95" s="223"/>
+      <c r="E95" s="223"/>
+      <c r="F95" s="223"/>
+      <c r="G95" s="223"/>
+      <c r="H95" s="223"/>
+      <c r="I95" s="223"/>
+      <c r="J95" s="223"/>
+      <c r="K95" s="223"/>
+      <c r="L95" s="223"/>
+      <c r="M95" s="223"/>
+      <c r="N95" s="223"/>
+      <c r="O95" s="223"/>
+      <c r="P95" s="223"/>
+      <c r="Q95" s="223"/>
+      <c r="R95" s="223"/>
+      <c r="S95" s="223"/>
+      <c r="T95" s="223"/>
     </row>
     <row r="96" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B96" s="239"/>
-      <c r="C96" s="239"/>
-      <c r="D96" s="239"/>
-      <c r="E96" s="239"/>
-      <c r="F96" s="239"/>
-      <c r="G96" s="239"/>
-      <c r="H96" s="239"/>
-      <c r="I96" s="239"/>
-      <c r="J96" s="239"/>
-      <c r="K96" s="239"/>
-      <c r="L96" s="239"/>
-      <c r="M96" s="239"/>
-      <c r="N96" s="239"/>
-      <c r="O96" s="239"/>
-      <c r="P96" s="239"/>
-      <c r="Q96" s="239"/>
-      <c r="R96" s="239"/>
-      <c r="S96" s="239"/>
-      <c r="T96" s="239"/>
+      <c r="B96" s="223"/>
+      <c r="C96" s="223"/>
+      <c r="D96" s="223"/>
+      <c r="E96" s="223"/>
+      <c r="F96" s="223"/>
+      <c r="G96" s="223"/>
+      <c r="H96" s="223"/>
+      <c r="I96" s="223"/>
+      <c r="J96" s="223"/>
+      <c r="K96" s="223"/>
+      <c r="L96" s="223"/>
+      <c r="M96" s="223"/>
+      <c r="N96" s="223"/>
+      <c r="O96" s="223"/>
+      <c r="P96" s="223"/>
+      <c r="Q96" s="223"/>
+      <c r="R96" s="223"/>
+      <c r="S96" s="223"/>
+      <c r="T96" s="223"/>
     </row>
     <row r="106" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="107" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B107" s="260" t="s">
+      <c r="B107" s="206" t="s">
         <v>156</v>
       </c>
-      <c r="C107" s="260"/>
-      <c r="D107" s="260"/>
-      <c r="E107" s="260"/>
-      <c r="F107" s="260"/>
-      <c r="G107" s="260"/>
-      <c r="H107" s="260"/>
-      <c r="I107" s="260"/>
-      <c r="J107" s="260"/>
-      <c r="K107" s="260"/>
-      <c r="L107" s="260"/>
-      <c r="M107" s="260"/>
-      <c r="N107" s="260"/>
-      <c r="O107" s="260"/>
-      <c r="P107" s="260"/>
-      <c r="Q107" s="260"/>
+      <c r="C107" s="206"/>
+      <c r="D107" s="206"/>
+      <c r="E107" s="206"/>
+      <c r="F107" s="206"/>
+      <c r="G107" s="206"/>
+      <c r="H107" s="206"/>
+      <c r="I107" s="206"/>
+      <c r="J107" s="206"/>
+      <c r="K107" s="206"/>
+      <c r="L107" s="206"/>
+      <c r="M107" s="206"/>
+      <c r="N107" s="206"/>
+      <c r="O107" s="206"/>
+      <c r="P107" s="206"/>
+      <c r="Q107" s="206"/>
     </row>
     <row r="108" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B108" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="C108" s="223" t="s">
+      <c r="C108" s="194" t="s">
         <v>2</v>
       </c>
-      <c r="D108" s="223"/>
+      <c r="D108" s="194"/>
       <c r="E108" s="8" t="s">
         <v>3</v>
       </c>
@@ -54836,10 +54836,10 @@
       </c>
     </row>
     <row r="109" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B109" s="244" t="s">
+      <c r="B109" s="285" t="s">
         <v>157</v>
       </c>
-      <c r="C109" s="241" t="s">
+      <c r="C109" s="213" t="s">
         <v>114</v>
       </c>
       <c r="D109" s="41" t="s">
@@ -54888,8 +54888,8 @@
       </c>
     </row>
     <row r="110" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B110" s="244"/>
-      <c r="C110" s="241"/>
+      <c r="B110" s="285"/>
+      <c r="C110" s="213"/>
       <c r="D110" s="41" t="s">
         <v>22</v>
       </c>
@@ -54937,33 +54937,33 @@
     </row>
     <row r="119" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="120" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B120" s="260" t="s">
+      <c r="B120" s="206" t="s">
         <v>161</v>
       </c>
-      <c r="C120" s="260"/>
-      <c r="D120" s="260"/>
-      <c r="E120" s="260"/>
-      <c r="F120" s="260"/>
-      <c r="G120" s="260"/>
-      <c r="H120" s="260"/>
-      <c r="I120" s="260"/>
-      <c r="J120" s="260"/>
-      <c r="K120" s="260"/>
-      <c r="L120" s="260"/>
-      <c r="M120" s="260"/>
-      <c r="N120" s="260"/>
-      <c r="O120" s="260"/>
-      <c r="P120" s="260"/>
-      <c r="Q120" s="260"/>
+      <c r="C120" s="206"/>
+      <c r="D120" s="206"/>
+      <c r="E120" s="206"/>
+      <c r="F120" s="206"/>
+      <c r="G120" s="206"/>
+      <c r="H120" s="206"/>
+      <c r="I120" s="206"/>
+      <c r="J120" s="206"/>
+      <c r="K120" s="206"/>
+      <c r="L120" s="206"/>
+      <c r="M120" s="206"/>
+      <c r="N120" s="206"/>
+      <c r="O120" s="206"/>
+      <c r="P120" s="206"/>
+      <c r="Q120" s="206"/>
     </row>
     <row r="121" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B121" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="C121" s="223" t="s">
+      <c r="C121" s="194" t="s">
         <v>2</v>
       </c>
-      <c r="D121" s="223"/>
+      <c r="D121" s="194"/>
       <c r="E121" s="8" t="s">
         <v>3</v>
       </c>
@@ -55005,10 +55005,10 @@
       </c>
     </row>
     <row r="122" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B122" s="244" t="s">
+      <c r="B122" s="285" t="s">
         <v>162</v>
       </c>
-      <c r="C122" s="241" t="s">
+      <c r="C122" s="213" t="s">
         <v>114</v>
       </c>
       <c r="D122" s="41" t="s">
@@ -55057,10 +55057,10 @@
       </c>
     </row>
     <row r="123" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B123" s="244" t="s">
+      <c r="B123" s="285" t="s">
         <v>162</v>
       </c>
-      <c r="C123" s="241" t="s">
+      <c r="C123" s="213" t="s">
         <v>114</v>
       </c>
       <c r="D123" s="41" t="s">
@@ -55109,10 +55109,10 @@
       </c>
     </row>
     <row r="124" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B124" s="244" t="s">
+      <c r="B124" s="285" t="s">
         <v>163</v>
       </c>
-      <c r="C124" s="241" t="s">
+      <c r="C124" s="213" t="s">
         <v>114</v>
       </c>
       <c r="D124" s="41" t="s">
@@ -55162,8 +55162,8 @@
       </c>
     </row>
     <row r="125" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B125" s="244"/>
-      <c r="C125" s="241"/>
+      <c r="B125" s="285"/>
+      <c r="C125" s="213"/>
       <c r="D125" s="41" t="s">
         <v>22</v>
       </c>
@@ -55212,18 +55212,36 @@
     </row>
   </sheetData>
   <mergeCells count="58">
-    <mergeCell ref="P56:P59"/>
-    <mergeCell ref="P60:P63"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="P36:R37"/>
+    <mergeCell ref="B124:B125"/>
+    <mergeCell ref="C124:C125"/>
+    <mergeCell ref="B122:B123"/>
+    <mergeCell ref="C122:C123"/>
+    <mergeCell ref="B20:R20"/>
+    <mergeCell ref="B21:R24"/>
+    <mergeCell ref="B109:B110"/>
+    <mergeCell ref="C109:C110"/>
+    <mergeCell ref="B89:B90"/>
+    <mergeCell ref="C89:C90"/>
+    <mergeCell ref="Q89:S90"/>
+    <mergeCell ref="B93:T96"/>
+    <mergeCell ref="B107:Q107"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="B120:Q120"/>
+    <mergeCell ref="C121:D121"/>
+    <mergeCell ref="Q88:S88"/>
+    <mergeCell ref="B87:S87"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="B64:Q64"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="B75:T78"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="B68:Q68"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="P66:P67"/>
+    <mergeCell ref="P70:P71"/>
     <mergeCell ref="B9:Q9"/>
     <mergeCell ref="C60:C61"/>
     <mergeCell ref="B13:B14"/>
@@ -55240,36 +55258,18 @@
     <mergeCell ref="B58:B59"/>
     <mergeCell ref="C58:C59"/>
     <mergeCell ref="C10:D10"/>
-    <mergeCell ref="Q88:S88"/>
-    <mergeCell ref="B87:S87"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="B64:Q64"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="B75:T78"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="B68:Q68"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="P66:P67"/>
-    <mergeCell ref="P70:P71"/>
-    <mergeCell ref="B124:B125"/>
-    <mergeCell ref="C124:C125"/>
-    <mergeCell ref="B122:B123"/>
-    <mergeCell ref="C122:C123"/>
-    <mergeCell ref="B20:R20"/>
-    <mergeCell ref="B21:R24"/>
-    <mergeCell ref="B109:B110"/>
-    <mergeCell ref="C109:C110"/>
-    <mergeCell ref="B89:B90"/>
-    <mergeCell ref="C89:C90"/>
-    <mergeCell ref="Q89:S90"/>
-    <mergeCell ref="B93:T96"/>
-    <mergeCell ref="B107:Q107"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="B120:Q120"/>
-    <mergeCell ref="C121:D121"/>
+    <mergeCell ref="P56:P59"/>
+    <mergeCell ref="P60:P63"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="P36:R37"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -55280,7 +55280,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6411E299-5866-CE44-ADC7-A0E34965AEA2}">
-  <dimension ref="B8:S110"/>
+  <dimension ref="B8:R110"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.109375" style="17"/>
@@ -55306,8 +55306,8 @@
     <row r="8" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B8" s="97"/>
       <c r="C8" s="97"/>
-      <c r="D8" s="206"/>
-      <c r="E8" s="206"/>
+      <c r="D8" s="299"/>
+      <c r="E8" s="299"/>
       <c r="F8" s="97"/>
       <c r="G8" s="97"/>
       <c r="H8" s="97"/>
@@ -55323,32 +55323,32 @@
       <c r="R8" s="97"/>
     </row>
     <row r="9" spans="2:18" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="209" t="s">
+      <c r="B9" s="308" t="s">
         <v>164</v>
       </c>
-      <c r="C9" s="209"/>
-      <c r="D9" s="209"/>
-      <c r="E9" s="209"/>
-      <c r="F9" s="209"/>
-      <c r="G9" s="209"/>
-      <c r="H9" s="209"/>
-      <c r="I9" s="209"/>
-      <c r="J9" s="209"/>
-      <c r="K9" s="209"/>
-      <c r="L9" s="209"/>
-      <c r="M9" s="209"/>
-      <c r="N9" s="209"/>
-      <c r="O9" s="209"/>
-      <c r="P9" s="209"/>
+      <c r="C9" s="308"/>
+      <c r="D9" s="308"/>
+      <c r="E9" s="308"/>
+      <c r="F9" s="308"/>
+      <c r="G9" s="308"/>
+      <c r="H9" s="308"/>
+      <c r="I9" s="308"/>
+      <c r="J9" s="308"/>
+      <c r="K9" s="308"/>
+      <c r="L9" s="308"/>
+      <c r="M9" s="308"/>
+      <c r="N9" s="308"/>
+      <c r="O9" s="308"/>
+      <c r="P9" s="308"/>
     </row>
     <row r="10" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B10" s="98" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="207" t="s">
+      <c r="C10" s="317" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="208"/>
+      <c r="D10" s="318"/>
       <c r="E10" s="12" t="s">
         <v>3</v>
       </c>
@@ -55388,10 +55388,10 @@
       <c r="Q10" s="97"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B11" s="186" t="s">
+      <c r="B11" s="319" t="s">
         <v>167</v>
       </c>
-      <c r="C11" s="186" t="s">
+      <c r="C11" s="319" t="s">
         <v>168</v>
       </c>
       <c r="D11" s="34" t="s">
@@ -55439,8 +55439,8 @@
       <c r="Q11" s="97"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B12" s="187"/>
-      <c r="C12" s="187"/>
+      <c r="B12" s="320"/>
+      <c r="C12" s="320"/>
       <c r="D12" s="34" t="s">
         <v>170</v>
       </c>
@@ -55486,10 +55486,10 @@
       <c r="Q12" s="97"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B13" s="186" t="s">
+      <c r="B13" s="319" t="s">
         <v>171</v>
       </c>
-      <c r="C13" s="186" t="s">
+      <c r="C13" s="319" t="s">
         <v>168</v>
       </c>
       <c r="D13" s="34" t="s">
@@ -55537,8 +55537,8 @@
       <c r="Q13" s="97"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B14" s="187"/>
-      <c r="C14" s="187"/>
+      <c r="B14" s="320"/>
+      <c r="C14" s="320"/>
       <c r="D14" s="34" t="s">
         <v>170</v>
       </c>
@@ -55584,10 +55584,10 @@
       <c r="Q14" s="97"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B15" s="186" t="s">
+      <c r="B15" s="319" t="s">
         <v>127</v>
       </c>
-      <c r="C15" s="186" t="s">
+      <c r="C15" s="319" t="s">
         <v>168</v>
       </c>
       <c r="D15" s="34" t="s">
@@ -55635,8 +55635,8 @@
       <c r="Q15" s="97"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B16" s="187"/>
-      <c r="C16" s="187"/>
+      <c r="B16" s="320"/>
+      <c r="C16" s="320"/>
       <c r="D16" s="34" t="s">
         <v>170</v>
       </c>
@@ -55696,93 +55696,93 @@
       <c r="N17" s="27"/>
     </row>
     <row r="18" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B18" s="193" t="s">
+      <c r="B18" s="323" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="194"/>
-      <c r="D18" s="194"/>
-      <c r="E18" s="194"/>
-      <c r="F18" s="194"/>
-      <c r="G18" s="194"/>
-      <c r="H18" s="194"/>
-      <c r="I18" s="194"/>
-      <c r="J18" s="194"/>
-      <c r="K18" s="194"/>
-      <c r="L18" s="194"/>
-      <c r="M18" s="194"/>
-      <c r="N18" s="194"/>
-      <c r="O18" s="194"/>
-      <c r="P18" s="195"/>
+      <c r="C18" s="324"/>
+      <c r="D18" s="324"/>
+      <c r="E18" s="324"/>
+      <c r="F18" s="324"/>
+      <c r="G18" s="324"/>
+      <c r="H18" s="324"/>
+      <c r="I18" s="324"/>
+      <c r="J18" s="324"/>
+      <c r="K18" s="324"/>
+      <c r="L18" s="324"/>
+      <c r="M18" s="324"/>
+      <c r="N18" s="324"/>
+      <c r="O18" s="324"/>
+      <c r="P18" s="325"/>
     </row>
     <row r="19" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="196" t="s">
+      <c r="B19" s="289" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="197"/>
-      <c r="D19" s="197"/>
-      <c r="E19" s="197"/>
-      <c r="F19" s="197"/>
-      <c r="G19" s="197"/>
-      <c r="H19" s="197"/>
-      <c r="I19" s="197"/>
-      <c r="J19" s="197"/>
-      <c r="K19" s="197"/>
-      <c r="L19" s="197"/>
-      <c r="M19" s="197"/>
-      <c r="N19" s="197"/>
-      <c r="O19" s="197"/>
-      <c r="P19" s="198"/>
+      <c r="C19" s="290"/>
+      <c r="D19" s="290"/>
+      <c r="E19" s="290"/>
+      <c r="F19" s="290"/>
+      <c r="G19" s="290"/>
+      <c r="H19" s="290"/>
+      <c r="I19" s="290"/>
+      <c r="J19" s="290"/>
+      <c r="K19" s="290"/>
+      <c r="L19" s="290"/>
+      <c r="M19" s="290"/>
+      <c r="N19" s="290"/>
+      <c r="O19" s="290"/>
+      <c r="P19" s="291"/>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B20" s="199"/>
-      <c r="C20" s="200"/>
-      <c r="D20" s="200"/>
-      <c r="E20" s="200"/>
-      <c r="F20" s="200"/>
-      <c r="G20" s="200"/>
-      <c r="H20" s="200"/>
-      <c r="I20" s="200"/>
-      <c r="J20" s="200"/>
-      <c r="K20" s="200"/>
-      <c r="L20" s="200"/>
-      <c r="M20" s="200"/>
-      <c r="N20" s="200"/>
-      <c r="O20" s="200"/>
-      <c r="P20" s="201"/>
+      <c r="B20" s="292"/>
+      <c r="C20" s="264"/>
+      <c r="D20" s="264"/>
+      <c r="E20" s="264"/>
+      <c r="F20" s="264"/>
+      <c r="G20" s="264"/>
+      <c r="H20" s="264"/>
+      <c r="I20" s="264"/>
+      <c r="J20" s="264"/>
+      <c r="K20" s="264"/>
+      <c r="L20" s="264"/>
+      <c r="M20" s="264"/>
+      <c r="N20" s="264"/>
+      <c r="O20" s="264"/>
+      <c r="P20" s="293"/>
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B21" s="199"/>
-      <c r="C21" s="200"/>
-      <c r="D21" s="200"/>
-      <c r="E21" s="200"/>
-      <c r="F21" s="200"/>
-      <c r="G21" s="200"/>
-      <c r="H21" s="200"/>
-      <c r="I21" s="200"/>
-      <c r="J21" s="200"/>
-      <c r="K21" s="200"/>
-      <c r="L21" s="200"/>
-      <c r="M21" s="200"/>
-      <c r="N21" s="200"/>
-      <c r="O21" s="200"/>
-      <c r="P21" s="201"/>
+      <c r="B21" s="292"/>
+      <c r="C21" s="264"/>
+      <c r="D21" s="264"/>
+      <c r="E21" s="264"/>
+      <c r="F21" s="264"/>
+      <c r="G21" s="264"/>
+      <c r="H21" s="264"/>
+      <c r="I21" s="264"/>
+      <c r="J21" s="264"/>
+      <c r="K21" s="264"/>
+      <c r="L21" s="264"/>
+      <c r="M21" s="264"/>
+      <c r="N21" s="264"/>
+      <c r="O21" s="264"/>
+      <c r="P21" s="293"/>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B22" s="202"/>
-      <c r="C22" s="203"/>
-      <c r="D22" s="203"/>
-      <c r="E22" s="203"/>
-      <c r="F22" s="203"/>
-      <c r="G22" s="203"/>
-      <c r="H22" s="203"/>
-      <c r="I22" s="203"/>
-      <c r="J22" s="203"/>
-      <c r="K22" s="203"/>
-      <c r="L22" s="203"/>
-      <c r="M22" s="203"/>
-      <c r="N22" s="203"/>
-      <c r="O22" s="203"/>
-      <c r="P22" s="204"/>
+      <c r="B22" s="294"/>
+      <c r="C22" s="295"/>
+      <c r="D22" s="295"/>
+      <c r="E22" s="295"/>
+      <c r="F22" s="295"/>
+      <c r="G22" s="295"/>
+      <c r="H22" s="295"/>
+      <c r="I22" s="295"/>
+      <c r="J22" s="295"/>
+      <c r="K22" s="295"/>
+      <c r="L22" s="295"/>
+      <c r="M22" s="295"/>
+      <c r="N22" s="295"/>
+      <c r="O22" s="295"/>
+      <c r="P22" s="296"/>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B23" s="25"/>
@@ -55912,33 +55912,33 @@
       <c r="N31" s="27"/>
     </row>
     <row r="32" spans="2:17" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B32" s="190" t="s">
+      <c r="B32" s="321" t="s">
         <v>173</v>
       </c>
-      <c r="C32" s="191"/>
-      <c r="D32" s="191"/>
-      <c r="E32" s="191"/>
-      <c r="F32" s="191"/>
-      <c r="G32" s="191"/>
-      <c r="H32" s="191"/>
-      <c r="I32" s="191"/>
-      <c r="J32" s="191"/>
-      <c r="K32" s="191"/>
-      <c r="L32" s="191"/>
-      <c r="M32" s="191"/>
-      <c r="N32" s="191"/>
-      <c r="O32" s="191"/>
-      <c r="P32" s="191"/>
-      <c r="Q32" s="192"/>
+      <c r="C32" s="302"/>
+      <c r="D32" s="302"/>
+      <c r="E32" s="302"/>
+      <c r="F32" s="302"/>
+      <c r="G32" s="302"/>
+      <c r="H32" s="302"/>
+      <c r="I32" s="302"/>
+      <c r="J32" s="302"/>
+      <c r="K32" s="302"/>
+      <c r="L32" s="302"/>
+      <c r="M32" s="302"/>
+      <c r="N32" s="302"/>
+      <c r="O32" s="302"/>
+      <c r="P32" s="302"/>
+      <c r="Q32" s="322"/>
     </row>
     <row r="33" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B33" s="98" t="s">
         <v>1</v>
       </c>
-      <c r="C33" s="205" t="s">
+      <c r="C33" s="326" t="s">
         <v>2</v>
       </c>
-      <c r="D33" s="205"/>
+      <c r="D33" s="326"/>
       <c r="E33" s="98" t="s">
         <v>130</v>
       </c>
@@ -55972,16 +55972,16 @@
       <c r="O33" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="P33" s="188" t="s">
+      <c r="P33" s="249" t="s">
         <v>36</v>
       </c>
-      <c r="Q33" s="189"/>
+      <c r="Q33" s="250"/>
     </row>
     <row r="34" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="215" t="s">
+      <c r="B34" s="315" t="s">
         <v>177</v>
       </c>
-      <c r="C34" s="216" t="s">
+      <c r="C34" s="316" t="s">
         <v>168</v>
       </c>
       <c r="D34" s="33" t="s">
@@ -56022,14 +56022,14 @@
       <c r="O34" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="P34" s="224" t="s">
+      <c r="P34" s="216" t="s">
         <v>178</v>
       </c>
-      <c r="Q34" s="225"/>
+      <c r="Q34" s="217"/>
     </row>
     <row r="35" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B35" s="215"/>
-      <c r="C35" s="216"/>
+      <c r="B35" s="315"/>
+      <c r="C35" s="316"/>
       <c r="D35" s="33" t="s">
         <v>22</v>
       </c>
@@ -56068,8 +56068,8 @@
       <c r="O35" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="P35" s="226"/>
-      <c r="Q35" s="227"/>
+      <c r="P35" s="278"/>
+      <c r="Q35" s="280"/>
     </row>
     <row r="36" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B36" s="91" t="s">
@@ -56116,8 +56116,8 @@
       <c r="O36" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="P36" s="228"/>
-      <c r="Q36" s="229"/>
+      <c r="P36" s="218"/>
+      <c r="Q36" s="219"/>
     </row>
     <row r="37" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B37" s="60"/>
@@ -56170,74 +56170,74 @@
       <c r="P39" s="7"/>
     </row>
     <row r="40" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B40" s="217" t="s">
+      <c r="B40" s="198" t="s">
         <v>33</v>
       </c>
-      <c r="C40" s="218"/>
-      <c r="D40" s="218"/>
-      <c r="E40" s="218"/>
-      <c r="F40" s="218"/>
-      <c r="G40" s="218"/>
-      <c r="H40" s="218"/>
-      <c r="I40" s="218"/>
-      <c r="J40" s="218"/>
-      <c r="K40" s="218"/>
-      <c r="L40" s="218"/>
-      <c r="M40" s="218"/>
-      <c r="N40" s="218"/>
-      <c r="O40" s="218"/>
-      <c r="P40" s="219"/>
+      <c r="C40" s="199"/>
+      <c r="D40" s="199"/>
+      <c r="E40" s="199"/>
+      <c r="F40" s="199"/>
+      <c r="G40" s="199"/>
+      <c r="H40" s="199"/>
+      <c r="I40" s="199"/>
+      <c r="J40" s="199"/>
+      <c r="K40" s="199"/>
+      <c r="L40" s="199"/>
+      <c r="M40" s="199"/>
+      <c r="N40" s="199"/>
+      <c r="O40" s="199"/>
+      <c r="P40" s="200"/>
     </row>
     <row r="41" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B41" s="217"/>
-      <c r="C41" s="218"/>
-      <c r="D41" s="218"/>
-      <c r="E41" s="218"/>
-      <c r="F41" s="218"/>
-      <c r="G41" s="218"/>
-      <c r="H41" s="218"/>
-      <c r="I41" s="218"/>
-      <c r="J41" s="218"/>
-      <c r="K41" s="218"/>
-      <c r="L41" s="218"/>
-      <c r="M41" s="218"/>
-      <c r="N41" s="218"/>
-      <c r="O41" s="218"/>
-      <c r="P41" s="219"/>
+      <c r="B41" s="198"/>
+      <c r="C41" s="199"/>
+      <c r="D41" s="199"/>
+      <c r="E41" s="199"/>
+      <c r="F41" s="199"/>
+      <c r="G41" s="199"/>
+      <c r="H41" s="199"/>
+      <c r="I41" s="199"/>
+      <c r="J41" s="199"/>
+      <c r="K41" s="199"/>
+      <c r="L41" s="199"/>
+      <c r="M41" s="199"/>
+      <c r="N41" s="199"/>
+      <c r="O41" s="199"/>
+      <c r="P41" s="200"/>
     </row>
     <row r="42" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B42" s="217"/>
-      <c r="C42" s="218"/>
-      <c r="D42" s="218"/>
-      <c r="E42" s="218"/>
-      <c r="F42" s="218"/>
-      <c r="G42" s="218"/>
-      <c r="H42" s="218"/>
-      <c r="I42" s="218"/>
-      <c r="J42" s="218"/>
-      <c r="K42" s="218"/>
-      <c r="L42" s="218"/>
-      <c r="M42" s="218"/>
-      <c r="N42" s="218"/>
-      <c r="O42" s="218"/>
-      <c r="P42" s="219"/>
+      <c r="B42" s="198"/>
+      <c r="C42" s="199"/>
+      <c r="D42" s="199"/>
+      <c r="E42" s="199"/>
+      <c r="F42" s="199"/>
+      <c r="G42" s="199"/>
+      <c r="H42" s="199"/>
+      <c r="I42" s="199"/>
+      <c r="J42" s="199"/>
+      <c r="K42" s="199"/>
+      <c r="L42" s="199"/>
+      <c r="M42" s="199"/>
+      <c r="N42" s="199"/>
+      <c r="O42" s="199"/>
+      <c r="P42" s="200"/>
     </row>
     <row r="43" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B43" s="220"/>
-      <c r="C43" s="221"/>
-      <c r="D43" s="221"/>
-      <c r="E43" s="221"/>
-      <c r="F43" s="221"/>
-      <c r="G43" s="221"/>
-      <c r="H43" s="221"/>
-      <c r="I43" s="221"/>
-      <c r="J43" s="221"/>
-      <c r="K43" s="221"/>
-      <c r="L43" s="221"/>
-      <c r="M43" s="221"/>
-      <c r="N43" s="221"/>
-      <c r="O43" s="221"/>
-      <c r="P43" s="222"/>
+      <c r="B43" s="201"/>
+      <c r="C43" s="202"/>
+      <c r="D43" s="202"/>
+      <c r="E43" s="202"/>
+      <c r="F43" s="202"/>
+      <c r="G43" s="202"/>
+      <c r="H43" s="202"/>
+      <c r="I43" s="202"/>
+      <c r="J43" s="202"/>
+      <c r="K43" s="202"/>
+      <c r="L43" s="202"/>
+      <c r="M43" s="202"/>
+      <c r="N43" s="202"/>
+      <c r="O43" s="202"/>
+      <c r="P43" s="203"/>
     </row>
     <row r="44" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B44" s="35"/>
@@ -56352,33 +56352,33 @@
       <c r="O51" s="97"/>
     </row>
     <row r="52" spans="2:17" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B52" s="212" t="s">
+      <c r="B52" s="312" t="s">
         <v>181</v>
       </c>
-      <c r="C52" s="213"/>
-      <c r="D52" s="213"/>
-      <c r="E52" s="213"/>
-      <c r="F52" s="213"/>
-      <c r="G52" s="213"/>
-      <c r="H52" s="213"/>
-      <c r="I52" s="213"/>
-      <c r="J52" s="213"/>
-      <c r="K52" s="213"/>
-      <c r="L52" s="213"/>
-      <c r="M52" s="213"/>
-      <c r="N52" s="213"/>
-      <c r="O52" s="213"/>
-      <c r="P52" s="213"/>
-      <c r="Q52" s="214"/>
+      <c r="C52" s="313"/>
+      <c r="D52" s="313"/>
+      <c r="E52" s="313"/>
+      <c r="F52" s="313"/>
+      <c r="G52" s="313"/>
+      <c r="H52" s="313"/>
+      <c r="I52" s="313"/>
+      <c r="J52" s="313"/>
+      <c r="K52" s="313"/>
+      <c r="L52" s="313"/>
+      <c r="M52" s="313"/>
+      <c r="N52" s="313"/>
+      <c r="O52" s="313"/>
+      <c r="P52" s="313"/>
+      <c r="Q52" s="314"/>
     </row>
     <row r="53" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B53" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="C53" s="223" t="s">
+      <c r="C53" s="194" t="s">
         <v>2</v>
       </c>
-      <c r="D53" s="223"/>
+      <c r="D53" s="194"/>
       <c r="E53" s="92" t="s">
         <v>3</v>
       </c>
@@ -56420,10 +56420,10 @@
       </c>
     </row>
     <row r="54" spans="2:17" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="210" t="s">
+      <c r="B54" s="208" t="s">
         <v>182</v>
       </c>
-      <c r="C54" s="211" t="s">
+      <c r="C54" s="297" t="s">
         <v>168</v>
       </c>
       <c r="D54" s="41" t="s">
@@ -56473,8 +56473,8 @@
       </c>
     </row>
     <row r="55" spans="2:17" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="210"/>
-      <c r="C55" s="211"/>
+      <c r="B55" s="208"/>
+      <c r="C55" s="297"/>
       <c r="D55" s="41" t="s">
         <v>22</v>
       </c>
@@ -56522,33 +56522,33 @@
       </c>
     </row>
     <row r="56" spans="2:17" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B56" s="212" t="s">
+      <c r="B56" s="312" t="s">
         <v>185</v>
       </c>
-      <c r="C56" s="213"/>
-      <c r="D56" s="213"/>
-      <c r="E56" s="213"/>
-      <c r="F56" s="213"/>
-      <c r="G56" s="213"/>
-      <c r="H56" s="213"/>
-      <c r="I56" s="213"/>
-      <c r="J56" s="213"/>
-      <c r="K56" s="213"/>
-      <c r="L56" s="213"/>
-      <c r="M56" s="213"/>
-      <c r="N56" s="213"/>
-      <c r="O56" s="213"/>
-      <c r="P56" s="213"/>
-      <c r="Q56" s="214"/>
+      <c r="C56" s="313"/>
+      <c r="D56" s="313"/>
+      <c r="E56" s="313"/>
+      <c r="F56" s="313"/>
+      <c r="G56" s="313"/>
+      <c r="H56" s="313"/>
+      <c r="I56" s="313"/>
+      <c r="J56" s="313"/>
+      <c r="K56" s="313"/>
+      <c r="L56" s="313"/>
+      <c r="M56" s="313"/>
+      <c r="N56" s="313"/>
+      <c r="O56" s="313"/>
+      <c r="P56" s="313"/>
+      <c r="Q56" s="314"/>
     </row>
     <row r="57" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B57" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="C57" s="223" t="s">
+      <c r="C57" s="194" t="s">
         <v>2</v>
       </c>
-      <c r="D57" s="223"/>
+      <c r="D57" s="194"/>
       <c r="E57" s="92" t="s">
         <v>3</v>
       </c>
@@ -56590,10 +56590,10 @@
       </c>
     </row>
     <row r="58" spans="2:17" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="210" t="s">
-        <v>75</v>
-      </c>
-      <c r="C58" s="211" t="s">
+      <c r="B58" s="208" t="s">
+        <v>75</v>
+      </c>
+      <c r="C58" s="297" t="s">
         <v>168</v>
       </c>
       <c r="D58" s="41" t="s">
@@ -56638,13 +56638,13 @@
       <c r="P58" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="Q58" s="234" t="s">
+      <c r="Q58" s="304" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="59" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B59" s="210"/>
-      <c r="C59" s="211"/>
+      <c r="B59" s="208"/>
+      <c r="C59" s="297"/>
       <c r="D59" s="41" t="s">
         <v>22</v>
       </c>
@@ -56687,36 +56687,36 @@
       <c r="P59" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="Q59" s="235"/>
+      <c r="Q59" s="305"/>
     </row>
     <row r="60" spans="2:17" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B60" s="230" t="s">
+      <c r="B60" s="301" t="s">
         <v>187</v>
       </c>
-      <c r="C60" s="191"/>
-      <c r="D60" s="191"/>
-      <c r="E60" s="191"/>
-      <c r="F60" s="191"/>
-      <c r="G60" s="191"/>
-      <c r="H60" s="191"/>
-      <c r="I60" s="191"/>
-      <c r="J60" s="191"/>
-      <c r="K60" s="191"/>
-      <c r="L60" s="191"/>
-      <c r="M60" s="191"/>
-      <c r="N60" s="191"/>
-      <c r="O60" s="191"/>
-      <c r="P60" s="191"/>
-      <c r="Q60" s="231"/>
+      <c r="C60" s="302"/>
+      <c r="D60" s="302"/>
+      <c r="E60" s="302"/>
+      <c r="F60" s="302"/>
+      <c r="G60" s="302"/>
+      <c r="H60" s="302"/>
+      <c r="I60" s="302"/>
+      <c r="J60" s="302"/>
+      <c r="K60" s="302"/>
+      <c r="L60" s="302"/>
+      <c r="M60" s="302"/>
+      <c r="N60" s="302"/>
+      <c r="O60" s="302"/>
+      <c r="P60" s="302"/>
+      <c r="Q60" s="303"/>
     </row>
     <row r="61" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B61" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="C61" s="232" t="s">
+      <c r="C61" s="282" t="s">
         <v>2</v>
       </c>
-      <c r="D61" s="232"/>
+      <c r="D61" s="282"/>
       <c r="E61" s="8" t="s">
         <v>3</v>
       </c>
@@ -56758,10 +56758,10 @@
       </c>
     </row>
     <row r="62" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="233" t="s">
+      <c r="B62" s="309" t="s">
         <v>188</v>
       </c>
-      <c r="C62" s="211" t="s">
+      <c r="C62" s="297" t="s">
         <v>168</v>
       </c>
       <c r="D62" s="41" t="s">
@@ -56806,13 +56806,13 @@
       <c r="P62" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="Q62" s="234" t="s">
+      <c r="Q62" s="304" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="63" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B63" s="233"/>
-      <c r="C63" s="211"/>
+      <c r="B63" s="309"/>
+      <c r="C63" s="297"/>
       <c r="D63" s="41" t="s">
         <v>22</v>
       </c>
@@ -56855,36 +56855,36 @@
       <c r="P63" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="Q63" s="235"/>
+      <c r="Q63" s="305"/>
     </row>
     <row r="64" spans="2:17" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B64" s="230" t="s">
+      <c r="B64" s="301" t="s">
         <v>189</v>
       </c>
-      <c r="C64" s="191"/>
-      <c r="D64" s="191"/>
-      <c r="E64" s="191"/>
-      <c r="F64" s="191"/>
-      <c r="G64" s="191"/>
-      <c r="H64" s="191"/>
-      <c r="I64" s="191"/>
-      <c r="J64" s="191"/>
-      <c r="K64" s="191"/>
-      <c r="L64" s="191"/>
-      <c r="M64" s="191"/>
-      <c r="N64" s="191"/>
-      <c r="O64" s="191"/>
-      <c r="P64" s="191"/>
-      <c r="Q64" s="231"/>
+      <c r="C64" s="302"/>
+      <c r="D64" s="302"/>
+      <c r="E64" s="302"/>
+      <c r="F64" s="302"/>
+      <c r="G64" s="302"/>
+      <c r="H64" s="302"/>
+      <c r="I64" s="302"/>
+      <c r="J64" s="302"/>
+      <c r="K64" s="302"/>
+      <c r="L64" s="302"/>
+      <c r="M64" s="302"/>
+      <c r="N64" s="302"/>
+      <c r="O64" s="302"/>
+      <c r="P64" s="302"/>
+      <c r="Q64" s="303"/>
     </row>
     <row r="65" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B65" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="C65" s="232" t="s">
+      <c r="C65" s="282" t="s">
         <v>2</v>
       </c>
-      <c r="D65" s="232"/>
+      <c r="D65" s="282"/>
       <c r="E65" s="8" t="s">
         <v>3</v>
       </c>
@@ -56926,10 +56926,10 @@
       </c>
     </row>
     <row r="66" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B66" s="233" t="s">
+      <c r="B66" s="309" t="s">
         <v>190</v>
       </c>
-      <c r="C66" s="211" t="s">
+      <c r="C66" s="297" t="s">
         <v>168</v>
       </c>
       <c r="D66" s="41" t="s">
@@ -56974,13 +56974,13 @@
       <c r="P66" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="Q66" s="236" t="s">
+      <c r="Q66" s="306" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="67" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B67" s="233"/>
-      <c r="C67" s="211"/>
+      <c r="B67" s="309"/>
+      <c r="C67" s="297"/>
       <c r="D67" s="41" t="s">
         <v>22</v>
       </c>
@@ -57023,36 +57023,36 @@
       <c r="P67" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="Q67" s="237"/>
+      <c r="Q67" s="310"/>
     </row>
     <row r="68" spans="2:18" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B68" s="230" t="s">
+      <c r="B68" s="301" t="s">
         <v>192</v>
       </c>
-      <c r="C68" s="191"/>
-      <c r="D68" s="191"/>
-      <c r="E68" s="191"/>
-      <c r="F68" s="191"/>
-      <c r="G68" s="191"/>
-      <c r="H68" s="191"/>
-      <c r="I68" s="191"/>
-      <c r="J68" s="191"/>
-      <c r="K68" s="191"/>
-      <c r="L68" s="191"/>
-      <c r="M68" s="191"/>
-      <c r="N68" s="191"/>
-      <c r="O68" s="191"/>
-      <c r="P68" s="191"/>
-      <c r="Q68" s="231"/>
+      <c r="C68" s="302"/>
+      <c r="D68" s="302"/>
+      <c r="E68" s="302"/>
+      <c r="F68" s="302"/>
+      <c r="G68" s="302"/>
+      <c r="H68" s="302"/>
+      <c r="I68" s="302"/>
+      <c r="J68" s="302"/>
+      <c r="K68" s="302"/>
+      <c r="L68" s="302"/>
+      <c r="M68" s="302"/>
+      <c r="N68" s="302"/>
+      <c r="O68" s="302"/>
+      <c r="P68" s="302"/>
+      <c r="Q68" s="303"/>
     </row>
     <row r="69" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B69" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="C69" s="232" t="s">
+      <c r="C69" s="282" t="s">
         <v>2</v>
       </c>
-      <c r="D69" s="232"/>
+      <c r="D69" s="282"/>
       <c r="E69" s="8" t="s">
         <v>3</v>
       </c>
@@ -57094,10 +57094,10 @@
       </c>
     </row>
     <row r="70" spans="2:18" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="210" t="s">
+      <c r="B70" s="208" t="s">
         <v>193</v>
       </c>
-      <c r="C70" s="211" t="s">
+      <c r="C70" s="297" t="s">
         <v>168</v>
       </c>
       <c r="D70" s="41" t="s">
@@ -57142,13 +57142,13 @@
       <c r="P70" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="Q70" s="236" t="s">
+      <c r="Q70" s="306" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="71" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B71" s="210"/>
-      <c r="C71" s="211"/>
+      <c r="B71" s="208"/>
+      <c r="C71" s="297"/>
       <c r="D71" s="41" t="s">
         <v>22</v>
       </c>
@@ -57191,36 +57191,36 @@
       <c r="P71" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="Q71" s="238"/>
+      <c r="Q71" s="311"/>
     </row>
     <row r="72" spans="2:18" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B72" s="230" t="s">
+      <c r="B72" s="301" t="s">
         <v>194</v>
       </c>
-      <c r="C72" s="191"/>
-      <c r="D72" s="191"/>
-      <c r="E72" s="191"/>
-      <c r="F72" s="191"/>
-      <c r="G72" s="191"/>
-      <c r="H72" s="191"/>
-      <c r="I72" s="191"/>
-      <c r="J72" s="191"/>
-      <c r="K72" s="191"/>
-      <c r="L72" s="191"/>
-      <c r="M72" s="191"/>
-      <c r="N72" s="209"/>
-      <c r="O72" s="191"/>
-      <c r="P72" s="191"/>
-      <c r="Q72" s="231"/>
+      <c r="C72" s="302"/>
+      <c r="D72" s="302"/>
+      <c r="E72" s="302"/>
+      <c r="F72" s="302"/>
+      <c r="G72" s="302"/>
+      <c r="H72" s="302"/>
+      <c r="I72" s="302"/>
+      <c r="J72" s="302"/>
+      <c r="K72" s="302"/>
+      <c r="L72" s="302"/>
+      <c r="M72" s="302"/>
+      <c r="N72" s="308"/>
+      <c r="O72" s="302"/>
+      <c r="P72" s="302"/>
+      <c r="Q72" s="303"/>
     </row>
     <row r="73" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B73" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="C73" s="232" t="s">
+      <c r="C73" s="282" t="s">
         <v>2</v>
       </c>
-      <c r="D73" s="232"/>
+      <c r="D73" s="282"/>
       <c r="E73" s="8" t="s">
         <v>3</v>
       </c>
@@ -57262,10 +57262,10 @@
       </c>
     </row>
     <row r="74" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B74" s="210" t="s">
+      <c r="B74" s="208" t="s">
         <v>195</v>
       </c>
-      <c r="C74" s="211" t="s">
+      <c r="C74" s="297" t="s">
         <v>168</v>
       </c>
       <c r="D74" s="41" t="s">
@@ -57310,13 +57310,13 @@
       <c r="P74" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="Q74" s="236" t="s">
+      <c r="Q74" s="306" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="75" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="255"/>
-      <c r="C75" s="245"/>
+      <c r="B75" s="300"/>
+      <c r="C75" s="298"/>
       <c r="D75" s="62" t="s">
         <v>22</v>
       </c>
@@ -57359,15 +57359,15 @@
       <c r="P75" s="62" t="s">
         <v>61</v>
       </c>
-      <c r="Q75" s="243"/>
+      <c r="Q75" s="307"/>
     </row>
     <row r="76" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B76" s="97"/>
       <c r="C76" s="97"/>
-      <c r="D76" s="206" t="s">
+      <c r="D76" s="299" t="s">
         <v>196</v>
       </c>
-      <c r="E76" s="206"/>
+      <c r="E76" s="299"/>
       <c r="F76" s="97"/>
       <c r="G76" s="97"/>
       <c r="H76" s="97"/>
@@ -57383,133 +57383,133 @@
       <c r="R76" s="97"/>
     </row>
     <row r="77" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B77" s="247" t="s">
+      <c r="B77" s="260" t="s">
         <v>32</v>
       </c>
-      <c r="C77" s="248"/>
-      <c r="D77" s="248"/>
-      <c r="E77" s="248"/>
-      <c r="F77" s="248"/>
-      <c r="G77" s="248"/>
-      <c r="H77" s="248"/>
-      <c r="I77" s="248"/>
-      <c r="J77" s="248"/>
-      <c r="K77" s="248"/>
-      <c r="L77" s="248"/>
-      <c r="M77" s="248"/>
-      <c r="N77" s="248"/>
-      <c r="O77" s="248"/>
-      <c r="P77" s="248"/>
-      <c r="Q77" s="248"/>
-      <c r="R77" s="249"/>
+      <c r="C77" s="261"/>
+      <c r="D77" s="261"/>
+      <c r="E77" s="261"/>
+      <c r="F77" s="261"/>
+      <c r="G77" s="261"/>
+      <c r="H77" s="261"/>
+      <c r="I77" s="261"/>
+      <c r="J77" s="261"/>
+      <c r="K77" s="261"/>
+      <c r="L77" s="261"/>
+      <c r="M77" s="261"/>
+      <c r="N77" s="261"/>
+      <c r="O77" s="261"/>
+      <c r="P77" s="261"/>
+      <c r="Q77" s="261"/>
+      <c r="R77" s="262"/>
     </row>
     <row r="78" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B78" s="250" t="s">
+      <c r="B78" s="263" t="s">
         <v>33</v>
       </c>
-      <c r="C78" s="200"/>
-      <c r="D78" s="200"/>
-      <c r="E78" s="200"/>
-      <c r="F78" s="200"/>
-      <c r="G78" s="200"/>
-      <c r="H78" s="200"/>
-      <c r="I78" s="200"/>
-      <c r="J78" s="200"/>
-      <c r="K78" s="200"/>
-      <c r="L78" s="200"/>
-      <c r="M78" s="200"/>
-      <c r="N78" s="200"/>
-      <c r="O78" s="200"/>
-      <c r="P78" s="200"/>
-      <c r="Q78" s="200"/>
-      <c r="R78" s="251"/>
+      <c r="C78" s="264"/>
+      <c r="D78" s="264"/>
+      <c r="E78" s="264"/>
+      <c r="F78" s="264"/>
+      <c r="G78" s="264"/>
+      <c r="H78" s="264"/>
+      <c r="I78" s="264"/>
+      <c r="J78" s="264"/>
+      <c r="K78" s="264"/>
+      <c r="L78" s="264"/>
+      <c r="M78" s="264"/>
+      <c r="N78" s="264"/>
+      <c r="O78" s="264"/>
+      <c r="P78" s="264"/>
+      <c r="Q78" s="264"/>
+      <c r="R78" s="265"/>
     </row>
     <row r="79" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B79" s="250"/>
-      <c r="C79" s="200"/>
-      <c r="D79" s="200"/>
-      <c r="E79" s="200"/>
-      <c r="F79" s="200"/>
-      <c r="G79" s="200"/>
-      <c r="H79" s="200"/>
-      <c r="I79" s="200"/>
-      <c r="J79" s="200"/>
-      <c r="K79" s="200"/>
-      <c r="L79" s="200"/>
-      <c r="M79" s="200"/>
-      <c r="N79" s="200"/>
-      <c r="O79" s="200"/>
-      <c r="P79" s="200"/>
-      <c r="Q79" s="200"/>
-      <c r="R79" s="251"/>
+      <c r="B79" s="263"/>
+      <c r="C79" s="264"/>
+      <c r="D79" s="264"/>
+      <c r="E79" s="264"/>
+      <c r="F79" s="264"/>
+      <c r="G79" s="264"/>
+      <c r="H79" s="264"/>
+      <c r="I79" s="264"/>
+      <c r="J79" s="264"/>
+      <c r="K79" s="264"/>
+      <c r="L79" s="264"/>
+      <c r="M79" s="264"/>
+      <c r="N79" s="264"/>
+      <c r="O79" s="264"/>
+      <c r="P79" s="264"/>
+      <c r="Q79" s="264"/>
+      <c r="R79" s="265"/>
     </row>
     <row r="80" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B80" s="250"/>
-      <c r="C80" s="200"/>
-      <c r="D80" s="200"/>
-      <c r="E80" s="200"/>
-      <c r="F80" s="200"/>
-      <c r="G80" s="200"/>
-      <c r="H80" s="200"/>
-      <c r="I80" s="200"/>
-      <c r="J80" s="200"/>
-      <c r="K80" s="200"/>
-      <c r="L80" s="200"/>
-      <c r="M80" s="200"/>
-      <c r="N80" s="200"/>
-      <c r="O80" s="200"/>
-      <c r="P80" s="200"/>
-      <c r="Q80" s="200"/>
-      <c r="R80" s="251"/>
+      <c r="B80" s="263"/>
+      <c r="C80" s="264"/>
+      <c r="D80" s="264"/>
+      <c r="E80" s="264"/>
+      <c r="F80" s="264"/>
+      <c r="G80" s="264"/>
+      <c r="H80" s="264"/>
+      <c r="I80" s="264"/>
+      <c r="J80" s="264"/>
+      <c r="K80" s="264"/>
+      <c r="L80" s="264"/>
+      <c r="M80" s="264"/>
+      <c r="N80" s="264"/>
+      <c r="O80" s="264"/>
+      <c r="P80" s="264"/>
+      <c r="Q80" s="264"/>
+      <c r="R80" s="265"/>
     </row>
     <row r="81" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B81" s="252"/>
-      <c r="C81" s="253"/>
-      <c r="D81" s="253"/>
-      <c r="E81" s="253"/>
-      <c r="F81" s="253"/>
-      <c r="G81" s="253"/>
-      <c r="H81" s="253"/>
-      <c r="I81" s="253"/>
-      <c r="J81" s="253"/>
-      <c r="K81" s="253"/>
-      <c r="L81" s="253"/>
-      <c r="M81" s="253"/>
-      <c r="N81" s="253"/>
-      <c r="O81" s="253"/>
-      <c r="P81" s="253"/>
-      <c r="Q81" s="253"/>
-      <c r="R81" s="254"/>
+      <c r="B81" s="266"/>
+      <c r="C81" s="267"/>
+      <c r="D81" s="267"/>
+      <c r="E81" s="267"/>
+      <c r="F81" s="267"/>
+      <c r="G81" s="267"/>
+      <c r="H81" s="267"/>
+      <c r="I81" s="267"/>
+      <c r="J81" s="267"/>
+      <c r="K81" s="267"/>
+      <c r="L81" s="267"/>
+      <c r="M81" s="267"/>
+      <c r="N81" s="267"/>
+      <c r="O81" s="267"/>
+      <c r="P81" s="267"/>
+      <c r="Q81" s="267"/>
+      <c r="R81" s="268"/>
     </row>
     <row r="89" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B89" s="246" t="s">
+      <c r="B89" s="269" t="s">
         <v>197</v>
       </c>
-      <c r="C89" s="246"/>
-      <c r="D89" s="246"/>
-      <c r="E89" s="246"/>
-      <c r="F89" s="246"/>
-      <c r="G89" s="246"/>
-      <c r="H89" s="246"/>
-      <c r="I89" s="246"/>
-      <c r="J89" s="246"/>
-      <c r="K89" s="246"/>
-      <c r="L89" s="246"/>
-      <c r="M89" s="246"/>
-      <c r="N89" s="246"/>
-      <c r="O89" s="246"/>
-      <c r="P89" s="246"/>
-      <c r="Q89" s="246"/>
-      <c r="R89" s="246"/>
+      <c r="C89" s="269"/>
+      <c r="D89" s="269"/>
+      <c r="E89" s="269"/>
+      <c r="F89" s="269"/>
+      <c r="G89" s="269"/>
+      <c r="H89" s="269"/>
+      <c r="I89" s="269"/>
+      <c r="J89" s="269"/>
+      <c r="K89" s="269"/>
+      <c r="L89" s="269"/>
+      <c r="M89" s="269"/>
+      <c r="N89" s="269"/>
+      <c r="O89" s="269"/>
+      <c r="P89" s="269"/>
+      <c r="Q89" s="269"/>
+      <c r="R89" s="269"/>
     </row>
     <row r="90" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B90" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C90" s="232" t="s">
+      <c r="C90" s="282" t="s">
         <v>2</v>
       </c>
-      <c r="D90" s="232"/>
+      <c r="D90" s="282"/>
       <c r="E90" s="98" t="s">
         <v>130</v>
       </c>
@@ -57546,16 +57546,16 @@
       <c r="P90" s="95" t="s">
         <v>123</v>
       </c>
-      <c r="Q90" s="223" t="s">
+      <c r="Q90" s="194" t="s">
         <v>36</v>
       </c>
-      <c r="R90" s="223"/>
+      <c r="R90" s="194"/>
     </row>
     <row r="91" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B91" s="240" t="s">
+      <c r="B91" s="195" t="s">
         <v>91</v>
       </c>
-      <c r="C91" s="241" t="s">
+      <c r="C91" s="213" t="s">
         <v>168</v>
       </c>
       <c r="D91" s="41" t="s">
@@ -57599,14 +57599,14 @@
       <c r="P91" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="Q91" s="242" t="s">
+      <c r="Q91" s="220" t="s">
         <v>44</v>
       </c>
-      <c r="R91" s="242"/>
+      <c r="R91" s="220"/>
     </row>
     <row r="92" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B92" s="240"/>
-      <c r="C92" s="241"/>
+      <c r="B92" s="195"/>
+      <c r="C92" s="213"/>
       <c r="D92" s="41" t="s">
         <v>22</v>
       </c>
@@ -57648,8 +57648,8 @@
       <c r="P92" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="Q92" s="242"/>
-      <c r="R92" s="242"/>
+      <c r="Q92" s="220"/>
+      <c r="R92" s="220"/>
     </row>
     <row r="94" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B94" s="5" t="s">
@@ -57673,82 +57673,82 @@
       <c r="R94" s="6"/>
     </row>
     <row r="95" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B95" s="239" t="s">
+      <c r="B95" s="223" t="s">
         <v>33</v>
       </c>
-      <c r="C95" s="239"/>
-      <c r="D95" s="239"/>
-      <c r="E95" s="239"/>
-      <c r="F95" s="239"/>
-      <c r="G95" s="239"/>
-      <c r="H95" s="239"/>
-      <c r="I95" s="239"/>
-      <c r="J95" s="239"/>
-      <c r="K95" s="239"/>
-      <c r="L95" s="239"/>
-      <c r="M95" s="239"/>
-      <c r="N95" s="239"/>
-      <c r="O95" s="239"/>
-      <c r="P95" s="239"/>
-      <c r="Q95" s="239"/>
-      <c r="R95" s="239"/>
+      <c r="C95" s="223"/>
+      <c r="D95" s="223"/>
+      <c r="E95" s="223"/>
+      <c r="F95" s="223"/>
+      <c r="G95" s="223"/>
+      <c r="H95" s="223"/>
+      <c r="I95" s="223"/>
+      <c r="J95" s="223"/>
+      <c r="K95" s="223"/>
+      <c r="L95" s="223"/>
+      <c r="M95" s="223"/>
+      <c r="N95" s="223"/>
+      <c r="O95" s="223"/>
+      <c r="P95" s="223"/>
+      <c r="Q95" s="223"/>
+      <c r="R95" s="223"/>
     </row>
     <row r="96" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B96" s="239"/>
-      <c r="C96" s="239"/>
-      <c r="D96" s="239"/>
-      <c r="E96" s="239"/>
-      <c r="F96" s="239"/>
-      <c r="G96" s="239"/>
-      <c r="H96" s="239"/>
-      <c r="I96" s="239"/>
-      <c r="J96" s="239"/>
-      <c r="K96" s="239"/>
-      <c r="L96" s="239"/>
-      <c r="M96" s="239"/>
-      <c r="N96" s="239"/>
-      <c r="O96" s="239"/>
-      <c r="P96" s="239"/>
-      <c r="Q96" s="239"/>
-      <c r="R96" s="239"/>
+      <c r="B96" s="223"/>
+      <c r="C96" s="223"/>
+      <c r="D96" s="223"/>
+      <c r="E96" s="223"/>
+      <c r="F96" s="223"/>
+      <c r="G96" s="223"/>
+      <c r="H96" s="223"/>
+      <c r="I96" s="223"/>
+      <c r="J96" s="223"/>
+      <c r="K96" s="223"/>
+      <c r="L96" s="223"/>
+      <c r="M96" s="223"/>
+      <c r="N96" s="223"/>
+      <c r="O96" s="223"/>
+      <c r="P96" s="223"/>
+      <c r="Q96" s="223"/>
+      <c r="R96" s="223"/>
     </row>
     <row r="97" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B97" s="239"/>
-      <c r="C97" s="239"/>
-      <c r="D97" s="239"/>
-      <c r="E97" s="239"/>
-      <c r="F97" s="239"/>
-      <c r="G97" s="239"/>
-      <c r="H97" s="239"/>
-      <c r="I97" s="239"/>
-      <c r="J97" s="239"/>
-      <c r="K97" s="239"/>
-      <c r="L97" s="239"/>
-      <c r="M97" s="239"/>
-      <c r="N97" s="239"/>
-      <c r="O97" s="239"/>
-      <c r="P97" s="239"/>
-      <c r="Q97" s="239"/>
-      <c r="R97" s="239"/>
+      <c r="B97" s="223"/>
+      <c r="C97" s="223"/>
+      <c r="D97" s="223"/>
+      <c r="E97" s="223"/>
+      <c r="F97" s="223"/>
+      <c r="G97" s="223"/>
+      <c r="H97" s="223"/>
+      <c r="I97" s="223"/>
+      <c r="J97" s="223"/>
+      <c r="K97" s="223"/>
+      <c r="L97" s="223"/>
+      <c r="M97" s="223"/>
+      <c r="N97" s="223"/>
+      <c r="O97" s="223"/>
+      <c r="P97" s="223"/>
+      <c r="Q97" s="223"/>
+      <c r="R97" s="223"/>
     </row>
     <row r="98" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B98" s="239"/>
-      <c r="C98" s="239"/>
-      <c r="D98" s="239"/>
-      <c r="E98" s="239"/>
-      <c r="F98" s="239"/>
-      <c r="G98" s="239"/>
-      <c r="H98" s="239"/>
-      <c r="I98" s="239"/>
-      <c r="J98" s="239"/>
-      <c r="K98" s="239"/>
-      <c r="L98" s="239"/>
-      <c r="M98" s="239"/>
-      <c r="N98" s="239"/>
-      <c r="O98" s="239"/>
-      <c r="P98" s="239"/>
-      <c r="Q98" s="239"/>
-      <c r="R98" s="239"/>
+      <c r="B98" s="223"/>
+      <c r="C98" s="223"/>
+      <c r="D98" s="223"/>
+      <c r="E98" s="223"/>
+      <c r="F98" s="223"/>
+      <c r="G98" s="223"/>
+      <c r="H98" s="223"/>
+      <c r="I98" s="223"/>
+      <c r="J98" s="223"/>
+      <c r="K98" s="223"/>
+      <c r="L98" s="223"/>
+      <c r="M98" s="223"/>
+      <c r="N98" s="223"/>
+      <c r="O98" s="223"/>
+      <c r="P98" s="223"/>
+      <c r="Q98" s="223"/>
+      <c r="R98" s="223"/>
     </row>
     <row r="99" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B99" s="94"/>
@@ -57785,34 +57785,34 @@
       <c r="C104" s="26"/>
     </row>
     <row r="105" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B105" s="256" t="s">
+      <c r="B105" s="192" t="s">
         <v>199</v>
       </c>
-      <c r="C105" s="257"/>
-      <c r="D105" s="257"/>
-      <c r="E105" s="257"/>
-      <c r="F105" s="257"/>
-      <c r="G105" s="257"/>
-      <c r="H105" s="257"/>
-      <c r="I105" s="257"/>
-      <c r="J105" s="257"/>
-      <c r="K105" s="257"/>
-      <c r="L105" s="257"/>
-      <c r="M105" s="257"/>
-      <c r="N105" s="257"/>
-      <c r="O105" s="257"/>
-      <c r="P105" s="257"/>
-      <c r="Q105" s="257"/>
-      <c r="R105" s="257"/>
+      <c r="C105" s="193"/>
+      <c r="D105" s="193"/>
+      <c r="E105" s="193"/>
+      <c r="F105" s="193"/>
+      <c r="G105" s="193"/>
+      <c r="H105" s="193"/>
+      <c r="I105" s="193"/>
+      <c r="J105" s="193"/>
+      <c r="K105" s="193"/>
+      <c r="L105" s="193"/>
+      <c r="M105" s="193"/>
+      <c r="N105" s="193"/>
+      <c r="O105" s="193"/>
+      <c r="P105" s="193"/>
+      <c r="Q105" s="193"/>
+      <c r="R105" s="193"/>
     </row>
     <row r="106" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B106" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="C106" s="223" t="s">
+      <c r="C106" s="194" t="s">
         <v>2</v>
       </c>
-      <c r="D106" s="223"/>
+      <c r="D106" s="194"/>
       <c r="E106" s="8" t="s">
         <v>3</v>
       </c>
@@ -57857,10 +57857,10 @@
       </c>
     </row>
     <row r="107" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B107" s="244" t="s">
+      <c r="B107" s="285" t="s">
         <v>102</v>
       </c>
-      <c r="C107" s="241" t="s">
+      <c r="C107" s="213" t="s">
         <v>168</v>
       </c>
       <c r="D107" s="41" t="s">
@@ -57912,8 +57912,8 @@
       </c>
     </row>
     <row r="108" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B108" s="244"/>
-      <c r="C108" s="241"/>
+      <c r="B108" s="285"/>
+      <c r="C108" s="213"/>
       <c r="D108" s="41" t="s">
         <v>22</v>
       </c>
@@ -57963,10 +57963,10 @@
       </c>
     </row>
     <row r="109" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B109" s="244" t="s">
+      <c r="B109" s="285" t="s">
         <v>163</v>
       </c>
-      <c r="C109" s="241" t="s">
+      <c r="C109" s="213" t="s">
         <v>168</v>
       </c>
       <c r="D109" s="41" t="s">
@@ -58019,8 +58019,8 @@
       </c>
     </row>
     <row r="110" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B110" s="244"/>
-      <c r="C110" s="241"/>
+      <c r="B110" s="285"/>
+      <c r="C110" s="213"/>
       <c r="D110" s="41" t="s">
         <v>22</v>
       </c>
@@ -58072,30 +58072,29 @@
     </row>
   </sheetData>
   <mergeCells count="63">
-    <mergeCell ref="C106:D106"/>
-    <mergeCell ref="B109:B110"/>
-    <mergeCell ref="C109:C110"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="B89:R89"/>
-    <mergeCell ref="D76:E76"/>
-    <mergeCell ref="B77:R77"/>
-    <mergeCell ref="B78:R81"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="B107:B108"/>
-    <mergeCell ref="C107:C108"/>
-    <mergeCell ref="B105:R105"/>
-    <mergeCell ref="B64:Q64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="Q58:Q59"/>
-    <mergeCell ref="B95:R98"/>
-    <mergeCell ref="Q90:R90"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="C91:C92"/>
-    <mergeCell ref="Q91:R92"/>
-    <mergeCell ref="Q74:Q75"/>
-    <mergeCell ref="B72:Q72"/>
-    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="P33:Q33"/>
+    <mergeCell ref="B32:Q32"/>
+    <mergeCell ref="B18:P18"/>
+    <mergeCell ref="B19:P22"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="B9:P9"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="B56:Q56"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="B40:P43"/>
+    <mergeCell ref="B52:Q52"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="P34:Q36"/>
     <mergeCell ref="C57:D57"/>
     <mergeCell ref="B68:Q68"/>
     <mergeCell ref="C69:D69"/>
@@ -58112,29 +58111,30 @@
     <mergeCell ref="B58:B59"/>
     <mergeCell ref="Q66:Q67"/>
     <mergeCell ref="Q70:Q71"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="B56:Q56"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="B40:P43"/>
-    <mergeCell ref="B52:Q52"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="P34:Q36"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="B9:P9"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="P33:Q33"/>
-    <mergeCell ref="B32:Q32"/>
-    <mergeCell ref="B18:P18"/>
-    <mergeCell ref="B19:P22"/>
-    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="B64:Q64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="Q58:Q59"/>
+    <mergeCell ref="B95:R98"/>
+    <mergeCell ref="Q90:R90"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="C91:C92"/>
+    <mergeCell ref="Q91:R92"/>
+    <mergeCell ref="Q74:Q75"/>
+    <mergeCell ref="B72:Q72"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="C106:D106"/>
+    <mergeCell ref="B109:B110"/>
+    <mergeCell ref="C109:C110"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="B89:R89"/>
+    <mergeCell ref="D76:E76"/>
+    <mergeCell ref="B77:R77"/>
+    <mergeCell ref="B78:R81"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="B107:B108"/>
+    <mergeCell ref="C107:C108"/>
+    <mergeCell ref="B105:R105"/>
   </mergeCells>
   <phoneticPr fontId="12" alignment="center"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -58177,33 +58177,33 @@
   </cols>
   <sheetData>
     <row r="7" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B7" s="256" t="s">
-        <v>200</v>
-      </c>
-      <c r="C7" s="257"/>
-      <c r="D7" s="257"/>
-      <c r="E7" s="257"/>
-      <c r="F7" s="257"/>
-      <c r="G7" s="257"/>
-      <c r="H7" s="257"/>
-      <c r="I7" s="257"/>
-      <c r="J7" s="257"/>
-      <c r="K7" s="257"/>
-      <c r="L7" s="257"/>
-      <c r="M7" s="257"/>
-      <c r="N7" s="257"/>
-      <c r="O7" s="257"/>
-      <c r="P7" s="257"/>
-      <c r="Q7" s="257"/>
+      <c r="B7" s="192" t="s">
+        <v>200</v>
+      </c>
+      <c r="C7" s="193"/>
+      <c r="D7" s="193"/>
+      <c r="E7" s="193"/>
+      <c r="F7" s="193"/>
+      <c r="G7" s="193"/>
+      <c r="H7" s="193"/>
+      <c r="I7" s="193"/>
+      <c r="J7" s="193"/>
+      <c r="K7" s="193"/>
+      <c r="L7" s="193"/>
+      <c r="M7" s="193"/>
+      <c r="N7" s="193"/>
+      <c r="O7" s="193"/>
+      <c r="P7" s="193"/>
+      <c r="Q7" s="193"/>
     </row>
     <row r="8" spans="2:19" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B8" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="223" t="s">
+      <c r="C8" s="194" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="223"/>
+      <c r="D8" s="194"/>
       <c r="E8" s="92" t="s">
         <v>3</v>
       </c>
@@ -58297,33 +58297,33 @@
       </c>
     </row>
     <row r="10" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B10" s="256" t="s">
-        <v>200</v>
-      </c>
-      <c r="C10" s="257"/>
-      <c r="D10" s="257"/>
-      <c r="E10" s="257"/>
-      <c r="F10" s="257"/>
-      <c r="G10" s="257"/>
-      <c r="H10" s="257"/>
-      <c r="I10" s="257"/>
-      <c r="J10" s="257"/>
-      <c r="K10" s="257"/>
-      <c r="L10" s="257"/>
-      <c r="M10" s="257"/>
-      <c r="N10" s="257"/>
-      <c r="O10" s="257"/>
-      <c r="P10" s="257"/>
-      <c r="Q10" s="257"/>
+      <c r="B10" s="192" t="s">
+        <v>200</v>
+      </c>
+      <c r="C10" s="193"/>
+      <c r="D10" s="193"/>
+      <c r="E10" s="193"/>
+      <c r="F10" s="193"/>
+      <c r="G10" s="193"/>
+      <c r="H10" s="193"/>
+      <c r="I10" s="193"/>
+      <c r="J10" s="193"/>
+      <c r="K10" s="193"/>
+      <c r="L10" s="193"/>
+      <c r="M10" s="193"/>
+      <c r="N10" s="193"/>
+      <c r="O10" s="193"/>
+      <c r="P10" s="193"/>
+      <c r="Q10" s="193"/>
     </row>
     <row r="11" spans="2:19" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B11" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="223" t="s">
+      <c r="C11" s="194" t="s">
         <v>2</v>
       </c>
-      <c r="D11" s="223"/>
+      <c r="D11" s="194"/>
       <c r="E11" s="92" t="s">
         <v>3</v>
       </c>
@@ -58365,10 +58365,10 @@
       </c>
     </row>
     <row r="12" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B12" s="289" t="s">
+      <c r="B12" s="196" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="240" t="s">
+      <c r="C12" s="195" t="s">
         <v>114</v>
       </c>
       <c r="D12" s="88" t="s">
@@ -58417,8 +58417,8 @@
       </c>
     </row>
     <row r="13" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B13" s="290"/>
-      <c r="C13" s="240"/>
+      <c r="B13" s="197"/>
+      <c r="C13" s="195"/>
       <c r="D13" s="88" t="s">
         <v>22</v>
       </c>
@@ -58465,34 +58465,34 @@
       </c>
     </row>
     <row r="14" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B14" s="256" t="s">
+      <c r="B14" s="192" t="s">
         <v>204</v>
       </c>
-      <c r="C14" s="257"/>
-      <c r="D14" s="257"/>
-      <c r="E14" s="257"/>
-      <c r="F14" s="257"/>
-      <c r="G14" s="257"/>
-      <c r="H14" s="257"/>
-      <c r="I14" s="257"/>
-      <c r="J14" s="257"/>
-      <c r="K14" s="257"/>
-      <c r="L14" s="257"/>
-      <c r="M14" s="257"/>
-      <c r="N14" s="257"/>
-      <c r="O14" s="257"/>
-      <c r="P14" s="257"/>
-      <c r="Q14" s="257"/>
-      <c r="R14" s="257"/>
+      <c r="C14" s="193"/>
+      <c r="D14" s="193"/>
+      <c r="E14" s="193"/>
+      <c r="F14" s="193"/>
+      <c r="G14" s="193"/>
+      <c r="H14" s="193"/>
+      <c r="I14" s="193"/>
+      <c r="J14" s="193"/>
+      <c r="K14" s="193"/>
+      <c r="L14" s="193"/>
+      <c r="M14" s="193"/>
+      <c r="N14" s="193"/>
+      <c r="O14" s="193"/>
+      <c r="P14" s="193"/>
+      <c r="Q14" s="193"/>
+      <c r="R14" s="193"/>
     </row>
     <row r="15" spans="2:19" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B15" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="C15" s="223" t="s">
+      <c r="C15" s="194" t="s">
         <v>2</v>
       </c>
-      <c r="D15" s="223"/>
+      <c r="D15" s="194"/>
       <c r="E15" s="92" t="s">
         <v>3</v>
       </c>
@@ -58540,10 +58540,10 @@
       </c>
     </row>
     <row r="16" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B16" s="240" t="s">
+      <c r="B16" s="195" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="240" t="s">
+      <c r="C16" s="195" t="s">
         <v>168</v>
       </c>
       <c r="D16" s="88" t="s">
@@ -58598,8 +58598,8 @@
       </c>
     </row>
     <row r="17" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B17" s="240"/>
-      <c r="C17" s="240"/>
+      <c r="B17" s="195"/>
+      <c r="C17" s="195"/>
       <c r="D17" s="88" t="s">
         <v>22</v>
       </c>
@@ -58652,33 +58652,33 @@
       </c>
     </row>
     <row r="18" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B18" s="325" t="s">
+      <c r="B18" s="188" t="s">
         <v>208</v>
       </c>
-      <c r="C18" s="326"/>
-      <c r="D18" s="326"/>
-      <c r="E18" s="326"/>
-      <c r="F18" s="326"/>
-      <c r="G18" s="326"/>
-      <c r="H18" s="326"/>
-      <c r="I18" s="326"/>
-      <c r="J18" s="326"/>
-      <c r="K18" s="326"/>
-      <c r="L18" s="326"/>
-      <c r="M18" s="326"/>
-      <c r="N18" s="326"/>
-      <c r="O18" s="326"/>
-      <c r="P18" s="326"/>
-      <c r="Q18" s="326"/>
+      <c r="C18" s="189"/>
+      <c r="D18" s="189"/>
+      <c r="E18" s="189"/>
+      <c r="F18" s="189"/>
+      <c r="G18" s="189"/>
+      <c r="H18" s="189"/>
+      <c r="I18" s="189"/>
+      <c r="J18" s="189"/>
+      <c r="K18" s="189"/>
+      <c r="L18" s="189"/>
+      <c r="M18" s="189"/>
+      <c r="N18" s="189"/>
+      <c r="O18" s="189"/>
+      <c r="P18" s="189"/>
+      <c r="Q18" s="189"/>
     </row>
     <row r="19" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B19" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="C19" s="223" t="s">
+      <c r="C19" s="194" t="s">
         <v>2</v>
       </c>
-      <c r="D19" s="223"/>
+      <c r="D19" s="194"/>
       <c r="E19" s="92" t="s">
         <v>3</v>
       </c>
@@ -58712,16 +58712,16 @@
       <c r="O19" s="92" t="s">
         <v>14</v>
       </c>
-      <c r="P19" s="323" t="s">
+      <c r="P19" s="186" t="s">
         <v>141</v>
       </c>
-      <c r="Q19" s="324"/>
+      <c r="Q19" s="187"/>
     </row>
     <row r="20" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B20" s="240" t="s">
+      <c r="B20" s="195" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="240" t="s">
+      <c r="C20" s="195" t="s">
         <v>209</v>
       </c>
       <c r="D20" s="88" t="s">
@@ -58768,8 +58768,8 @@
       <c r="Q20" s="41"/>
     </row>
     <row r="21" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B21" s="240"/>
-      <c r="C21" s="240"/>
+      <c r="B21" s="195"/>
+      <c r="C21" s="195"/>
       <c r="D21" s="88" t="s">
         <v>22</v>
       </c>
@@ -58814,32 +58814,32 @@
       <c r="Q21" s="41"/>
     </row>
     <row r="22" spans="2:19" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="270" t="s">
+      <c r="B22" s="190" t="s">
         <v>211</v>
       </c>
-      <c r="C22" s="271"/>
-      <c r="D22" s="271"/>
-      <c r="E22" s="271"/>
-      <c r="F22" s="271"/>
-      <c r="G22" s="271"/>
-      <c r="H22" s="271"/>
-      <c r="I22" s="271"/>
-      <c r="J22" s="271"/>
-      <c r="K22" s="271"/>
-      <c r="L22" s="271"/>
-      <c r="M22" s="271"/>
-      <c r="N22" s="271"/>
-      <c r="O22" s="271"/>
+      <c r="C22" s="191"/>
+      <c r="D22" s="191"/>
+      <c r="E22" s="191"/>
+      <c r="F22" s="191"/>
+      <c r="G22" s="191"/>
+      <c r="H22" s="191"/>
+      <c r="I22" s="191"/>
+      <c r="J22" s="191"/>
+      <c r="K22" s="191"/>
+      <c r="L22" s="191"/>
+      <c r="M22" s="191"/>
+      <c r="N22" s="191"/>
+      <c r="O22" s="191"/>
       <c r="P22" s="183"/>
     </row>
     <row r="23" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B23" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="C23" s="223" t="s">
+      <c r="C23" s="194" t="s">
         <v>2</v>
       </c>
-      <c r="D23" s="223"/>
+      <c r="D23" s="194"/>
       <c r="E23" s="92" t="s">
         <v>3</v>
       </c>
@@ -58873,14 +58873,14 @@
       <c r="O23" s="92" t="s">
         <v>141</v>
       </c>
-      <c r="P23" s="321"/>
-      <c r="Q23" s="322"/>
+      <c r="P23" s="204"/>
+      <c r="Q23" s="205"/>
     </row>
     <row r="24" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B24" s="240" t="s">
+      <c r="B24" s="195" t="s">
         <v>16</v>
       </c>
-      <c r="C24" s="240" t="s">
+      <c r="C24" s="195" t="s">
         <v>212</v>
       </c>
       <c r="D24" s="88" t="s">
@@ -58925,8 +58925,8 @@
       <c r="P24" s="181"/>
     </row>
     <row r="25" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B25" s="240"/>
-      <c r="C25" s="240"/>
+      <c r="B25" s="195"/>
+      <c r="C25" s="195"/>
       <c r="D25" s="88" t="s">
         <v>22</v>
       </c>
@@ -58989,78 +58989,78 @@
       <c r="Q27" s="7"/>
     </row>
     <row r="28" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B28" s="217" t="s">
+      <c r="B28" s="198" t="s">
         <v>33</v>
       </c>
-      <c r="C28" s="218"/>
-      <c r="D28" s="218"/>
-      <c r="E28" s="218"/>
-      <c r="F28" s="218"/>
-      <c r="G28" s="218"/>
-      <c r="H28" s="218"/>
-      <c r="I28" s="218"/>
-      <c r="J28" s="218"/>
-      <c r="K28" s="218"/>
-      <c r="L28" s="218"/>
-      <c r="M28" s="218"/>
-      <c r="N28" s="218"/>
-      <c r="O28" s="218"/>
-      <c r="P28" s="218"/>
-      <c r="Q28" s="219"/>
+      <c r="C28" s="199"/>
+      <c r="D28" s="199"/>
+      <c r="E28" s="199"/>
+      <c r="F28" s="199"/>
+      <c r="G28" s="199"/>
+      <c r="H28" s="199"/>
+      <c r="I28" s="199"/>
+      <c r="J28" s="199"/>
+      <c r="K28" s="199"/>
+      <c r="L28" s="199"/>
+      <c r="M28" s="199"/>
+      <c r="N28" s="199"/>
+      <c r="O28" s="199"/>
+      <c r="P28" s="199"/>
+      <c r="Q28" s="200"/>
     </row>
     <row r="29" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B29" s="217"/>
-      <c r="C29" s="218"/>
-      <c r="D29" s="218"/>
-      <c r="E29" s="218"/>
-      <c r="F29" s="218"/>
-      <c r="G29" s="218"/>
-      <c r="H29" s="218"/>
-      <c r="I29" s="218"/>
-      <c r="J29" s="218"/>
-      <c r="K29" s="218"/>
-      <c r="L29" s="218"/>
-      <c r="M29" s="218"/>
-      <c r="N29" s="218"/>
-      <c r="O29" s="218"/>
-      <c r="P29" s="218"/>
-      <c r="Q29" s="219"/>
+      <c r="B29" s="198"/>
+      <c r="C29" s="199"/>
+      <c r="D29" s="199"/>
+      <c r="E29" s="199"/>
+      <c r="F29" s="199"/>
+      <c r="G29" s="199"/>
+      <c r="H29" s="199"/>
+      <c r="I29" s="199"/>
+      <c r="J29" s="199"/>
+      <c r="K29" s="199"/>
+      <c r="L29" s="199"/>
+      <c r="M29" s="199"/>
+      <c r="N29" s="199"/>
+      <c r="O29" s="199"/>
+      <c r="P29" s="199"/>
+      <c r="Q29" s="200"/>
     </row>
     <row r="30" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B30" s="217"/>
-      <c r="C30" s="218"/>
-      <c r="D30" s="218"/>
-      <c r="E30" s="218"/>
-      <c r="F30" s="218"/>
-      <c r="G30" s="218"/>
-      <c r="H30" s="218"/>
-      <c r="I30" s="218"/>
-      <c r="J30" s="218"/>
-      <c r="K30" s="218"/>
-      <c r="L30" s="218"/>
-      <c r="M30" s="218"/>
-      <c r="N30" s="218"/>
-      <c r="O30" s="218"/>
-      <c r="P30" s="218"/>
-      <c r="Q30" s="219"/>
+      <c r="B30" s="198"/>
+      <c r="C30" s="199"/>
+      <c r="D30" s="199"/>
+      <c r="E30" s="199"/>
+      <c r="F30" s="199"/>
+      <c r="G30" s="199"/>
+      <c r="H30" s="199"/>
+      <c r="I30" s="199"/>
+      <c r="J30" s="199"/>
+      <c r="K30" s="199"/>
+      <c r="L30" s="199"/>
+      <c r="M30" s="199"/>
+      <c r="N30" s="199"/>
+      <c r="O30" s="199"/>
+      <c r="P30" s="199"/>
+      <c r="Q30" s="200"/>
     </row>
     <row r="31" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B31" s="220"/>
-      <c r="C31" s="221"/>
-      <c r="D31" s="221"/>
-      <c r="E31" s="221"/>
-      <c r="F31" s="221"/>
-      <c r="G31" s="221"/>
-      <c r="H31" s="221"/>
-      <c r="I31" s="221"/>
-      <c r="J31" s="221"/>
-      <c r="K31" s="221"/>
-      <c r="L31" s="221"/>
-      <c r="M31" s="221"/>
-      <c r="N31" s="221"/>
-      <c r="O31" s="221"/>
-      <c r="P31" s="221"/>
-      <c r="Q31" s="222"/>
+      <c r="B31" s="201"/>
+      <c r="C31" s="202"/>
+      <c r="D31" s="202"/>
+      <c r="E31" s="202"/>
+      <c r="F31" s="202"/>
+      <c r="G31" s="202"/>
+      <c r="H31" s="202"/>
+      <c r="I31" s="202"/>
+      <c r="J31" s="202"/>
+      <c r="K31" s="202"/>
+      <c r="L31" s="202"/>
+      <c r="M31" s="202"/>
+      <c r="N31" s="202"/>
+      <c r="O31" s="202"/>
+      <c r="P31" s="202"/>
+      <c r="Q31" s="203"/>
     </row>
     <row r="32" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B32" s="28"/>
@@ -59191,6 +59191,11 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="Q8QWR99fVBSjr/N+QJ5sN0j0nsH8KPKoQYLV4vBQ74oWL/09oW0eyqdJeaMlf/zDXBq0rfJdHkHd9SkH2J1I6Q==" saltValue="HK24cjogG/wtsm2rA2gHiA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="21">
+    <mergeCell ref="B28:Q31"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="P23:Q23"/>
     <mergeCell ref="P19:Q19"/>
     <mergeCell ref="B18:Q18"/>
     <mergeCell ref="B22:O22"/>
@@ -59207,11 +59212,6 @@
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="C12:C13"/>
-    <mergeCell ref="B28:Q31"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="P23:Q23"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -59221,6 +59221,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8bf418b7-79e0-4993-aa07-d31c53a64380">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="268ad1c4-fabf-4dd0-b894-8fd5403102c0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BF631F92D611394D900040A4BC36CE07" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="711a2ec75ffd0c152903cfa2dedf38be">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8bf418b7-79e0-4993-aa07-d31c53a64380" xmlns:ns3="268ad1c4-fabf-4dd0-b894-8fd5403102c0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0628c710989f2757c815e19c03677863" ns2:_="" ns3:_="">
     <xsd:import namespace="8bf418b7-79e0-4993-aa07-d31c53a64380"/>
@@ -59443,27 +59463,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{900DAED1-575B-462E-9521-61C8D8B6DAE7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8bf418b7-79e0-4993-aa07-d31c53a64380"/>
+    <ds:schemaRef ds:uri="268ad1c4-fabf-4dd0-b894-8fd5403102c0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8bf418b7-79e0-4993-aa07-d31c53a64380">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="268ad1c4-fabf-4dd0-b894-8fd5403102c0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AAFA3EB-B8AB-4135-B122-0B0233A6C07D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A722593-7143-4ACD-9A00-2A0E70214590}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -59480,23 +59499,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AAFA3EB-B8AB-4135-B122-0B0233A6C07D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{900DAED1-575B-462E-9521-61C8D8B6DAE7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8bf418b7-79e0-4993-aa07-d31c53a64380"/>
-    <ds:schemaRef ds:uri="268ad1c4-fabf-4dd0-b894-8fd5403102c0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>